--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q237"/>
+  <dimension ref="A1:Q238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -18157,7 +18157,7 @@
     <row r="230" ht="90" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.5-seed42/experiment_20260921_120326.json</t>
+          <t>nvflare-local-eps0.1-seed42/experiment_20260921_140256.json</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005871; Yeom medio=0.49943211120599784; Shadow medio=0.49976200000000004; LiRA composto=0.501998</t>
+          <t>LiRA medio=0.4988614; Yeom medio=0.5018064078840749; Shadow medio=0.5014569000000001; LiRA composto=0.498668</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.5-seed42/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.1-seed42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr">
@@ -18234,7 +18234,7 @@
     <row r="231" ht="90" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
+          <t>nvflare-local-eps0.5-seed42/experiment_20260921_120326.json</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -18244,11 +18244,11 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I231" s="3" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
+          <t>LiRA medio=0.5005871; Yeom medio=0.49943211120599784; Shadow medio=0.49976200000000004; LiRA composto=0.501998</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.5-seed42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M231" s="4" t="inlineStr">
@@ -18311,7 +18311,7 @@
     <row r="232" ht="90" customHeight="1">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
+          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -18325,7 +18325,7 @@
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
+          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="233" ht="90" customHeight="1">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
+          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="D233" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
+          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M233" s="4" t="inlineStr">
@@ -18465,7 +18465,7 @@
     <row r="234" ht="90" customHeight="1">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
+          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
+          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr">
@@ -18542,7 +18542,7 @@
     <row r="235" ht="90" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
+          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -18556,7 +18556,7 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
+          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M235" s="4" t="inlineStr">
@@ -18619,7 +18619,7 @@
     <row r="236" ht="90" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
+          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -18629,11 +18629,11 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H236" s="3" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
+          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr">
@@ -18696,7 +18696,7 @@
     <row r="237" ht="90" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
+          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr">
@@ -18769,6 +18769,83 @@
       </c>
       <c r="P237" s="3" t="n"/>
       <c r="Q237" s="3" t="n"/>
+    </row>
+    <row r="238" ht="90" customHeight="1">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I238" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J238" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M238" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O238" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P238" s="3" t="n"/>
+      <c r="Q238" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q238"/>
+  <dimension ref="A1:Q258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=1; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=1; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=1; epoche=5; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=1; epoche=5; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=0.21421011636007342</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=None</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
@@ -18157,7 +18157,7 @@
     <row r="230" ht="90" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.1-seed42/experiment_20260921_140256.json</t>
+          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -18171,7 +18171,7 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988614; Yeom medio=0.5018064078840749; Shadow medio=0.5014569000000001; LiRA composto=0.498668</t>
+          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.1-seed42/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr">
@@ -18234,7 +18234,7 @@
     <row r="231" ht="90" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.5-seed42/experiment_20260921_120326.json</t>
+          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -18248,7 +18248,7 @@
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005871; Yeom medio=0.49943211120599784; Shadow medio=0.49976200000000004; LiRA composto=0.501998</t>
+          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.5-seed42/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M231" s="4" t="inlineStr">
@@ -18846,6 +18846,1546 @@
       </c>
       <c r="P238" s="3" t="n"/>
       <c r="Q238" s="3" t="n"/>
+    </row>
+    <row r="239" ht="90" customHeight="1">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps16/experiment_20260923_183148.json</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I239" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J239" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M239" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O239" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P239" s="3" t="n"/>
+      <c r="Q239" s="3" t="n"/>
+    </row>
+    <row r="240" ht="90" customHeight="1">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps16/experiment_20260923_203243.json</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I240" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J240" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M240" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O240" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P240" s="3" t="n"/>
+      <c r="Q240" s="3" t="n"/>
+    </row>
+    <row r="241" ht="90" customHeight="1">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps16/experiment_20260923_223219.json</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I241" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J241" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M241" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O241" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P241" s="3" t="n"/>
+      <c r="Q241" s="3" t="n"/>
+    </row>
+    <row r="242" ht="90" customHeight="1">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps16/experiment_20260924_003215.json</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I242" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J242" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
+        </is>
+      </c>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M242" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O242" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P242" s="3" t="n"/>
+      <c r="Q242" s="3" t="n"/>
+    </row>
+    <row r="243" ht="90" customHeight="1">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps16/experiment_20260924_023219.json</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I243" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J243" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
+        </is>
+      </c>
+      <c r="K243" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L243" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M243" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O243" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P243" s="3" t="n"/>
+      <c r="Q243" s="3" t="n"/>
+    </row>
+    <row r="244" ht="90" customHeight="1">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps2/experiment_20260922_134148.json</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I244" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J244" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M244" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O244" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P244" s="3" t="n"/>
+      <c r="Q244" s="3" t="n"/>
+    </row>
+    <row r="245" ht="90" customHeight="1">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps2/experiment_20260922_154640.json</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H245" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I245" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J245" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
+        </is>
+      </c>
+      <c r="K245" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L245" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M245" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O245" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P245" s="3" t="n"/>
+      <c r="Q245" s="3" t="n"/>
+    </row>
+    <row r="246" ht="90" customHeight="1">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps2/experiment_20260922_175039.json</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I246" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M246" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O246" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P246" s="3" t="n"/>
+      <c r="Q246" s="3" t="n"/>
+    </row>
+    <row r="247" ht="90" customHeight="1">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps2/experiment_20260922_180414.json</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I247" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J247" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M247" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O247" s="3" t="inlineStr">
+        <is>
+          <t>nessuna metrica MIA nel JSON</t>
+        </is>
+      </c>
+      <c r="P247" s="3" t="n"/>
+      <c r="Q247" s="3" t="n"/>
+    </row>
+    <row r="248" ht="90" customHeight="1">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps2/experiment_20260922_200439.json</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I248" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J248" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O248" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P248" s="3" t="n"/>
+      <c r="Q248" s="3" t="n"/>
+    </row>
+    <row r="249" ht="90" customHeight="1">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps4/experiment_20260922_220310.json</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I249" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J249" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M249" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O249" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P249" s="3" t="n"/>
+      <c r="Q249" s="3" t="n"/>
+    </row>
+    <row r="250" ht="90" customHeight="1">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps4/experiment_20260923_000138.json</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I250" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J250" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M250" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O250" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P250" s="3" t="n"/>
+      <c r="Q250" s="3" t="n"/>
+    </row>
+    <row r="251" ht="90" customHeight="1">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps4/experiment_20260923_020058.json</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I251" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J251" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M251" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O251" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P251" s="3" t="n"/>
+      <c r="Q251" s="3" t="n"/>
+    </row>
+    <row r="252" ht="90" customHeight="1">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps4/experiment_20260923_040025.json</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I252" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J252" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M252" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O252" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P252" s="3" t="n"/>
+      <c r="Q252" s="3" t="n"/>
+    </row>
+    <row r="253" ht="90" customHeight="1">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps4/experiment_20260923_055955.json</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I253" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J253" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M253" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O253" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P253" s="3" t="n"/>
+      <c r="Q253" s="3" t="n"/>
+    </row>
+    <row r="254" ht="90" customHeight="1">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_080158.json</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I254" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J254" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M254" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O254" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P254" s="3" t="n"/>
+      <c r="Q254" s="3" t="n"/>
+    </row>
+    <row r="255" ht="90" customHeight="1">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_100736.json</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I255" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J255" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M255" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O255" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P255" s="3" t="n"/>
+      <c r="Q255" s="3" t="n"/>
+    </row>
+    <row r="256" ht="90" customHeight="1">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_121447.json</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I256" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J256" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M256" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O256" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P256" s="3" t="n"/>
+      <c r="Q256" s="3" t="n"/>
+    </row>
+    <row r="257" ht="90" customHeight="1">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_142154.json</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M257" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O257" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P257" s="3" t="n"/>
+      <c r="Q257" s="3" t="n"/>
+    </row>
+    <row r="258" ht="90" customHeight="1">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_162834.json</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M258" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O258" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P258" s="3" t="n"/>
+      <c r="Q258" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q258"/>
+  <dimension ref="A1:Q259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -19620,7 +19620,7 @@
     <row r="249" ht="90" customHeight="1">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260922_220310.json</t>
+          <t>rq1-eps2/experiment_20260924_102430.json</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -19630,11 +19630,11 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D249" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
+          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="L249" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M249" s="4" t="inlineStr">
@@ -19697,7 +19697,7 @@
     <row r="250" ht="90" customHeight="1">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_000138.json</t>
+          <t>rq1-eps4/experiment_20260922_220310.json</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -19711,7 +19711,7 @@
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
+          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
         </is>
       </c>
       <c r="K250" s="3" t="inlineStr">
@@ -19774,7 +19774,7 @@
     <row r="251" ht="90" customHeight="1">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_020058.json</t>
+          <t>rq1-eps4/experiment_20260923_000138.json</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
+          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
         </is>
       </c>
       <c r="K251" s="3" t="inlineStr">
@@ -19851,7 +19851,7 @@
     <row r="252" ht="90" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_040025.json</t>
+          <t>rq1-eps4/experiment_20260923_020058.json</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -19865,7 +19865,7 @@
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
+          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
         </is>
       </c>
       <c r="K252" s="3" t="inlineStr">
@@ -19928,7 +19928,7 @@
     <row r="253" ht="90" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_055955.json</t>
+          <t>rq1-eps4/experiment_20260923_040025.json</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -19942,7 +19942,7 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
+          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
         </is>
       </c>
       <c r="K253" s="3" t="inlineStr">
@@ -20005,7 +20005,7 @@
     <row r="254" ht="90" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_080158.json</t>
+          <t>rq1-eps4/experiment_20260923_055955.json</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -20015,11 +20015,11 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
+          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M254" s="4" t="inlineStr">
@@ -20082,7 +20082,7 @@
     <row r="255" ht="90" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_100736.json</t>
+          <t>rq1-eps8/experiment_20260923_080158.json</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -20096,7 +20096,7 @@
         </is>
       </c>
       <c r="D255" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
+          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
@@ -20159,7 +20159,7 @@
     <row r="256" ht="90" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_121447.json</t>
+          <t>rq1-eps8/experiment_20260923_100736.json</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -20173,7 +20173,7 @@
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
+          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="257" ht="90" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_142154.json</t>
+          <t>rq1-eps8/experiment_20260923_121447.json</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="D257" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
         </is>
       </c>
       <c r="K257" s="3" t="inlineStr">
@@ -20313,7 +20313,7 @@
     <row r="258" ht="90" customHeight="1">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_162834.json</t>
+          <t>rq1-eps8/experiment_20260923_142154.json</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
         </is>
       </c>
       <c r="K258" s="3" t="inlineStr">
@@ -20386,6 +20386,83 @@
       </c>
       <c r="P258" s="3" t="n"/>
       <c r="Q258" s="3" t="n"/>
+    </row>
+    <row r="259" ht="90" customHeight="1">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_162834.json</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I259" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J259" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M259" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O259" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P259" s="3" t="n"/>
+      <c r="Q259" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q259"/>
+  <dimension ref="A1:Q261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8443,17 +8443,17 @@
     <row r="104" ht="90" customHeight="1">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>_d1_canary_realdp/experiment_20260915_155515.json</t>
+          <t>_ctrl_common_init/experiment_20260924_164941.json</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -8466,42 +8466,42 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=3.0; eps_avanzata=13.466136166722686; eps_migliore=3.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5684823333333333; Yeom medio=0.5125405041450996; Shadow medio=0.4964413333333333; LiRA composto=0.585495; canary raw=0.522222</t>
+          <t>LiRA medio=0.5007892; Yeom medio=0.4976995214031545; Shadow medio=0.4996777; LiRA composto=0.499127</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/ctrl_common_init_s42.log</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>experiments/_d1_canary_realdp/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M104" s="5" t="inlineStr">
-        <is>
-          <t>incompleta</t>
+          <t>experiments/_ctrl_common_init/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>il blocco 'canary' non e' registrato nel config del JSON (i run anteriori allo Sprint 10zz+113 non lo salvavano) e NON esiste un log con il nome di questo sweep: k, duplicati e swap_assignment non sono ricavabili da nessuna evidenza. Dedurli dal nome della cartella sarebbe l'analogia che la guida vieta</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P104" s="3" t="n"/>
@@ -8520,17 +8520,17 @@
     <row r="105" ht="90" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>_diag_eps16_dpfedavg/experiment_20260825_185903.json</t>
+          <t>_d1_canary_realdp/experiment_20260915_155515.json</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=48.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=3.0; eps_avanzata=13.466136166722686; eps_migliore=3.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009666666666667; Yeom medio=0.49929623738820234; Shadow medio=0.49944066666666664; LiRA composto=0.502921</t>
+          <t>LiRA medio=0.5684823333333333; Yeom medio=0.5125405041450996; Shadow medio=0.4964413333333333; LiRA composto=0.585495; canary raw=0.522222</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
@@ -8573,12 +8573,12 @@
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>experiments/_diag_eps16_dpfedavg/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M105" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+          <t>experiments/_d1_canary_realdp/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>il blocco 'canary' non e' registrato nel config del JSON (i run anteriori allo Sprint 10zz+113 non lo salvavano) e NON esiste un log con il nome di questo sweep: k, duplicati e swap_assignment non sono ricavabili da nessuna evidenza. Dedurli dal nome della cartella sarebbe l'analogia che la guida vieta</t>
         </is>
       </c>
       <c r="P105" s="3" t="n"/>
@@ -8597,7 +8597,7 @@
     <row r="106" ht="90" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>_diag_eps8_dpfedavg/experiment_20260825_181943.json</t>
+          <t>_diag_eps16_dpfedavg/experiment_20260825_185903.json</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=24.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=48.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4984166666666667; Yeom medio=0.4983470669966777; Shadow medio=0.4996566666666667; LiRA composto=0.498507</t>
+          <t>LiRA medio=0.5009666666666667; Yeom medio=0.49929623738820234; Shadow medio=0.49944066666666664; LiRA composto=0.502921</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>experiments/_diag_eps8_dpfedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_diag_eps16_dpfedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
@@ -8674,7 +8674,7 @@
     <row r="107" ht="90" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>_diag_matched_formula/experiment_20260825_105509.json</t>
+          <t>_diag_eps8_dpfedavg/experiment_20260825_181943.json</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=24.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
+          <t>LiRA medio=0.4984166666666667; Yeom medio=0.4983470669966777; Shadow medio=0.4996566666666667; LiRA composto=0.498507</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>experiments/_diag_matched_formula/ (JSON + xlsx + history/)</t>
+          <t>experiments/_diag_eps8_dpfedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
@@ -8751,7 +8751,7 @@
     <row r="108" ht="90" customHeight="1">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>_diag_matched_formula_central/experiment_20260825_113549.json</t>
+          <t>_diag_matched_formula/experiment_20260825_105509.json</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.57541; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.502163</t>
+          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>experiments/_diag_matched_formula_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_diag_matched_formula/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
@@ -8828,7 +8828,7 @@
     <row r="109" ht="90" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>_fedmia_gradient_composed/experiment_20260909_121051.json</t>
+          <t>_diag_matched_formula_central/experiment_20260825_113549.json</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
@@ -8856,22 +8856,22 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4976726; Yeom medio=0.4981408010032867; Shadow medio=0.4993120999999999; LiRA composto=0.499417</t>
+          <t>LiRA medio=0.57541; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.502163</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>experiments/_fedmia_gradient_composed/ (JSON + xlsx + history/)</t>
+          <t>experiments/_diag_matched_formula_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M109" s="4" t="inlineStr">
@@ -8905,21 +8905,21 @@
     <row r="110" ht="90" customHeight="1">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>_final_rdp_base_s123/experiment_20260917_114537.json</t>
+          <t>_fedmia_gradient_composed/experiment_20260909_121051.json</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3716253333333333; Yeom medio=0.544175343292591; Shadow medio=0.522849; LiRA composto=0.370585; canary raw=0.5475</t>
+          <t>LiRA medio=0.4976726; Yeom medio=0.4981408010032867; Shadow medio=0.4993120999999999; LiRA composto=0.499417</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_rdp_base_s123/ (JSON + xlsx + history/)</t>
+          <t>experiments/_fedmia_gradient_composed/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P110" s="3" t="n"/>
@@ -8982,7 +8982,7 @@
     <row r="111" ht="90" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>_final_rdp_base_s42/experiment_20260917_101623.json</t>
+          <t>_final_rdp_base_s123/experiment_20260917_114537.json</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -8992,11 +8992,11 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
+          <t>LiRA medio=0.3716253333333333; Yeom medio=0.544175343292591; Shadow medio=0.522849; LiRA composto=0.370585; canary raw=0.5475</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_rdp_base_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_rdp_base_s123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
@@ -9059,7 +9059,7 @@
     <row r="112" ht="90" customHeight="1">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>_final_rdp_base_s456/experiment_20260917_131212.json</t>
+          <t>_final_rdp_base_s42/experiment_20260917_101623.json</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9069,11 +9069,11 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=None</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3989773333333333; Yeom medio=0.521484080277652; Shadow medio=0.5131353333333334; LiRA composto=0.394945; canary raw=0.5225</t>
+          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_rdp_base_s456/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_rdp_base_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
@@ -9136,7 +9136,7 @@
     <row r="113" ht="90" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>_final_rdp_swap_s123/experiment_20260917_122014.json</t>
+          <t>_final_rdp_base_s456/experiment_20260917_131212.json</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9146,11 +9146,11 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>123</v>
+        <v>456</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.36622400000000005; Yeom medio=0.5097470574920778; Shadow medio=0.5274679999999999; LiRA composto=0.359186; canary raw=0.53</t>
+          <t>LiRA medio=0.3989773333333333; Yeom medio=0.521484080277652; Shadow medio=0.5131353333333334; LiRA composto=0.394945; canary raw=0.5225</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="L113" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_rdp_swap_s123/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_rdp_base_s456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="114" ht="90" customHeight="1">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>_final_rdp_swap_s42/experiment_20260917_105048.json</t>
+          <t>_final_rdp_swap_s123/experiment_20260917_122014.json</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4395576666666667; Yeom medio=0.5423692847442281; Shadow medio=0.570198; LiRA composto=0.432963; canary raw=0.5425</t>
+          <t>LiRA medio=0.36622400000000005; Yeom medio=0.5097470574920778; Shadow medio=0.5274679999999999; LiRA composto=0.359186; canary raw=0.53</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_rdp_swap_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_rdp_swap_s123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
@@ -9290,7 +9290,7 @@
     <row r="115" ht="90" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>_final_rdp_swap_s456/experiment_20260917_134602.json</t>
+          <t>_final_rdp_swap_s42/experiment_20260917_105048.json</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3885706666666667; Yeom medio=0.5285762788592123; Shadow medio=0.5455383333333333; LiRA composto=0.36846; canary raw=0.5325</t>
+          <t>LiRA medio=0.4395576666666667; Yeom medio=0.5423692847442281; Shadow medio=0.570198; LiRA composto=0.432963; canary raw=0.5425</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_rdp_swap_s456/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_rdp_swap_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
@@ -9367,7 +9367,7 @@
     <row r="116" ht="90" customHeight="1">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>_final_ref_base_s123/experiment_20260917_110026.json</t>
+          <t>_final_rdp_swap_s456/experiment_20260917_134602.json</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -9377,11 +9377,11 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True; record_dp: enabled=True, nm=5.0, eps_record_dp=3.792014934616144</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>123</v>
+        <v>456</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.615377; Yeom medio=0.6045462690508526; Shadow medio=0.497404; LiRA composto=0.62657; canary raw=0.78</t>
+          <t>LiRA medio=0.3885706666666667; Yeom medio=0.5285762788592123; Shadow medio=0.5455383333333333; LiRA composto=0.36846; canary raw=0.5325</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_ref_base_s123/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_rdp_swap_s456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
@@ -9444,7 +9444,7 @@
     <row r="117" ht="90" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>_final_ref_base_s42/experiment_20260917_093221.json</t>
+          <t>_final_ref_base_s123/experiment_20260917_110026.json</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -9454,11 +9454,11 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
+          <t>LiRA medio=0.615377; Yeom medio=0.6045462690508526; Shadow medio=0.497404; LiRA composto=0.62657; canary raw=0.78</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_ref_base_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_ref_base_s123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
@@ -9521,7 +9521,7 @@
     <row r="118" ht="90" customHeight="1">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>_final_ref_base_s456/experiment_20260917_122939.json</t>
+          <t>_final_ref_base_s42/experiment_20260917_093221.json</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -9531,11 +9531,11 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.6429623333333333; Yeom medio=0.5848658895427795; Shadow medio=0.563997; LiRA composto=0.64425; canary raw=0.7625</t>
+          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_ref_base_s456/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_ref_base_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
@@ -9598,7 +9598,7 @@
     <row r="119" ht="90" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>_final_ref_swap_s123/experiment_20260917_111003.json</t>
+          <t>_final_ref_base_s456/experiment_20260917_122939.json</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>123</v>
+        <v>456</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.6251559999999999; Yeom medio=0.5902345518334088; Shadow medio=0.5192203333333333; LiRA composto=0.657257; canary raw=0.8175</t>
+          <t>LiRA medio=0.6429623333333333; Yeom medio=0.5848658895427795; Shadow medio=0.563997; LiRA composto=0.64425; canary raw=0.7625</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_ref_swap_s123/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_ref_base_s456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
@@ -9675,7 +9675,7 @@
     <row r="120" ht="90" customHeight="1">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>_final_ref_swap_s42/experiment_20260917_094148.json</t>
+          <t>_final_ref_swap_s123/experiment_20260917_111003.json</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -9685,11 +9685,11 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5788006666666666; Yeom medio=0.5812797080126754; Shadow medio=0.5382526666666666; LiRA composto=0.590644; canary raw=0.665</t>
+          <t>LiRA medio=0.6251559999999999; Yeom medio=0.5902345518334088; Shadow medio=0.5192203333333333; LiRA composto=0.657257; canary raw=0.8175</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_ref_swap_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_ref_swap_s123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
@@ -9752,7 +9752,7 @@
     <row r="121" ht="90" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>_final_ref_swap_s456/experiment_20260917_123857.json</t>
+          <t>_final_ref_swap_s42/experiment_20260917_094148.json</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -9762,11 +9762,11 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.6724739999999999; Yeom medio=0.5979586351290177; Shadow medio=0.5162023333333333; LiRA composto=0.678944; canary raw=0.7975</t>
+          <t>LiRA medio=0.5788006666666666; Yeom medio=0.5812797080126754; Shadow medio=0.5382526666666666; LiRA composto=0.590644; canary raw=0.665</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>experiments/_final_ref_swap_s456/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_ref_swap_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
@@ -9829,21 +9829,21 @@
     <row r="122" ht="90" customHeight="1">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>_hour_circular_encoding/experiment_20260831_161645.json</t>
+          <t>_final_ref_swap_s456/experiment_20260917_123857.json</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=32; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5077716666666667; Yeom medio=0.5180579176114891; Shadow medio=0.49286333333333326; LiRA composto=0.500047</t>
+          <t>LiRA medio=0.6724739999999999; Yeom medio=0.5979586351290177; Shadow medio=0.5162023333333333; LiRA composto=0.678944; canary raw=0.7975</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>experiments/_hour_circular_encoding/ (JSON + xlsx + history/)</t>
+          <t>experiments/_final_ref_swap_s456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P122" s="3" t="n"/>
@@ -9906,17 +9906,17 @@
     <row r="123" ht="90" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>_rdp_balanced_recorddp_fast/experiment_20260917_064655.json</t>
+          <t>_hour_circular_encoding/experiment_20260831_161645.json</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D123" s="3" t="n">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3886876666666666; Yeom medio=0.5163276180775616; Shadow medio=0.5461393333333333; LiRA composto=0.35769; canary raw=0.435</t>
+          <t>LiRA medio=0.5077716666666667; Yeom medio=0.5180579176114891; Shadow medio=0.49286333333333326; LiRA composto=0.500047</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="L123" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_balanced_recorddp_fast/ (JSON + xlsx + history/)</t>
+          <t>experiments/_hour_circular_encoding/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P123" s="3" t="n"/>
@@ -9983,17 +9983,17 @@
     <row r="124" ht="90" customHeight="1">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>_rdp_e1000_s5_s42/experiment_20260917_081852.json</t>
+          <t>_prova_recorddp/experiment_20260924_144713.json</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=0.9936577181915225</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale — record-DP (diagnostico)</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -10021,27 +10021,27 @@
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>logs/rdp_e1000_s5.log</t>
+          <t>logs/prova_recorddp_s42_attacchi_saltati.log</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_e1000_s5_s42/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M124" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+          <t>experiments/_prova_recorddp/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessuna metrica MIA nel JSON</t>
         </is>
       </c>
       <c r="P124" s="3" t="n"/>
@@ -10060,7 +10060,7 @@
     <row r="125" ht="90" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>_rdp_eps163_s42/experiment_20260917_072712.json</t>
+          <t>_rdp_balanced_recorddp_fast/experiment_20260917_064655.json</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.38548333333333334; Yeom medio=0.5171245473064735; Shadow medio=0.5352726666666667; LiRA composto=0.297562; canary raw=0.54</t>
+          <t>LiRA medio=0.3886876666666666; Yeom medio=0.5163276180775616; Shadow medio=0.5461393333333333; LiRA composto=0.35769; canary raw=0.435</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_eps163_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_balanced_recorddp_fast/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
@@ -10137,7 +10137,7 @@
     <row r="126" ht="90" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>_rdp_eps474_s42/experiment_20260917_072736.json</t>
+          <t>_rdp_e1000_s5_s42/experiment_20260917_081852.json</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -10180,17 +10180,17 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4051313333333333; Yeom medio=0.5234622566772296; Shadow medio=0.551126; LiRA composto=0.337742; canary raw=0.56</t>
+          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/rdp_e1000_s5.log</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_eps474_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_e1000_s5_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
@@ -10214,7 +10214,7 @@
     <row r="127" ht="90" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>_rdp_nm005_swap_s42/experiment_20260917_071708.json</t>
+          <t>_rdp_eps163_s42/experiment_20260917_072712.json</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D127" s="3" t="n">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.40725966666666674; Yeom medio=0.5490818809416025; Shadow medio=0.59682; LiRA composto=0.406503; canary raw=0.675</t>
+          <t>LiRA medio=0.38548333333333334; Yeom medio=0.5171245473064735; Shadow medio=0.5352726666666667; LiRA composto=0.297562; canary raw=0.54</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_nm005_swap_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_eps163_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -10291,7 +10291,7 @@
     <row r="128" ht="90" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>_rdp_recorddp_nm005/experiment_20260917_065335.json</t>
+          <t>_rdp_eps474_s42/experiment_20260917_072736.json</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3775196666666667; Yeom medio=0.5008205070167496; Shadow medio=0.5375216666666667; LiRA composto=0.343919; canary raw=0.4625</t>
+          <t>LiRA medio=0.4051313333333333; Yeom medio=0.5234622566772296; Shadow medio=0.551126; LiRA composto=0.337742; canary raw=0.56</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_recorddp_nm005/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_eps474_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
     <row r="129" ht="90" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>_rdp_recorddp_nm01/experiment_20260917_065015.json</t>
+          <t>_rdp_nm005_swap_s42/experiment_20260917_071708.json</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3853766666666667; Yeom medio=0.48447874226648563; Shadow medio=0.5364559999999999; LiRA composto=0.355141; canary raw=0.4675</t>
+          <t>LiRA medio=0.40725966666666674; Yeom medio=0.5490818809416025; Shadow medio=0.59682; LiRA composto=0.406503; canary raw=0.675</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_recorddp_nm01/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_nm005_swap_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
@@ -10445,7 +10445,7 @@
     <row r="130" ht="90" customHeight="1">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>_rdp_ref_e10_s42/experiment_20260917_072648.json</t>
+          <t>_rdp_recorddp_nm005/experiment_20260917_065335.json</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.611027; Yeom medio=0.49774360570393844; Shadow medio=0.525556; LiRA composto=0.669276; canary raw=0.4925</t>
+          <t>LiRA medio=0.3775196666666667; Yeom medio=0.5008205070167496; Shadow medio=0.5375216666666667; LiRA composto=0.343919; canary raw=0.4625</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_ref_e10_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_recorddp_nm005/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
@@ -10522,7 +10522,7 @@
     <row r="131" ht="90" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>_ref_e1000_group_s42/experiment_20260917_073820.json</t>
+          <t>_rdp_recorddp_nm01/experiment_20260917_065015.json</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
+          <t>LiRA medio=0.3853766666666667; Yeom medio=0.48447874226648563; Shadow medio=0.5364559999999999; LiRA composto=0.355141; canary raw=0.4675</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>logs/ref_e1000_group.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>experiments/_ref_e1000_group_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_recorddp_nm01/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -10599,17 +10599,17 @@
     <row r="132" ht="90" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_135401.json</t>
+          <t>_rdp_ref_e10_s42/experiment_20260917_072648.json</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -10637,12 +10637,12 @@
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.611027; Yeom medio=0.49774360570393844; Shadow medio=0.525556; LiRA composto=0.669276; canary raw=0.4925</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_ref_e10_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P132" s="3" t="n"/>
@@ -10676,17 +10676,17 @@
     <row r="133" ht="90" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_151156.json</t>
+          <t>_ref_e1000_group_s42/experiment_20260917_073820.json</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D133" s="3" t="n">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -10714,22 +10714,22 @@
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/ref_e1000_group.log</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
+          <t>experiments/_ref_e1000_group_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P133" s="3" t="n"/>
@@ -10753,7 +10753,7 @@
     <row r="134" ht="90" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_181649.json</t>
+          <t>_robustness_entity_split/experiment_20260831_135401.json</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -10830,7 +10830,7 @@
     <row r="135" ht="90" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>_smoke_centralized_control/experiment_20260901_141640.json</t>
+          <t>_robustness_entity_split/experiment_20260831_151156.json</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D135" s="3" t="n">
@@ -10868,12 +10868,12 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_centralized_control/ (JSON + xlsx + history/)</t>
+          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
@@ -10907,7 +10907,7 @@
     <row r="136" ht="90" customHeight="1">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260901_141146.json</t>
+          <t>_robustness_entity_split/experiment_20260831_181649.json</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -10945,12 +10945,12 @@
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
@@ -10984,7 +10984,7 @@
     <row r="137" ht="90" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260901_191839.json</t>
+          <t>_smoke_centralized_control/experiment_20260901_141640.json</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_centralized_control/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="138" ht="90" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260902_062136.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260901_141146.json</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row r="139" ht="90" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260902_131018.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260901_191839.json</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="140" ht="90" customHeight="1">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_n16/experiment_20260901_143530.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260902_062136.json</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_n16/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -11292,7 +11292,7 @@
     <row r="141" ht="90" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_n16_v2/experiment_20260901_150314.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260902_131018.json</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_n16_v2/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
@@ -11369,7 +11369,7 @@
     <row r="142" ht="90" customHeight="1">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_normalized/experiment_20260902_140132.json</t>
+          <t>_smoke_fedmia_gradient_n16/experiment_20260901_143530.json</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_normalized/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_n16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="143" ht="90" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>_smoke_sb2_dp-fedavg/experiment_20260917_210602.json</t>
+          <t>_smoke_fedmia_gradient_n16_v2/experiment_20260901_150314.json</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D143" s="3" t="n">
@@ -11474,22 +11474,22 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>1 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.494587; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.494587</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_sb2_dp-fedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_n16_v2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
@@ -11523,7 +11523,7 @@
     <row r="144" ht="90" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>_smoke_sb2_local/experiment_20260917_210627.json</t>
+          <t>_smoke_fedmia_gradient_normalized/experiment_20260902_140132.json</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -11551,22 +11551,22 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>1 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.491745; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.491745</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_sb2_local/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_normalized/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
@@ -11600,7 +11600,7 @@
     <row r="145" ht="90" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>_smoke_stradaB_dp-fedavg/experiment_20260917_205626.json</t>
+          <t>_smoke_sb2_dp-fedavg/experiment_20260917_210602.json</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.499264; Yeom medio=0.4981025148508319; Shadow medio=0.497864; LiRA composto=0.499264</t>
+          <t>LiRA medio=0.494587; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.494587</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_stradaB_dp-fedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_sb2_dp-fedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
@@ -11677,7 +11677,7 @@
     <row r="146" ht="90" customHeight="1">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>_verify_10rounds_central/experiment_20260826_150039.json</t>
+          <t>_smoke_sb2_local/experiment_20260917_210627.json</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -11705,22 +11705,22 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>1 round valutati</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013407; Yeom medio=0.49943881126863526; Shadow medio=0.49939399999999995; LiRA composto=0.501579</t>
+          <t>LiRA medio=0.491745; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.491745</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_10rounds_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_sb2_local/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr">
@@ -11754,7 +11754,7 @@
     <row r="147" ht="90" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>_verify_10rounds_nodp/experiment_20260826_121351.json</t>
+          <t>_smoke_stradaB_dp-fedavg/experiment_20260917_205626.json</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D147" s="3" t="n">
@@ -11782,22 +11782,22 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>1 round valutati</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
+          <t>LiRA medio=0.499264; Yeom medio=0.4981025148508319; Shadow medio=0.497864; LiRA composto=0.499264</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_10rounds_nodp/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_stradaB_dp-fedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
     <row r="148" ht="90" customHeight="1">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>_verify_mu_anchor/experiment_20260821_045041.json</t>
+          <t>_verify_10rounds_central/experiment_20260826_150039.json</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -11859,22 +11859,22 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
+          <t>LiRA medio=0.5013407; Yeom medio=0.49943881126863526; Shadow medio=0.49939399999999995; LiRA composto=0.501579</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_mu_anchor/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_10rounds_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="149" ht="90" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>_verify_outlier_fix/experiment_20260821_030556.json</t>
+          <t>_verify_10rounds_nodp/experiment_20260826_121351.json</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.436568; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.30242</t>
+          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_outlier_fix/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_10rounds_nodp/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
@@ -11985,7 +11985,7 @@
     <row r="150" ht="90" customHeight="1">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>_verify_shadow_universe_central/experiment_20260825_142623.json</t>
+          <t>_verify_mu_anchor/experiment_20260821_045041.json</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.501707; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.500864</t>
+          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_shadow_universe_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_mu_anchor/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -12062,7 +12062,7 @@
     <row r="151" ht="90" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>_verify_shadow_universe_nodp/experiment_20260825_123128.json</t>
+          <t>_verify_outlier_fix/experiment_20260821_030556.json</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.502457; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.498992</t>
+          <t>LiRA medio=0.436568; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.30242</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_shadow_universe_nodp/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_outlier_fix/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="152" ht="90" customHeight="1">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_101722.json</t>
+          <t>_verify_shadow_universe_central/experiment_20260825_142623.json</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -12172,17 +12172,17 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005919; Yeom medio=0.49896493538774356; Shadow medio=0.49793459999999995; LiRA composto=0.50205</t>
+          <t>LiRA medio=0.501707; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.500864</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_shadow_universe_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
@@ -12216,7 +12216,7 @@
     <row r="153" ht="90" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_132410.json</t>
+          <t>_verify_shadow_universe_nodp/experiment_20260825_123128.json</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -12226,11 +12226,11 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -12244,22 +12244,22 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007217; Yeom medio=0.4973242024691359; Shadow medio=0.49804750000000003; LiRA composto=0.5011</t>
+          <t>LiRA medio=0.502457; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.498992</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_shadow_universe_nodp/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -12293,7 +12293,7 @@
     <row r="154" ht="90" customHeight="1">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_152449.json</t>
+          <t>central-sweep5/experiment_20260904_101722.json</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -12307,7 +12307,7 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003599999999999; Yeom medio=0.500791060952068; Shadow medio=0.5014752; LiRA composto=0.503782</t>
+          <t>LiRA medio=0.5005919; Yeom medio=0.49896493538774356; Shadow medio=0.49793459999999995; LiRA composto=0.50205</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
@@ -12370,7 +12370,7 @@
     <row r="155" ht="90" customHeight="1">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_172351.json</t>
+          <t>central-sweep5/experiment_20260904_132410.json</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -12384,7 +12384,7 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49905990000000006; Yeom medio=0.500571496779277; Shadow medio=0.500362; LiRA composto=0.495431</t>
+          <t>LiRA medio=0.5007217; Yeom medio=0.4973242024691359; Shadow medio=0.49804750000000003; LiRA composto=0.5011</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
@@ -12447,7 +12447,7 @@
     <row r="156" ht="90" customHeight="1">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_192220.json</t>
+          <t>central-sweep5/experiment_20260904_152449.json</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987811; Yeom medio=0.5031364589234597; Shadow medio=0.5001119; LiRA composto=0.498958</t>
+          <t>LiRA medio=0.5003599999999999; Yeom medio=0.500791060952068; Shadow medio=0.5014752; LiRA composto=0.503782</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="157" ht="90" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_125850.json</t>
+          <t>central-sweep5/experiment_20260904_172351.json</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -12534,11 +12534,11 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5011854000000001; Yeom medio=0.49965422177892016; Shadow medio=0.4990378000000001; LiRA composto=0.502787</t>
+          <t>LiRA medio=0.49905990000000006; Yeom medio=0.500571496779277; Shadow medio=0.500362; LiRA composto=0.495431</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -12601,7 +12601,7 @@
     <row r="158" ht="90" customHeight="1">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_191408.json</t>
+          <t>central-sweep5/experiment_20260904_192220.json</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -12611,11 +12611,11 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009991000000001; Yeom medio=0.4972590761864777; Shadow medio=0.4984662999999999; LiRA composto=0.505951</t>
+          <t>LiRA medio=0.4987811; Yeom medio=0.5031364589234597; Shadow medio=0.5001119; LiRA composto=0.498958</t>
         </is>
       </c>
       <c r="K158" s="3" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
@@ -12678,7 +12678,7 @@
     <row r="159" ht="90" customHeight="1">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_211234.json</t>
+          <t>central-sweep6/experiment_20260906_125850.json</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -12692,7 +12692,7 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4992345; Yeom medio=0.500988430412608; Shadow medio=0.5016581; LiRA composto=0.496234</t>
+          <t>LiRA medio=0.5011854000000001; Yeom medio=0.49965422177892016; Shadow medio=0.4990378000000001; LiRA composto=0.502787</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
@@ -12755,7 +12755,7 @@
     <row r="160" ht="90" customHeight="1">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_231027.json</t>
+          <t>central-sweep6/experiment_20260906_191408.json</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5017716000000001; Yeom medio=0.5013164942039221; Shadow medio=0.5005728; LiRA composto=0.50808</t>
+          <t>LiRA medio=0.5009991000000001; Yeom medio=0.4972590761864777; Shadow medio=0.4984662999999999; LiRA composto=0.505951</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
@@ -12832,7 +12832,7 @@
     <row r="161" ht="90" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260907_010817.json</t>
+          <t>central-sweep6/experiment_20260906_211234.json</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -12846,7 +12846,7 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49917149999999993; Yeom medio=0.5037495900610333; Shadow medio=0.500691; LiRA composto=0.49906</t>
+          <t>LiRA medio=0.4992345; Yeom medio=0.500988430412608; Shadow medio=0.5016581; LiRA composto=0.496234</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="162" ht="90" customHeight="1">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_030628.json</t>
+          <t>central-sweep6/experiment_20260906_231027.json</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -12919,11 +12919,11 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49977089999999996; Yeom medio=0.49805428686925496; Shadow medio=0.49676210000000004; LiRA composto=0.498855</t>
+          <t>LiRA medio=0.5017716000000001; Yeom medio=0.5013164942039221; Shadow medio=0.5005728; LiRA composto=0.50808</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -12986,7 +12986,7 @@
     <row r="163" ht="90" customHeight="1">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_050525.json</t>
+          <t>central-sweep6/experiment_20260907_010817.json</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -12996,11 +12996,11 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996276; Yeom medio=0.4971502873000452; Shadow medio=0.49816270000000007; LiRA composto=0.50023</t>
+          <t>LiRA medio=0.49917149999999993; Yeom medio=0.5037495900610333; Shadow medio=0.500691; LiRA composto=0.49906</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="L163" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <row r="164" ht="90" customHeight="1">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_070400.json</t>
+          <t>central-sweep7/experiment_20260907_030628.json</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -13077,7 +13077,7 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002849; Yeom medio=0.5002013692212844; Shadow medio=0.4996085; LiRA composto=0.503648</t>
+          <t>LiRA medio=0.49977089999999996; Yeom medio=0.49805428686925496; Shadow medio=0.49676210000000004; LiRA composto=0.498855</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
@@ -13140,7 +13140,7 @@
     <row r="165" ht="90" customHeight="1">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_090208.json</t>
+          <t>central-sweep7/experiment_20260907_050525.json</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006189; Yeom medio=0.5009834468601285; Shadow medio=0.5005473; LiRA composto=0.502658</t>
+          <t>LiRA medio=0.4996276; Yeom medio=0.4971502873000452; Shadow medio=0.49816270000000007; LiRA composto=0.50023</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="166" ht="90" customHeight="1">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_110100.json</t>
+          <t>central-sweep7/experiment_20260907_070400.json</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -13231,7 +13231,7 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5020007000000001; Yeom medio=0.5036042090648936; Shadow medio=0.5011106; LiRA composto=0.50446</t>
+          <t>LiRA medio=0.5002849; Yeom medio=0.5002013692212844; Shadow medio=0.4996085; LiRA composto=0.503648</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="167" ht="90" customHeight="1">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_071625.json</t>
+          <t>central-sweep7/experiment_20260907_090208.json</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -13304,11 +13304,11 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -13322,12 +13322,12 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
+          <t>LiRA medio=0.5006189; Yeom medio=0.5009834468601285; Shadow medio=0.5005473; LiRA composto=0.502658</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M167" s="4" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="168" ht="90" customHeight="1">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_091555.json</t>
+          <t>central-sweep7/experiment_20260907_110100.json</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -13381,11 +13381,11 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
+          <t>LiRA medio=0.5020007000000001; Yeom medio=0.5036042090648936; Shadow medio=0.5011106; LiRA composto=0.50446</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr">
@@ -13448,7 +13448,7 @@
     <row r="169" ht="90" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_111424.json</t>
+          <t>dp-sweep4/experiment_20260905_071625.json</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
+          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr">
@@ -13525,7 +13525,7 @@
     <row r="170" ht="90" customHeight="1">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_131307.json</t>
+          <t>dp-sweep4/experiment_20260905_091555.json</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
+          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
@@ -13602,7 +13602,7 @@
     <row r="171" ht="90" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_151128.json</t>
+          <t>dp-sweep4/experiment_20260905_111424.json</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
+          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr">
@@ -13679,7 +13679,7 @@
     <row r="172" ht="90" customHeight="1">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_171005.json</t>
+          <t>dp-sweep4/experiment_20260905_131307.json</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -13689,11 +13689,11 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
+          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
         </is>
       </c>
       <c r="K172" s="3" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
@@ -13756,7 +13756,7 @@
     <row r="173" ht="90" customHeight="1">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_190905.json</t>
+          <t>dp-sweep4/experiment_20260905_151128.json</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -13766,11 +13766,11 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
+          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M173" s="4" t="inlineStr">
@@ -13833,7 +13833,7 @@
     <row r="174" ht="90" customHeight="1">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_210838.json</t>
+          <t>dp-sweep5/experiment_20260905_171005.json</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -13847,7 +13847,7 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
+          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
@@ -13910,7 +13910,7 @@
     <row r="175" ht="90" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_230738.json</t>
+          <t>dp-sweep5/experiment_20260905_190905.json</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
+          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
@@ -13987,7 +13987,7 @@
     <row r="176" ht="90" customHeight="1">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260906_010556.json</t>
+          <t>dp-sweep5/experiment_20260905_210838.json</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
+          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr">
@@ -14064,7 +14064,7 @@
     <row r="177" ht="90" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_030425.json</t>
+          <t>dp-sweep5/experiment_20260905_230738.json</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -14074,11 +14074,11 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
+          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
         </is>
       </c>
       <c r="K177" s="3" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
@@ -14141,7 +14141,7 @@
     <row r="178" ht="90" customHeight="1">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_050301.json</t>
+          <t>dp-sweep5/experiment_20260906_010556.json</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -14151,11 +14151,11 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
+          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
         </is>
       </c>
       <c r="K178" s="3" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
@@ -14218,7 +14218,7 @@
     <row r="179" ht="90" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_070124.json</t>
+          <t>dp-sweep6/experiment_20260906_030425.json</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -14232,7 +14232,7 @@
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
+          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
         </is>
       </c>
       <c r="K179" s="3" t="inlineStr">
@@ -14295,7 +14295,7 @@
     <row r="180" ht="90" customHeight="1">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_090022.json</t>
+          <t>dp-sweep6/experiment_20260906_050301.json</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -14309,7 +14309,7 @@
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
+          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
         </is>
       </c>
       <c r="K180" s="3" t="inlineStr">
@@ -14372,7 +14372,7 @@
     <row r="181" ht="90" customHeight="1">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_105941.json</t>
+          <t>dp-sweep6/experiment_20260906_070124.json</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -14386,7 +14386,7 @@
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
+          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr">
@@ -14449,7 +14449,7 @@
     <row r="182" ht="90" customHeight="1">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260917_230655.json</t>
+          <t>dp-sweep6/experiment_20260906_090022.json</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -14459,11 +14459,11 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.498673; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.497625</t>
+          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
         </is>
       </c>
       <c r="K182" s="3" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
@@ -14526,7 +14526,7 @@
     <row r="183" ht="90" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_010547.json</t>
+          <t>dp-sweep6/experiment_20260906_105941.json</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -14536,11 +14536,11 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5008796; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.499315</t>
+          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr">
@@ -14603,7 +14603,7 @@
     <row r="184" ht="90" customHeight="1">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_030414.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260917_230655.json</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -14617,7 +14617,7 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49872580000000005; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498937</t>
+          <t>LiRA medio=0.498673; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.497625</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="185" ht="90" customHeight="1">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_050226.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_010547.json</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991087; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.4982</t>
+          <t>LiRA medio=0.5008796; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.499315</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
@@ -14757,7 +14757,7 @@
     <row r="186" ht="90" customHeight="1">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_070126.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_030414.json</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5012004000000001; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.503942</t>
+          <t>LiRA medio=0.49872580000000005; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498937</t>
         </is>
       </c>
       <c r="K186" s="3" t="inlineStr">
@@ -14834,7 +14834,7 @@
     <row r="187" ht="90" customHeight="1">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_090012.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_050226.json</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -14844,11 +14844,11 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991078; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.497224</t>
+          <t>LiRA medio=0.4991087; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.4982</t>
         </is>
       </c>
       <c r="K187" s="3" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
@@ -14911,7 +14911,7 @@
     <row r="188" ht="90" customHeight="1">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_110316.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_070126.json</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -14921,11 +14921,11 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49917960000000006; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.494169</t>
+          <t>LiRA medio=0.5012004000000001; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.503942</t>
         </is>
       </c>
       <c r="K188" s="3" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr">
@@ -14988,7 +14988,7 @@
     <row r="189" ht="90" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_130646.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_090012.json</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49895890000000004; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.49704</t>
+          <t>LiRA medio=0.4991078; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.497224</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
@@ -15065,7 +15065,7 @@
     <row r="190" ht="90" customHeight="1">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_152053.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_110316.json</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987621; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.49875</t>
+          <t>LiRA medio=0.49917960000000006; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.494169</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr">
@@ -15142,7 +15142,7 @@
     <row r="191" ht="90" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_172416.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_130646.json</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500696; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.503045</t>
+          <t>LiRA medio=0.49895890000000004; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.49704</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
@@ -15219,7 +15219,7 @@
     <row r="192" ht="90" customHeight="1">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_192336.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_152053.json</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -15229,11 +15229,11 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4981084; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.496392</t>
+          <t>LiRA medio=0.4987621; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.49875</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
@@ -15296,7 +15296,7 @@
     <row r="193" ht="90" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_212202.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_172416.json</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -15306,11 +15306,11 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991732000000001; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.494029</t>
+          <t>LiRA medio=0.500696; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.503045</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
@@ -15373,7 +15373,7 @@
     <row r="194" ht="90" customHeight="1">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_232046.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_192336.json</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -15387,7 +15387,7 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933639999999996; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.497262</t>
+          <t>LiRA medio=0.4981084; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.496392</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
@@ -15450,7 +15450,7 @@
     <row r="195" ht="90" customHeight="1">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_011840.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_212202.json</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991316; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.497253</t>
+          <t>LiRA medio=0.4991732000000001; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.494029</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
@@ -15527,7 +15527,7 @@
     <row r="196" ht="90" customHeight="1">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_031737.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_232046.json</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -15541,7 +15541,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002686000000001; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.500625</t>
+          <t>LiRA medio=0.49933639999999996; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.497262</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
@@ -15604,7 +15604,7 @@
     <row r="197" ht="90" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260831_184338.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_011840.json</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -15614,11 +15614,11 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -15632,12 +15632,12 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.4991316; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.497253</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
@@ -15681,7 +15681,7 @@
     <row r="198" ht="90" customHeight="1">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260831_213159.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_031737.json</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -15691,11 +15691,11 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -15709,12 +15709,12 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009480999999999; Yeom medio=0.497243057057373; Shadow medio=0.5001202; LiRA composto=0.501827</t>
+          <t>LiRA medio=0.5002686000000001; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.500625</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr">
@@ -15758,7 +15758,7 @@
     <row r="199" ht="90" customHeight="1">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_071856.json</t>
+          <t>entity-split-sweep1/experiment_20260831_184338.json</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -15772,7 +15772,7 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000713999999999; Yeom medio=0.4869039249495624; Shadow medio=0.4864776; LiRA composto=0.500347</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr">
@@ -15835,7 +15835,7 @@
     <row r="200" ht="90" customHeight="1">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_093057.json</t>
+          <t>entity-split-sweep1/experiment_20260831_213159.json</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -15849,7 +15849,7 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5044566; Yeom medio=0.5396062512497303; Shadow medio=0.5344805; LiRA composto=0.509723</t>
+          <t>LiRA medio=0.5009480999999999; Yeom medio=0.497243057057373; Shadow medio=0.5001202; LiRA composto=0.501827</t>
         </is>
       </c>
       <c r="K200" s="3" t="inlineStr">
@@ -15912,7 +15912,7 @@
     <row r="201" ht="90" customHeight="1">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_113947.json</t>
+          <t>entity-split-sweep1/experiment_20260901_071856.json</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5024798; Yeom medio=0.521343607391918; Shadow medio=0.5159754999999999; LiRA composto=0.507003</t>
+          <t>LiRA medio=0.5000713999999999; Yeom medio=0.4869039249495624; Shadow medio=0.4864776; LiRA composto=0.500347</t>
         </is>
       </c>
       <c r="K201" s="3" t="inlineStr">
@@ -15989,7 +15989,7 @@
     <row r="202" ht="90" customHeight="1">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260904_212056.json</t>
+          <t>entity-split-sweep1/experiment_20260901_093057.json</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -15999,11 +15999,11 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -16017,12 +16017,12 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
+          <t>LiRA medio=0.5044566; Yeom medio=0.5396062512497303; Shadow medio=0.5344805; LiRA composto=0.509723</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M202" s="4" t="inlineStr">
@@ -16066,7 +16066,7 @@
     <row r="203" ht="90" customHeight="1">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260904_231951.json</t>
+          <t>entity-split-sweep1/experiment_20260901_113947.json</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -16076,11 +16076,11 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
@@ -16094,12 +16094,12 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
+          <t>LiRA medio=0.5024798; Yeom medio=0.521343607391918; Shadow medio=0.5159754999999999; LiRA composto=0.507003</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M203" s="4" t="inlineStr">
@@ -16143,7 +16143,7 @@
     <row r="204" ht="90" customHeight="1">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_011919.json</t>
+          <t>local-sweep3/experiment_20260904_212056.json</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
+          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
@@ -16220,7 +16220,7 @@
     <row r="205" ht="90" customHeight="1">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_031832.json</t>
+          <t>local-sweep3/experiment_20260904_231951.json</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -16234,7 +16234,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
+          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
@@ -16297,7 +16297,7 @@
     <row r="206" ht="90" customHeight="1">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_051744.json</t>
+          <t>local-sweep3/experiment_20260905_011919.json</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
+          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="207" ht="90" customHeight="1">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_131024.json</t>
+          <t>local-sweep3/experiment_20260905_031832.json</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -16384,11 +16384,11 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
+          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M207" s="4" t="inlineStr">
@@ -16451,7 +16451,7 @@
     <row r="208" ht="90" customHeight="1">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_151044.json</t>
+          <t>local-sweep3/experiment_20260905_051744.json</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -16461,11 +16461,11 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
+          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M208" s="4" t="inlineStr">
@@ -16528,7 +16528,7 @@
     <row r="209" ht="90" customHeight="1">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_200759.json</t>
+          <t>local-sweep4/experiment_20260907_131024.json</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -16542,7 +16542,7 @@
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
+          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr">
@@ -16605,7 +16605,7 @@
     <row r="210" ht="90" customHeight="1">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_220601.json</t>
+          <t>local-sweep4/experiment_20260907_151044.json</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -16619,7 +16619,7 @@
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
+          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
@@ -16682,7 +16682,7 @@
     <row r="211" ht="90" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260908_000358.json</t>
+          <t>local-sweep4/experiment_20260907_200759.json</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -16696,7 +16696,7 @@
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
+          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr">
@@ -16759,7 +16759,7 @@
     <row r="212" ht="90" customHeight="1">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_020230.json</t>
+          <t>local-sweep4/experiment_20260907_220601.json</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -16769,11 +16769,11 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
+          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr">
@@ -16836,7 +16836,7 @@
     <row r="213" ht="90" customHeight="1">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_040043.json</t>
+          <t>local-sweep4/experiment_20260908_000358.json</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -16846,11 +16846,11 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
+          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M213" s="4" t="inlineStr">
@@ -16913,7 +16913,7 @@
     <row r="214" ht="90" customHeight="1">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_055925.json</t>
+          <t>local-sweep5/experiment_20260908_020230.json</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -16927,7 +16927,7 @@
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
+          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr">
@@ -16990,7 +16990,7 @@
     <row r="215" ht="90" customHeight="1">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_075822.json</t>
+          <t>local-sweep5/experiment_20260908_040043.json</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -17004,7 +17004,7 @@
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
+          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">
@@ -17067,7 +17067,7 @@
     <row r="216" ht="90" customHeight="1">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_100349.json</t>
+          <t>local-sweep5/experiment_20260908_055925.json</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -17081,7 +17081,7 @@
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
+          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
         </is>
       </c>
       <c r="K216" s="3" t="inlineStr">
@@ -17144,7 +17144,7 @@
     <row r="217" ht="90" customHeight="1">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_121719.json</t>
+          <t>local-sweep5/experiment_20260908_075822.json</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -17154,11 +17154,11 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -17172,12 +17172,12 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -17187,17 +17187,17 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
+          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M217" s="4" t="inlineStr">
@@ -17221,7 +17221,7 @@
     <row r="218" ht="90" customHeight="1">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_142331.json</t>
+          <t>local-sweep5/experiment_20260908_100349.json</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -17231,11 +17231,11 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -17249,12 +17249,12 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I218" s="3" t="inlineStr">
@@ -17264,17 +17264,17 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001166; Yeom medio=0.4977689383995224; Shadow medio=0.5013555000000001; LiRA composto=0.496078</t>
+          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M218" s="4" t="inlineStr">
@@ -17298,7 +17298,7 @@
     <row r="219" ht="90" customHeight="1">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_162411.json</t>
+          <t>nodp-sweep2/experiment_20260908_121719.json</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49979699999999994; Yeom medio=0.5012321998500424; Shadow medio=0.5028671; LiRA composto=0.503626</t>
+          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
@@ -17375,7 +17375,7 @@
     <row r="220" ht="90" customHeight="1">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_182356.json</t>
+          <t>nodp-sweep2/experiment_20260908_142331.json</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -17389,7 +17389,7 @@
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994059999999999; Yeom medio=0.5037555029217773; Shadow medio=0.5027257; LiRA composto=0.498701</t>
+          <t>LiRA medio=0.5001166; Yeom medio=0.4977689383995224; Shadow medio=0.5013555000000001; LiRA composto=0.496078</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
@@ -17452,7 +17452,7 @@
     <row r="221" ht="90" customHeight="1">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_202354.json</t>
+          <t>nodp-sweep2/experiment_20260908_162411.json</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007714; Yeom medio=0.5004956024284777; Shadow medio=0.5029101; LiRA composto=0.501679</t>
+          <t>LiRA medio=0.49979699999999994; Yeom medio=0.5012321998500424; Shadow medio=0.5028671; LiRA composto=0.503626</t>
         </is>
       </c>
       <c r="K221" s="3" t="inlineStr">
@@ -17529,7 +17529,7 @@
     <row r="222" ht="90" customHeight="1">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed123-eps0.5/experiment_20260914_152619.json</t>
+          <t>nodp-sweep2/experiment_20260908_182356.json</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -17539,11 +17539,11 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -17557,12 +17557,12 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I222" s="3" t="inlineStr">
@@ -17572,17 +17572,17 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010704; Yeom medio=0.49885817165752017; Shadow medio=0.49721390000000004; LiRA composto=0.505366</t>
+          <t>LiRA medio=0.4994059999999999; Yeom medio=0.5037555029217773; Shadow medio=0.5027257; LiRA composto=0.498701</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed123-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M222" s="4" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="223" ht="90" customHeight="1">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed123/experiment_20260910_172634.json</t>
+          <t>nodp-sweep2/experiment_20260908_202354.json</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -17616,13 +17616,11 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 123: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>1234</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -17636,12 +17634,12 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr">
@@ -17651,17 +17649,17 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000368; Yeom medio=0.49981732394504885; Shadow medio=0.49837070000000006; LiRA composto=0.500623</t>
+          <t>LiRA medio=0.5007714; Yeom medio=0.5004956024284777; Shadow medio=0.5029101; LiRA composto=0.501679</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M223" s="4" t="inlineStr">
@@ -17685,7 +17683,7 @@
     <row r="224" ht="90" customHeight="1">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed1234/experiment_20260911_122836.json</t>
+          <t>nvflare-central-seed123-eps0.5/experiment_20260914_152619.json</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -17695,13 +17693,11 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 1234: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>123</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -17720,7 +17716,7 @@
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I224" s="3" t="inlineStr">
@@ -17730,7 +17726,7 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5012264; Yeom medio=0.5012137493317419; Shadow medio=0.5008147000000001; LiRA composto=0.506321</t>
+          <t>LiRA medio=0.5010704; Yeom medio=0.49885817165752017; Shadow medio=0.49721390000000004; LiRA composto=0.505366</t>
         </is>
       </c>
       <c r="K224" s="3" t="inlineStr">
@@ -17740,7 +17736,7 @@
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed123-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M224" s="4" t="inlineStr">
@@ -17764,7 +17760,7 @@
     <row r="225" ht="90" customHeight="1">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed42-eps0.5/experiment_20260914_130854.json</t>
+          <t>nvflare-central-seed123/experiment_20260910_172634.json</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -17774,11 +17770,13 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="n">
-        <v>42</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 123: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -17797,7 +17795,7 @@
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr">
@@ -17807,7 +17805,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994279; Yeom medio=0.49465245749743075; Shadow medio=0.4958531; LiRA composto=0.500887</t>
+          <t>LiRA medio=0.5000368; Yeom medio=0.49981732394504885; Shadow medio=0.49837070000000006; LiRA composto=0.500623</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr">
@@ -17817,7 +17815,7 @@
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed42-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M225" s="4" t="inlineStr">
@@ -17841,7 +17839,7 @@
     <row r="226" ht="90" customHeight="1">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed456-eps0.5/experiment_20260914_175355.json</t>
+          <t>nvflare-central-seed1234/experiment_20260911_122836.json</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -17851,12 +17849,12 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 1234: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
@@ -17876,7 +17874,7 @@
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr">
@@ -17886,7 +17884,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5011443; Yeom medio=0.49762605437521107; Shadow medio=0.4992915; LiRA composto=0.504601</t>
+          <t>LiRA medio=0.5012264; Yeom medio=0.5012137493317419; Shadow medio=0.5008147000000001; LiRA composto=0.506321</t>
         </is>
       </c>
       <c r="K226" s="3" t="inlineStr">
@@ -17896,7 +17894,7 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed456-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M226" s="4" t="inlineStr">
@@ -17920,7 +17918,7 @@
     <row r="227" ht="90" customHeight="1">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed456/experiment_20260910_222515.json</t>
+          <t>nvflare-central-seed42-eps0.5/experiment_20260914_130854.json</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -17930,13 +17928,11 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>42</v>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
@@ -17955,7 +17951,7 @@
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -17965,7 +17961,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5015437; Yeom medio=0.4976337915896831; Shadow medio=0.5007618; LiRA composto=0.505552</t>
+          <t>LiRA medio=0.4994279; Yeom medio=0.49465245749743075; Shadow medio=0.4958531; LiRA composto=0.500887</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
@@ -17975,7 +17971,7 @@
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed42-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M227" s="4" t="inlineStr">
@@ -17999,7 +17995,7 @@
     <row r="228" ht="90" customHeight="1">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed789-eps0.5/experiment_20260914_205551.json</t>
+          <t>nvflare-central-seed456-eps0.5/experiment_20260914_175355.json</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -18014,7 +18010,7 @@
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
@@ -18034,7 +18030,7 @@
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I228" s="3" t="inlineStr">
@@ -18044,7 +18040,7 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005679; Yeom medio=0.49992255315113887; Shadow medio=0.4980574; LiRA composto=0.502025</t>
+          <t>LiRA medio=0.5011443; Yeom medio=0.49762605437521107; Shadow medio=0.4992915; LiRA composto=0.504601</t>
         </is>
       </c>
       <c r="K228" s="3" t="inlineStr">
@@ -18054,7 +18050,7 @@
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed789-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed456-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M228" s="4" t="inlineStr">
@@ -18078,7 +18074,7 @@
     <row r="229" ht="90" customHeight="1">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed789/experiment_20260911_095435.json</t>
+          <t>nvflare-central-seed456/experiment_20260910_222515.json</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -18093,7 +18089,7 @@
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
@@ -18123,7 +18119,7 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002807; Yeom medio=0.5002761736218346; Shadow medio=0.49890680000000004; LiRA composto=0.504216</t>
+          <t>LiRA medio=0.5015437; Yeom medio=0.4976337915896831; Shadow medio=0.5007618; LiRA composto=0.505552</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr">
@@ -18133,7 +18129,7 @@
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M229" s="4" t="inlineStr">
@@ -18157,7 +18153,7 @@
     <row r="230" ht="90" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
+          <t>nvflare-central-seed789-eps0.5/experiment_20260914_205551.json</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -18167,11 +18163,13 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="n">
-        <v>1234</v>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
@@ -18185,12 +18183,12 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr">
@@ -18200,7 +18198,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
+          <t>LiRA medio=0.5005679; Yeom medio=0.49992255315113887; Shadow medio=0.4980574; LiRA composto=0.502025</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
@@ -18210,7 +18208,7 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed789-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr">
@@ -18234,7 +18232,7 @@
     <row r="231" ht="90" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
+          <t>nvflare-central-seed789/experiment_20260911_095435.json</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -18244,11 +18242,13 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="n">
-        <v>1234</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -18262,12 +18262,12 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I231" s="3" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
+          <t>LiRA medio=0.5002807; Yeom medio=0.5002761736218346; Shadow medio=0.49890680000000004; LiRA composto=0.504216</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M231" s="4" t="inlineStr">
@@ -18311,7 +18311,7 @@
     <row r="232" ht="90" customHeight="1">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
+          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -18321,11 +18321,11 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
+          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="233" ht="90" customHeight="1">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
+          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D233" s="3" t="n">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
+          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M233" s="4" t="inlineStr">
@@ -18465,7 +18465,7 @@
     <row r="234" ht="90" customHeight="1">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
+          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
+          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr">
@@ -18542,7 +18542,7 @@
     <row r="235" ht="90" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
+          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -18556,7 +18556,7 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>456</v>
+        <v>1234</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
+          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M235" s="4" t="inlineStr">
@@ -18619,7 +18619,7 @@
     <row r="236" ht="90" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
+          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
+          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr">
@@ -18696,7 +18696,7 @@
     <row r="237" ht="90" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
+          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -18706,11 +18706,11 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D237" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H237" s="3" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
+          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M237" s="4" t="inlineStr">
@@ -18773,7 +18773,7 @@
     <row r="238" ht="90" customHeight="1">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
+          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -18783,11 +18783,11 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
+          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M238" s="4" t="inlineStr">
@@ -18850,7 +18850,7 @@
     <row r="239" ht="90" customHeight="1">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_183148.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -18860,7 +18860,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D239" s="3" t="n">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr">
@@ -18893,7 +18893,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
+          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M239" s="4" t="inlineStr">
@@ -18927,7 +18927,7 @@
     <row r="240" ht="90" customHeight="1">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_203243.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -18937,11 +18937,11 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
+          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M240" s="4" t="inlineStr">
@@ -19004,7 +19004,7 @@
     <row r="241" ht="90" customHeight="1">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_223219.json</t>
+          <t>rq1-eps16/experiment_20260923_183148.json</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -19018,7 +19018,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
+          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
         </is>
       </c>
       <c r="K241" s="3" t="inlineStr">
@@ -19081,7 +19081,7 @@
     <row r="242" ht="90" customHeight="1">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260924_003215.json</t>
+          <t>rq1-eps16/experiment_20260923_203243.json</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -19095,7 +19095,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
+          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
         </is>
       </c>
       <c r="K242" s="3" t="inlineStr">
@@ -19158,7 +19158,7 @@
     <row r="243" ht="90" customHeight="1">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260924_023219.json</t>
+          <t>rq1-eps16/experiment_20260923_223219.json</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -19172,7 +19172,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
+          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
         </is>
       </c>
       <c r="K243" s="3" t="inlineStr">
@@ -19235,7 +19235,7 @@
     <row r="244" ht="90" customHeight="1">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_134148.json</t>
+          <t>rq1-eps16/experiment_20260924_003215.json</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -19245,11 +19245,11 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
+          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M244" s="4" t="inlineStr">
@@ -19312,7 +19312,7 @@
     <row r="245" ht="90" customHeight="1">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_154640.json</t>
+          <t>rq1-eps16/experiment_20260924_023219.json</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -19322,11 +19322,11 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D245" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
+          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M245" s="4" t="inlineStr">
@@ -19389,7 +19389,7 @@
     <row r="246" ht="90" customHeight="1">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_175039.json</t>
+          <t>rq1-eps2/experiment_20260922_134148.json</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
+          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
         </is>
       </c>
       <c r="K246" s="3" t="inlineStr">
@@ -19466,7 +19466,7 @@
     <row r="247" ht="90" customHeight="1">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_180414.json</t>
+          <t>rq1-eps2/experiment_20260922_154640.json</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -19480,7 +19480,7 @@
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
+          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr">
@@ -19522,9 +19522,9 @@
           <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
-      <c r="M247" s="5" t="inlineStr">
-        <is>
-          <t>incompleta</t>
+      <c r="M247" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="O247" s="3" t="inlineStr">
         <is>
-          <t>nessuna metrica MIA nel JSON</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P247" s="3" t="n"/>
@@ -19543,7 +19543,7 @@
     <row r="248" ht="90" customHeight="1">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_200439.json</t>
+          <t>rq1-eps2/experiment_20260922_175039.json</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -19557,7 +19557,7 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
+          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
@@ -19620,7 +19620,7 @@
     <row r="249" ht="90" customHeight="1">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260924_102430.json</t>
+          <t>rq1-eps2/experiment_20260922_180414.json</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr">
@@ -19676,9 +19676,9 @@
           <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
-      <c r="M249" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+      <c r="M249" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="O249" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessuna metrica MIA nel JSON</t>
         </is>
       </c>
       <c r="P249" s="3" t="n"/>
@@ -19697,7 +19697,7 @@
     <row r="250" ht="90" customHeight="1">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260922_220310.json</t>
+          <t>rq1-eps2/experiment_20260922_200439.json</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -19707,11 +19707,11 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I250" s="3" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
+          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
         </is>
       </c>
       <c r="K250" s="3" t="inlineStr">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M250" s="4" t="inlineStr">
@@ -19774,7 +19774,7 @@
     <row r="251" ht="90" customHeight="1">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_000138.json</t>
+          <t>rq1-eps2/experiment_20260924_102430.json</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -19784,11 +19784,11 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
+          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
         </is>
       </c>
       <c r="K251" s="3" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M251" s="4" t="inlineStr">
@@ -19851,7 +19851,7 @@
     <row r="252" ht="90" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_020058.json</t>
+          <t>rq1-eps4/experiment_20260922_220310.json</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -19865,7 +19865,7 @@
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
+          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
         </is>
       </c>
       <c r="K252" s="3" t="inlineStr">
@@ -19928,7 +19928,7 @@
     <row r="253" ht="90" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_040025.json</t>
+          <t>rq1-eps4/experiment_20260923_000138.json</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -19942,7 +19942,7 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
+          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
         </is>
       </c>
       <c r="K253" s="3" t="inlineStr">
@@ -20005,7 +20005,7 @@
     <row r="254" ht="90" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_055955.json</t>
+          <t>rq1-eps4/experiment_20260923_020058.json</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -20019,7 +20019,7 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
+          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
@@ -20082,7 +20082,7 @@
     <row r="255" ht="90" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_080158.json</t>
+          <t>rq1-eps4/experiment_20260923_040025.json</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -20092,11 +20092,11 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D255" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
+          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M255" s="4" t="inlineStr">
@@ -20159,7 +20159,7 @@
     <row r="256" ht="90" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_100736.json</t>
+          <t>rq1-eps4/experiment_20260923_055955.json</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -20169,11 +20169,11 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I256" s="3" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
+          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M256" s="4" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="257" ht="90" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_121447.json</t>
+          <t>rq1-eps8/experiment_20260923_080158.json</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="D257" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
+          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
         </is>
       </c>
       <c r="K257" s="3" t="inlineStr">
@@ -20313,7 +20313,7 @@
     <row r="258" ht="90" customHeight="1">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_142154.json</t>
+          <t>rq1-eps8/experiment_20260923_100736.json</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
         </is>
       </c>
       <c r="K258" s="3" t="inlineStr">
@@ -20390,7 +20390,7 @@
     <row r="259" ht="90" customHeight="1">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_162834.json</t>
+          <t>rq1-eps8/experiment_20260923_121447.json</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
         </is>
       </c>
       <c r="K259" s="3" t="inlineStr">
@@ -20463,6 +20463,160 @@
       </c>
       <c r="P259" s="3" t="n"/>
       <c r="Q259" s="3" t="n"/>
+    </row>
+    <row r="260" ht="90" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_142154.json</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J260" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M260" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O260" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P260" s="3" t="n"/>
+      <c r="Q260" s="3" t="n"/>
+    </row>
+    <row r="261" ht="90" customHeight="1">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_162834.json</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J261" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M261" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O261" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P261" s="3" t="n"/>
+      <c r="Q261" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q261"/>
+  <dimension ref="A1:Q263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9983,7 +9983,7 @@
     <row r="124" ht="90" customHeight="1">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>_prova_recorddp/experiment_20260924_144713.json</t>
+          <t>_op_C0.25_eps16/experiment_20260924_192923.json</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=0.9936577181915225</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP (diagnostico)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -10026,22 +10026,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
+          <t>LiRA medio=0.5003383; Yeom medio=0.496648749543413; Shadow medio=0.49485660000000004; LiRA composto=0.502446</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>logs/prova_recorddp_s42_attacchi_saltati.log</t>
+          <t>logs/op_C0.25_eps16.log</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>experiments/_prova_recorddp/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M124" s="5" t="inlineStr">
-        <is>
-          <t>incompleta</t>
+          <t>experiments/_op_C0.25_eps16/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>nessuna metrica MIA nel JSON</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P124" s="3" t="n"/>
@@ -10060,17 +10060,17 @@
     <row r="125" ht="90" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>_rdp_balanced_recorddp_fast/experiment_20260917_064655.json</t>
+          <t>_op_eps64/experiment_20260924_212917.json</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
@@ -10083,37 +10083,37 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3886876666666666; Yeom medio=0.5163276180775616; Shadow medio=0.5461393333333333; LiRA composto=0.35769; canary raw=0.435</t>
+          <t>LiRA medio=0.49855; Yeom medio=0.4992467157518548; Shadow medio=0.4996785; LiRA composto=0.499981</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/op_eps64.log</t>
         </is>
       </c>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_balanced_recorddp_fast/ (JSON + xlsx + history/)</t>
+          <t>experiments/_op_eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P125" s="3" t="n"/>
@@ -10137,17 +10137,17 @@
     <row r="126" ht="90" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>_rdp_e1000_s5_s42/experiment_20260917_081852.json</t>
+          <t>_prova_recorddp/experiment_20260924_144713.json</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=0.9936577181915225</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale — record-DP (diagnostico)</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -10175,27 +10175,27 @@
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>logs/rdp_e1000_s5.log</t>
+          <t>logs/prova_recorddp_s42_attacchi_saltati.log</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_e1000_s5_s42/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M126" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+          <t>experiments/_prova_recorddp/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M126" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessuna metrica MIA nel JSON</t>
         </is>
       </c>
       <c r="P126" s="3" t="n"/>
@@ -10214,7 +10214,7 @@
     <row r="127" ht="90" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>_rdp_eps163_s42/experiment_20260917_072712.json</t>
+          <t>_rdp_balanced_recorddp_fast/experiment_20260917_064655.json</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D127" s="3" t="n">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.38548333333333334; Yeom medio=0.5171245473064735; Shadow medio=0.5352726666666667; LiRA composto=0.297562; canary raw=0.54</t>
+          <t>LiRA medio=0.3886876666666666; Yeom medio=0.5163276180775616; Shadow medio=0.5461393333333333; LiRA composto=0.35769; canary raw=0.435</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_eps163_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_balanced_recorddp_fast/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -10291,7 +10291,7 @@
     <row r="128" ht="90" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>_rdp_eps474_s42/experiment_20260917_072736.json</t>
+          <t>_rdp_e1000_s5_s42/experiment_20260917_081852.json</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -10334,17 +10334,17 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4051313333333333; Yeom medio=0.5234622566772296; Shadow medio=0.551126; LiRA composto=0.337742; canary raw=0.56</t>
+          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/rdp_e1000_s5.log</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_eps474_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_e1000_s5_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -10368,7 +10368,7 @@
     <row r="129" ht="90" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>_rdp_nm005_swap_s42/experiment_20260917_071708.json</t>
+          <t>_rdp_eps163_s42/experiment_20260917_072712.json</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.40725966666666674; Yeom medio=0.5490818809416025; Shadow medio=0.59682; LiRA composto=0.406503; canary raw=0.675</t>
+          <t>LiRA medio=0.38548333333333334; Yeom medio=0.5171245473064735; Shadow medio=0.5352726666666667; LiRA composto=0.297562; canary raw=0.54</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_nm005_swap_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_eps163_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
@@ -10445,7 +10445,7 @@
     <row r="130" ht="90" customHeight="1">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>_rdp_recorddp_nm005/experiment_20260917_065335.json</t>
+          <t>_rdp_eps474_s42/experiment_20260917_072736.json</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3775196666666667; Yeom medio=0.5008205070167496; Shadow medio=0.5375216666666667; LiRA composto=0.343919; canary raw=0.4625</t>
+          <t>LiRA medio=0.4051313333333333; Yeom medio=0.5234622566772296; Shadow medio=0.551126; LiRA composto=0.337742; canary raw=0.56</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_recorddp_nm005/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_eps474_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
@@ -10522,7 +10522,7 @@
     <row r="131" ht="90" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>_rdp_recorddp_nm01/experiment_20260917_065015.json</t>
+          <t>_rdp_nm005_swap_s42/experiment_20260917_071708.json</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3853766666666667; Yeom medio=0.48447874226648563; Shadow medio=0.5364559999999999; LiRA composto=0.355141; canary raw=0.4675</t>
+          <t>LiRA medio=0.40725966666666674; Yeom medio=0.5490818809416025; Shadow medio=0.59682; LiRA composto=0.406503; canary raw=0.675</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_recorddp_nm01/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_nm005_swap_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -10599,7 +10599,7 @@
     <row r="132" ht="90" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>_rdp_ref_e10_s42/experiment_20260917_072648.json</t>
+          <t>_rdp_recorddp_nm005/experiment_20260917_065335.json</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.611027; Yeom medio=0.49774360570393844; Shadow medio=0.525556; LiRA composto=0.669276; canary raw=0.4925</t>
+          <t>LiRA medio=0.3775196666666667; Yeom medio=0.5008205070167496; Shadow medio=0.5375216666666667; LiRA composto=0.343919; canary raw=0.4625</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_ref_e10_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_recorddp_nm005/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
@@ -10676,7 +10676,7 @@
     <row r="133" ht="90" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>_ref_e1000_group_s42/experiment_20260917_073820.json</t>
+          <t>_rdp_recorddp_nm01/experiment_20260917_065015.json</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D133" s="3" t="n">
@@ -10719,17 +10719,17 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
+          <t>LiRA medio=0.3853766666666667; Yeom medio=0.48447874226648563; Shadow medio=0.5364559999999999; LiRA composto=0.355141; canary raw=0.4675</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>logs/ref_e1000_group.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>experiments/_ref_e1000_group_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_recorddp_nm01/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
@@ -10753,17 +10753,17 @@
     <row r="134" ht="90" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_135401.json</t>
+          <t>_rdp_ref_e10_s42/experiment_20260917_072648.json</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.611027; Yeom medio=0.49774360570393844; Shadow medio=0.525556; LiRA composto=0.669276; canary raw=0.4925</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_ref_e10_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P134" s="3" t="n"/>
@@ -10830,17 +10830,17 @@
     <row r="135" ht="90" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_151156.json</t>
+          <t>_ref_e1000_group_s42/experiment_20260917_073820.json</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D135" s="3" t="n">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -10868,22 +10868,22 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/ref_e1000_group.log</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
+          <t>experiments/_ref_e1000_group_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P135" s="3" t="n"/>
@@ -10907,7 +10907,7 @@
     <row r="136" ht="90" customHeight="1">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_181649.json</t>
+          <t>_robustness_entity_split/experiment_20260831_135401.json</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -10984,7 +10984,7 @@
     <row r="137" ht="90" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>_smoke_centralized_control/experiment_20260901_141640.json</t>
+          <t>_robustness_entity_split/experiment_20260831_151156.json</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D137" s="3" t="n">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_centralized_control/ (JSON + xlsx + history/)</t>
+          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="138" ht="90" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260901_141146.json</t>
+          <t>_robustness_entity_split/experiment_20260831_181649.json</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row r="139" ht="90" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260901_191839.json</t>
+          <t>_smoke_centralized_control/experiment_20260901_141640.json</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_centralized_control/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="140" ht="90" customHeight="1">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260902_062136.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260901_141146.json</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
     <row r="141" ht="90" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260902_131018.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260901_191839.json</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
     <row r="142" ht="90" customHeight="1">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_n16/experiment_20260901_143530.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260902_062136.json</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_n16/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="143" ht="90" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_n16_v2/experiment_20260901_150314.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260902_131018.json</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_n16_v2/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
@@ -11523,7 +11523,7 @@
     <row r="144" ht="90" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_normalized/experiment_20260902_140132.json</t>
+          <t>_smoke_fedmia_gradient_n16/experiment_20260901_143530.json</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_normalized/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_n16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
@@ -11600,7 +11600,7 @@
     <row r="145" ht="90" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>_smoke_sb2_dp-fedavg/experiment_20260917_210602.json</t>
+          <t>_smoke_fedmia_gradient_n16_v2/experiment_20260901_150314.json</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
@@ -11628,22 +11628,22 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>1 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.494587; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.494587</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_sb2_dp-fedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_n16_v2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
@@ -11677,7 +11677,7 @@
     <row r="146" ht="90" customHeight="1">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>_smoke_sb2_local/experiment_20260917_210627.json</t>
+          <t>_smoke_fedmia_gradient_normalized/experiment_20260902_140132.json</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -11705,22 +11705,22 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>1 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.491745; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.491745</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_sb2_local/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_normalized/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr">
@@ -11754,7 +11754,7 @@
     <row r="147" ht="90" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>_smoke_stradaB_dp-fedavg/experiment_20260917_205626.json</t>
+          <t>_smoke_sb2_dp-fedavg/experiment_20260917_210602.json</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D147" s="3" t="n">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.499264; Yeom medio=0.4981025148508319; Shadow medio=0.497864; LiRA composto=0.499264</t>
+          <t>LiRA medio=0.494587; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.494587</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_stradaB_dp-fedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_sb2_dp-fedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
     <row r="148" ht="90" customHeight="1">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>_verify_10rounds_central/experiment_20260826_150039.json</t>
+          <t>_smoke_sb2_local/experiment_20260917_210627.json</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -11859,22 +11859,22 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>1 round valutati</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013407; Yeom medio=0.49943881126863526; Shadow medio=0.49939399999999995; LiRA composto=0.501579</t>
+          <t>LiRA medio=0.491745; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.491745</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_10rounds_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_sb2_local/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="149" ht="90" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>_verify_10rounds_nodp/experiment_20260826_121351.json</t>
+          <t>_smoke_stradaB_dp-fedavg/experiment_20260917_205626.json</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
@@ -11936,22 +11936,22 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>1 round valutati</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
+          <t>LiRA medio=0.499264; Yeom medio=0.4981025148508319; Shadow medio=0.497864; LiRA composto=0.499264</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_10rounds_nodp/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_stradaB_dp-fedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
@@ -11985,7 +11985,7 @@
     <row r="150" ht="90" customHeight="1">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>_verify_mu_anchor/experiment_20260821_045041.json</t>
+          <t>_verify_10rounds_central/experiment_20260826_150039.json</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -12013,22 +12013,22 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
+          <t>LiRA medio=0.5013407; Yeom medio=0.49943881126863526; Shadow medio=0.49939399999999995; LiRA composto=0.501579</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_mu_anchor/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_10rounds_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -12062,7 +12062,7 @@
     <row r="151" ht="90" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>_verify_outlier_fix/experiment_20260821_030556.json</t>
+          <t>_verify_10rounds_nodp/experiment_20260826_121351.json</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D151" s="3" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.436568; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.30242</t>
+          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_outlier_fix/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_10rounds_nodp/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="152" ht="90" customHeight="1">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>_verify_shadow_universe_central/experiment_20260825_142623.json</t>
+          <t>_verify_mu_anchor/experiment_20260821_045041.json</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.501707; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.500864</t>
+          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_shadow_universe_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_mu_anchor/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
@@ -12216,7 +12216,7 @@
     <row r="153" ht="90" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>_verify_shadow_universe_nodp/experiment_20260825_123128.json</t>
+          <t>_verify_outlier_fix/experiment_20260821_030556.json</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.502457; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.498992</t>
+          <t>LiRA medio=0.436568; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.30242</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_shadow_universe_nodp/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_outlier_fix/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -12293,7 +12293,7 @@
     <row r="154" ht="90" customHeight="1">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_101722.json</t>
+          <t>_verify_shadow_universe_central/experiment_20260825_142623.json</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -12326,17 +12326,17 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005919; Yeom medio=0.49896493538774356; Shadow medio=0.49793459999999995; LiRA composto=0.50205</t>
+          <t>LiRA medio=0.501707; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.500864</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_shadow_universe_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
@@ -12370,7 +12370,7 @@
     <row r="155" ht="90" customHeight="1">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_132410.json</t>
+          <t>_verify_shadow_universe_nodp/experiment_20260825_123128.json</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -12380,11 +12380,11 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -12398,22 +12398,22 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007217; Yeom medio=0.4973242024691359; Shadow medio=0.49804750000000003; LiRA composto=0.5011</t>
+          <t>LiRA medio=0.502457; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.498992</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_shadow_universe_nodp/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
@@ -12447,7 +12447,7 @@
     <row r="156" ht="90" customHeight="1">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_152449.json</t>
+          <t>central-sweep5/experiment_20260904_101722.json</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -12461,7 +12461,7 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003599999999999; Yeom medio=0.500791060952068; Shadow medio=0.5014752; LiRA composto=0.503782</t>
+          <t>LiRA medio=0.5005919; Yeom medio=0.49896493538774356; Shadow medio=0.49793459999999995; LiRA composto=0.50205</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="157" ht="90" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_172351.json</t>
+          <t>central-sweep5/experiment_20260904_132410.json</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -12538,7 +12538,7 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49905990000000006; Yeom medio=0.500571496779277; Shadow medio=0.500362; LiRA composto=0.495431</t>
+          <t>LiRA medio=0.5007217; Yeom medio=0.4973242024691359; Shadow medio=0.49804750000000003; LiRA composto=0.5011</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -12601,7 +12601,7 @@
     <row r="158" ht="90" customHeight="1">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_192220.json</t>
+          <t>central-sweep5/experiment_20260904_152449.json</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987811; Yeom medio=0.5031364589234597; Shadow medio=0.5001119; LiRA composto=0.498958</t>
+          <t>LiRA medio=0.5003599999999999; Yeom medio=0.500791060952068; Shadow medio=0.5014752; LiRA composto=0.503782</t>
         </is>
       </c>
       <c r="K158" s="3" t="inlineStr">
@@ -12678,7 +12678,7 @@
     <row r="159" ht="90" customHeight="1">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_125850.json</t>
+          <t>central-sweep5/experiment_20260904_172351.json</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -12688,11 +12688,11 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5011854000000001; Yeom medio=0.49965422177892016; Shadow medio=0.4990378000000001; LiRA composto=0.502787</t>
+          <t>LiRA medio=0.49905990000000006; Yeom medio=0.500571496779277; Shadow medio=0.500362; LiRA composto=0.495431</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
@@ -12755,7 +12755,7 @@
     <row r="160" ht="90" customHeight="1">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_191408.json</t>
+          <t>central-sweep5/experiment_20260904_192220.json</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -12765,11 +12765,11 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009991000000001; Yeom medio=0.4972590761864777; Shadow medio=0.4984662999999999; LiRA composto=0.505951</t>
+          <t>LiRA medio=0.4987811; Yeom medio=0.5031364589234597; Shadow medio=0.5001119; LiRA composto=0.498958</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
@@ -12832,7 +12832,7 @@
     <row r="161" ht="90" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_211234.json</t>
+          <t>central-sweep6/experiment_20260906_125850.json</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -12846,7 +12846,7 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4992345; Yeom medio=0.500988430412608; Shadow medio=0.5016581; LiRA composto=0.496234</t>
+          <t>LiRA medio=0.5011854000000001; Yeom medio=0.49965422177892016; Shadow medio=0.4990378000000001; LiRA composto=0.502787</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="162" ht="90" customHeight="1">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_231027.json</t>
+          <t>central-sweep6/experiment_20260906_191408.json</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5017716000000001; Yeom medio=0.5013164942039221; Shadow medio=0.5005728; LiRA composto=0.50808</t>
+          <t>LiRA medio=0.5009991000000001; Yeom medio=0.4972590761864777; Shadow medio=0.4984662999999999; LiRA composto=0.505951</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
@@ -12986,7 +12986,7 @@
     <row r="163" ht="90" customHeight="1">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260907_010817.json</t>
+          <t>central-sweep6/experiment_20260906_211234.json</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -13000,7 +13000,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49917149999999993; Yeom medio=0.5037495900610333; Shadow medio=0.500691; LiRA composto=0.49906</t>
+          <t>LiRA medio=0.4992345; Yeom medio=0.500988430412608; Shadow medio=0.5016581; LiRA composto=0.496234</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <row r="164" ht="90" customHeight="1">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_030628.json</t>
+          <t>central-sweep6/experiment_20260906_231027.json</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -13073,11 +13073,11 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49977089999999996; Yeom medio=0.49805428686925496; Shadow medio=0.49676210000000004; LiRA composto=0.498855</t>
+          <t>LiRA medio=0.5017716000000001; Yeom medio=0.5013164942039221; Shadow medio=0.5005728; LiRA composto=0.50808</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
@@ -13140,7 +13140,7 @@
     <row r="165" ht="90" customHeight="1">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_050525.json</t>
+          <t>central-sweep6/experiment_20260907_010817.json</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -13150,11 +13150,11 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996276; Yeom medio=0.4971502873000452; Shadow medio=0.49816270000000007; LiRA composto=0.50023</t>
+          <t>LiRA medio=0.49917149999999993; Yeom medio=0.5037495900610333; Shadow medio=0.500691; LiRA composto=0.49906</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="L165" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="166" ht="90" customHeight="1">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_070400.json</t>
+          <t>central-sweep7/experiment_20260907_030628.json</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -13231,7 +13231,7 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002849; Yeom medio=0.5002013692212844; Shadow medio=0.4996085; LiRA composto=0.503648</t>
+          <t>LiRA medio=0.49977089999999996; Yeom medio=0.49805428686925496; Shadow medio=0.49676210000000004; LiRA composto=0.498855</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="167" ht="90" customHeight="1">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_090208.json</t>
+          <t>central-sweep7/experiment_20260907_050525.json</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006189; Yeom medio=0.5009834468601285; Shadow medio=0.5005473; LiRA composto=0.502658</t>
+          <t>LiRA medio=0.4996276; Yeom medio=0.4971502873000452; Shadow medio=0.49816270000000007; LiRA composto=0.50023</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="168" ht="90" customHeight="1">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_110100.json</t>
+          <t>central-sweep7/experiment_20260907_070400.json</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5020007000000001; Yeom medio=0.5036042090648936; Shadow medio=0.5011106; LiRA composto=0.50446</t>
+          <t>LiRA medio=0.5002849; Yeom medio=0.5002013692212844; Shadow medio=0.4996085; LiRA composto=0.503648</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
@@ -13448,7 +13448,7 @@
     <row r="169" ht="90" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_071625.json</t>
+          <t>central-sweep7/experiment_20260907_090208.json</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -13458,11 +13458,11 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
+          <t>LiRA medio=0.5006189; Yeom medio=0.5009834468601285; Shadow medio=0.5005473; LiRA composto=0.502658</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M169" s="4" t="inlineStr">
@@ -13525,7 +13525,7 @@
     <row r="170" ht="90" customHeight="1">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_091555.json</t>
+          <t>central-sweep7/experiment_20260907_110100.json</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -13535,11 +13535,11 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -13553,12 +13553,12 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
+          <t>LiRA medio=0.5020007000000001; Yeom medio=0.5036042090648936; Shadow medio=0.5011106; LiRA composto=0.50446</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
@@ -13602,7 +13602,7 @@
     <row r="171" ht="90" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_111424.json</t>
+          <t>dp-sweep4/experiment_20260905_071625.json</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
+          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr">
@@ -13679,7 +13679,7 @@
     <row r="172" ht="90" customHeight="1">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_131307.json</t>
+          <t>dp-sweep4/experiment_20260905_091555.json</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -13693,7 +13693,7 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
+          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
         </is>
       </c>
       <c r="K172" s="3" t="inlineStr">
@@ -13756,7 +13756,7 @@
     <row r="173" ht="90" customHeight="1">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_151128.json</t>
+          <t>dp-sweep4/experiment_20260905_111424.json</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -13770,7 +13770,7 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
+          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
@@ -13833,7 +13833,7 @@
     <row r="174" ht="90" customHeight="1">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_171005.json</t>
+          <t>dp-sweep4/experiment_20260905_131307.json</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -13843,11 +13843,11 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
+          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr">
@@ -13910,7 +13910,7 @@
     <row r="175" ht="90" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_190905.json</t>
+          <t>dp-sweep4/experiment_20260905_151128.json</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -13920,11 +13920,11 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
+          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M175" s="4" t="inlineStr">
@@ -13987,7 +13987,7 @@
     <row r="176" ht="90" customHeight="1">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_210838.json</t>
+          <t>dp-sweep5/experiment_20260905_171005.json</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
+          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr">
@@ -14064,7 +14064,7 @@
     <row r="177" ht="90" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_230738.json</t>
+          <t>dp-sweep5/experiment_20260905_190905.json</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
+          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
         </is>
       </c>
       <c r="K177" s="3" t="inlineStr">
@@ -14141,7 +14141,7 @@
     <row r="178" ht="90" customHeight="1">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260906_010556.json</t>
+          <t>dp-sweep5/experiment_20260905_210838.json</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
+          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
         </is>
       </c>
       <c r="K178" s="3" t="inlineStr">
@@ -14218,7 +14218,7 @@
     <row r="179" ht="90" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_030425.json</t>
+          <t>dp-sweep5/experiment_20260905_230738.json</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -14228,11 +14228,11 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
+          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
         </is>
       </c>
       <c r="K179" s="3" t="inlineStr">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
@@ -14295,7 +14295,7 @@
     <row r="180" ht="90" customHeight="1">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_050301.json</t>
+          <t>dp-sweep5/experiment_20260906_010556.json</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -14305,11 +14305,11 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
+          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
         </is>
       </c>
       <c r="K180" s="3" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
@@ -14372,7 +14372,7 @@
     <row r="181" ht="90" customHeight="1">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_070124.json</t>
+          <t>dp-sweep6/experiment_20260906_030425.json</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -14386,7 +14386,7 @@
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
+          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr">
@@ -14449,7 +14449,7 @@
     <row r="182" ht="90" customHeight="1">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_090022.json</t>
+          <t>dp-sweep6/experiment_20260906_050301.json</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
+          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
         </is>
       </c>
       <c r="K182" s="3" t="inlineStr">
@@ -14526,7 +14526,7 @@
     <row r="183" ht="90" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_105941.json</t>
+          <t>dp-sweep6/experiment_20260906_070124.json</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -14540,7 +14540,7 @@
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
+          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr">
@@ -14603,7 +14603,7 @@
     <row r="184" ht="90" customHeight="1">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260917_230655.json</t>
+          <t>dp-sweep6/experiment_20260906_090022.json</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -14613,11 +14613,11 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.498673; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.497625</t>
+          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="185" ht="90" customHeight="1">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_010547.json</t>
+          <t>dp-sweep6/experiment_20260906_105941.json</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -14690,11 +14690,11 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5008796; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.499315</t>
+          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr">
@@ -14757,7 +14757,7 @@
     <row r="186" ht="90" customHeight="1">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_030414.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260917_230655.json</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49872580000000005; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498937</t>
+          <t>LiRA medio=0.498673; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.497625</t>
         </is>
       </c>
       <c r="K186" s="3" t="inlineStr">
@@ -14834,7 +14834,7 @@
     <row r="187" ht="90" customHeight="1">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_050226.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_010547.json</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -14848,7 +14848,7 @@
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991087; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.4982</t>
+          <t>LiRA medio=0.5008796; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.499315</t>
         </is>
       </c>
       <c r="K187" s="3" t="inlineStr">
@@ -14911,7 +14911,7 @@
     <row r="188" ht="90" customHeight="1">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_070126.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_030414.json</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -14925,7 +14925,7 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5012004000000001; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.503942</t>
+          <t>LiRA medio=0.49872580000000005; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498937</t>
         </is>
       </c>
       <c r="K188" s="3" t="inlineStr">
@@ -14988,7 +14988,7 @@
     <row r="189" ht="90" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_090012.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_050226.json</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -14998,11 +14998,11 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991078; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.497224</t>
+          <t>LiRA medio=0.4991087; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.4982</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
@@ -15065,7 +15065,7 @@
     <row r="190" ht="90" customHeight="1">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_110316.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_070126.json</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -15075,11 +15075,11 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49917960000000006; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.494169</t>
+          <t>LiRA medio=0.5012004000000001; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.503942</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
@@ -15142,7 +15142,7 @@
     <row r="191" ht="90" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_130646.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_090012.json</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49895890000000004; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.49704</t>
+          <t>LiRA medio=0.4991078; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.497224</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
@@ -15219,7 +15219,7 @@
     <row r="192" ht="90" customHeight="1">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_152053.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_110316.json</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987621; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.49875</t>
+          <t>LiRA medio=0.49917960000000006; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.494169</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
@@ -15296,7 +15296,7 @@
     <row r="193" ht="90" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_172416.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_130646.json</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -15310,7 +15310,7 @@
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500696; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.503045</t>
+          <t>LiRA medio=0.49895890000000004; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.49704</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
@@ -15373,7 +15373,7 @@
     <row r="194" ht="90" customHeight="1">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_192336.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_152053.json</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -15383,11 +15383,11 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4981084; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.496392</t>
+          <t>LiRA medio=0.4987621; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.49875</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
@@ -15450,7 +15450,7 @@
     <row r="195" ht="90" customHeight="1">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_212202.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_172416.json</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -15460,11 +15460,11 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991732000000001; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.494029</t>
+          <t>LiRA medio=0.500696; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.503045</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
@@ -15527,7 +15527,7 @@
     <row r="196" ht="90" customHeight="1">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_232046.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_192336.json</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -15541,7 +15541,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933639999999996; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.497262</t>
+          <t>LiRA medio=0.4981084; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.496392</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
@@ -15604,7 +15604,7 @@
     <row r="197" ht="90" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_011840.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_212202.json</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -15618,7 +15618,7 @@
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991316; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.497253</t>
+          <t>LiRA medio=0.4991732000000001; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.494029</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
@@ -15681,7 +15681,7 @@
     <row r="198" ht="90" customHeight="1">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_031737.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_232046.json</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -15695,7 +15695,7 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002686000000001; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.500625</t>
+          <t>LiRA medio=0.49933639999999996; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.497262</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
@@ -15758,7 +15758,7 @@
     <row r="199" ht="90" customHeight="1">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260831_184338.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_011840.json</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -15768,11 +15768,11 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
@@ -15786,12 +15786,12 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.4991316; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.497253</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
@@ -15835,7 +15835,7 @@
     <row r="200" ht="90" customHeight="1">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260831_213159.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_031737.json</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -15845,11 +15845,11 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -15863,12 +15863,12 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009480999999999; Yeom medio=0.497243057057373; Shadow medio=0.5001202; LiRA composto=0.501827</t>
+          <t>LiRA medio=0.5002686000000001; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.500625</t>
         </is>
       </c>
       <c r="K200" s="3" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M200" s="4" t="inlineStr">
@@ -15912,7 +15912,7 @@
     <row r="201" ht="90" customHeight="1">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_071856.json</t>
+          <t>entity-split-sweep1/experiment_20260831_184338.json</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000713999999999; Yeom medio=0.4869039249495624; Shadow medio=0.4864776; LiRA composto=0.500347</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K201" s="3" t="inlineStr">
@@ -15989,7 +15989,7 @@
     <row r="202" ht="90" customHeight="1">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_093057.json</t>
+          <t>entity-split-sweep1/experiment_20260831_213159.json</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5044566; Yeom medio=0.5396062512497303; Shadow medio=0.5344805; LiRA composto=0.509723</t>
+          <t>LiRA medio=0.5009480999999999; Yeom medio=0.497243057057373; Shadow medio=0.5001202; LiRA composto=0.501827</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
@@ -16066,7 +16066,7 @@
     <row r="203" ht="90" customHeight="1">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_113947.json</t>
+          <t>entity-split-sweep1/experiment_20260901_071856.json</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5024798; Yeom medio=0.521343607391918; Shadow medio=0.5159754999999999; LiRA composto=0.507003</t>
+          <t>LiRA medio=0.5000713999999999; Yeom medio=0.4869039249495624; Shadow medio=0.4864776; LiRA composto=0.500347</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr">
@@ -16143,7 +16143,7 @@
     <row r="204" ht="90" customHeight="1">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260904_212056.json</t>
+          <t>entity-split-sweep1/experiment_20260901_093057.json</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -16153,11 +16153,11 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
@@ -16171,12 +16171,12 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I204" s="3" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
+          <t>LiRA medio=0.5044566; Yeom medio=0.5396062512497303; Shadow medio=0.5344805; LiRA composto=0.509723</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr">
@@ -16220,7 +16220,7 @@
     <row r="205" ht="90" customHeight="1">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260904_231951.json</t>
+          <t>entity-split-sweep1/experiment_20260901_113947.json</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -16230,11 +16230,11 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -16248,12 +16248,12 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I205" s="3" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
+          <t>LiRA medio=0.5024798; Yeom medio=0.521343607391918; Shadow medio=0.5159754999999999; LiRA composto=0.507003</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
@@ -16297,7 +16297,7 @@
     <row r="206" ht="90" customHeight="1">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_011919.json</t>
+          <t>local-sweep3/experiment_20260904_212056.json</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
+          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="207" ht="90" customHeight="1">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_031832.json</t>
+          <t>local-sweep3/experiment_20260904_231951.json</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -16388,7 +16388,7 @@
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
+          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
@@ -16451,7 +16451,7 @@
     <row r="208" ht="90" customHeight="1">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_051744.json</t>
+          <t>local-sweep3/experiment_20260905_011919.json</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
+          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
@@ -16528,7 +16528,7 @@
     <row r="209" ht="90" customHeight="1">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_131024.json</t>
+          <t>local-sweep3/experiment_20260905_031832.json</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -16538,11 +16538,11 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
+          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M209" s="4" t="inlineStr">
@@ -16605,7 +16605,7 @@
     <row r="210" ht="90" customHeight="1">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_151044.json</t>
+          <t>local-sweep3/experiment_20260905_051744.json</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -16615,11 +16615,11 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
+          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr">
@@ -16682,7 +16682,7 @@
     <row r="211" ht="90" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_200759.json</t>
+          <t>local-sweep4/experiment_20260907_131024.json</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -16696,7 +16696,7 @@
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
+          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr">
@@ -16759,7 +16759,7 @@
     <row r="212" ht="90" customHeight="1">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_220601.json</t>
+          <t>local-sweep4/experiment_20260907_151044.json</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -16773,7 +16773,7 @@
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
+          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr">
@@ -16836,7 +16836,7 @@
     <row r="213" ht="90" customHeight="1">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260908_000358.json</t>
+          <t>local-sweep4/experiment_20260907_200759.json</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -16850,7 +16850,7 @@
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
+          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
@@ -16913,7 +16913,7 @@
     <row r="214" ht="90" customHeight="1">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_020230.json</t>
+          <t>local-sweep4/experiment_20260907_220601.json</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -16923,11 +16923,11 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
+          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M214" s="4" t="inlineStr">
@@ -16990,7 +16990,7 @@
     <row r="215" ht="90" customHeight="1">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_040043.json</t>
+          <t>local-sweep4/experiment_20260908_000358.json</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -17000,11 +17000,11 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
+          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
@@ -17067,7 +17067,7 @@
     <row r="216" ht="90" customHeight="1">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_055925.json</t>
+          <t>local-sweep5/experiment_20260908_020230.json</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -17081,7 +17081,7 @@
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
+          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
         </is>
       </c>
       <c r="K216" s="3" t="inlineStr">
@@ -17144,7 +17144,7 @@
     <row r="217" ht="90" customHeight="1">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_075822.json</t>
+          <t>local-sweep5/experiment_20260908_040043.json</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -17158,7 +17158,7 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
+          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr">
@@ -17221,7 +17221,7 @@
     <row r="218" ht="90" customHeight="1">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_100349.json</t>
+          <t>local-sweep5/experiment_20260908_055925.json</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -17235,7 +17235,7 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
+          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr">
@@ -17298,7 +17298,7 @@
     <row r="219" ht="90" customHeight="1">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_121719.json</t>
+          <t>local-sweep5/experiment_20260908_075822.json</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -17308,11 +17308,11 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
@@ -17326,12 +17326,12 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I219" s="3" t="inlineStr">
@@ -17341,17 +17341,17 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
+          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M219" s="4" t="inlineStr">
@@ -17375,7 +17375,7 @@
     <row r="220" ht="90" customHeight="1">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_142331.json</t>
+          <t>local-sweep5/experiment_20260908_100349.json</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -17385,11 +17385,11 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -17403,12 +17403,12 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I220" s="3" t="inlineStr">
@@ -17418,17 +17418,17 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001166; Yeom medio=0.4977689383995224; Shadow medio=0.5013555000000001; LiRA composto=0.496078</t>
+          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M220" s="4" t="inlineStr">
@@ -17452,7 +17452,7 @@
     <row r="221" ht="90" customHeight="1">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_162411.json</t>
+          <t>nodp-sweep2/experiment_20260908_121719.json</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49979699999999994; Yeom medio=0.5012321998500424; Shadow medio=0.5028671; LiRA composto=0.503626</t>
+          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
         </is>
       </c>
       <c r="K221" s="3" t="inlineStr">
@@ -17529,7 +17529,7 @@
     <row r="222" ht="90" customHeight="1">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_182356.json</t>
+          <t>nodp-sweep2/experiment_20260908_142331.json</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994059999999999; Yeom medio=0.5037555029217773; Shadow medio=0.5027257; LiRA composto=0.498701</t>
+          <t>LiRA medio=0.5001166; Yeom medio=0.4977689383995224; Shadow medio=0.5013555000000001; LiRA composto=0.496078</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="223" ht="90" customHeight="1">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_202354.json</t>
+          <t>nodp-sweep2/experiment_20260908_162411.json</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -17620,7 +17620,7 @@
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007714; Yeom medio=0.5004956024284777; Shadow medio=0.5029101; LiRA composto=0.501679</t>
+          <t>LiRA medio=0.49979699999999994; Yeom medio=0.5012321998500424; Shadow medio=0.5028671; LiRA composto=0.503626</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr">
@@ -17683,7 +17683,7 @@
     <row r="224" ht="90" customHeight="1">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed123-eps0.5/experiment_20260914_152619.json</t>
+          <t>nodp-sweep2/experiment_20260908_182356.json</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -17693,11 +17693,11 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -17711,12 +17711,12 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I224" s="3" t="inlineStr">
@@ -17726,17 +17726,17 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010704; Yeom medio=0.49885817165752017; Shadow medio=0.49721390000000004; LiRA composto=0.505366</t>
+          <t>LiRA medio=0.4994059999999999; Yeom medio=0.5037555029217773; Shadow medio=0.5027257; LiRA composto=0.498701</t>
         </is>
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed123-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M224" s="4" t="inlineStr">
@@ -17760,7 +17760,7 @@
     <row r="225" ht="90" customHeight="1">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed123/experiment_20260910_172634.json</t>
+          <t>nodp-sweep2/experiment_20260908_202354.json</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -17770,13 +17770,11 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 123: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>1234</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -17790,12 +17788,12 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr">
@@ -17805,17 +17803,17 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000368; Yeom medio=0.49981732394504885; Shadow medio=0.49837070000000006; LiRA composto=0.500623</t>
+          <t>LiRA medio=0.5007714; Yeom medio=0.5004956024284777; Shadow medio=0.5029101; LiRA composto=0.501679</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M225" s="4" t="inlineStr">
@@ -17839,7 +17837,7 @@
     <row r="226" ht="90" customHeight="1">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed1234/experiment_20260911_122836.json</t>
+          <t>nvflare-central-seed123-eps0.5/experiment_20260914_152619.json</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -17849,13 +17847,11 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 1234: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>123</v>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
@@ -17874,7 +17870,7 @@
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr">
@@ -17884,7 +17880,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5012264; Yeom medio=0.5012137493317419; Shadow medio=0.5008147000000001; LiRA composto=0.506321</t>
+          <t>LiRA medio=0.5010704; Yeom medio=0.49885817165752017; Shadow medio=0.49721390000000004; LiRA composto=0.505366</t>
         </is>
       </c>
       <c r="K226" s="3" t="inlineStr">
@@ -17894,7 +17890,7 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed123-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M226" s="4" t="inlineStr">
@@ -17918,7 +17914,7 @@
     <row r="227" ht="90" customHeight="1">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed42-eps0.5/experiment_20260914_130854.json</t>
+          <t>nvflare-central-seed123/experiment_20260910_172634.json</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -17928,11 +17924,13 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="n">
-        <v>42</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 123: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
@@ -17951,7 +17949,7 @@
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -17961,7 +17959,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994279; Yeom medio=0.49465245749743075; Shadow medio=0.4958531; LiRA composto=0.500887</t>
+          <t>LiRA medio=0.5000368; Yeom medio=0.49981732394504885; Shadow medio=0.49837070000000006; LiRA composto=0.500623</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
@@ -17971,7 +17969,7 @@
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed42-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M227" s="4" t="inlineStr">
@@ -17995,7 +17993,7 @@
     <row r="228" ht="90" customHeight="1">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed456-eps0.5/experiment_20260914_175355.json</t>
+          <t>nvflare-central-seed1234/experiment_20260911_122836.json</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -18005,12 +18003,12 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 1234: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
@@ -18030,7 +18028,7 @@
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I228" s="3" t="inlineStr">
@@ -18040,7 +18038,7 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5011443; Yeom medio=0.49762605437521107; Shadow medio=0.4992915; LiRA composto=0.504601</t>
+          <t>LiRA medio=0.5012264; Yeom medio=0.5012137493317419; Shadow medio=0.5008147000000001; LiRA composto=0.506321</t>
         </is>
       </c>
       <c r="K228" s="3" t="inlineStr">
@@ -18050,7 +18048,7 @@
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed456-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M228" s="4" t="inlineStr">
@@ -18074,7 +18072,7 @@
     <row r="229" ht="90" customHeight="1">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed456/experiment_20260910_222515.json</t>
+          <t>nvflare-central-seed42-eps0.5/experiment_20260914_130854.json</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -18084,13 +18082,11 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>42</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
@@ -18109,7 +18105,7 @@
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
@@ -18119,7 +18115,7 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5015437; Yeom medio=0.4976337915896831; Shadow medio=0.5007618; LiRA composto=0.505552</t>
+          <t>LiRA medio=0.4994279; Yeom medio=0.49465245749743075; Shadow medio=0.4958531; LiRA composto=0.500887</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr">
@@ -18129,7 +18125,7 @@
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed42-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M229" s="4" t="inlineStr">
@@ -18153,7 +18149,7 @@
     <row r="230" ht="90" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed789-eps0.5/experiment_20260914_205551.json</t>
+          <t>nvflare-central-seed456-eps0.5/experiment_20260914_175355.json</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -18168,7 +18164,7 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
@@ -18188,7 +18184,7 @@
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr">
@@ -18198,7 +18194,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005679; Yeom medio=0.49992255315113887; Shadow medio=0.4980574; LiRA composto=0.502025</t>
+          <t>LiRA medio=0.5011443; Yeom medio=0.49762605437521107; Shadow medio=0.4992915; LiRA composto=0.504601</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
@@ -18208,7 +18204,7 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed789-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed456-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr">
@@ -18232,7 +18228,7 @@
     <row r="231" ht="90" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed789/experiment_20260911_095435.json</t>
+          <t>nvflare-central-seed456/experiment_20260910_222515.json</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -18247,7 +18243,7 @@
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
@@ -18277,7 +18273,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002807; Yeom medio=0.5002761736218346; Shadow medio=0.49890680000000004; LiRA composto=0.504216</t>
+          <t>LiRA medio=0.5015437; Yeom medio=0.4976337915896831; Shadow medio=0.5007618; LiRA composto=0.505552</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
@@ -18287,7 +18283,7 @@
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M231" s="4" t="inlineStr">
@@ -18311,7 +18307,7 @@
     <row r="232" ht="90" customHeight="1">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
+          <t>nvflare-central-seed789-eps0.5/experiment_20260914_205551.json</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -18321,11 +18317,13 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="n">
-        <v>1234</v>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -18339,12 +18337,12 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr">
@@ -18354,7 +18352,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
+          <t>LiRA medio=0.5005679; Yeom medio=0.49992255315113887; Shadow medio=0.4980574; LiRA composto=0.502025</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
@@ -18364,7 +18362,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed789-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr">
@@ -18388,7 +18386,7 @@
     <row r="233" ht="90" customHeight="1">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
+          <t>nvflare-central-seed789/experiment_20260911_095435.json</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -18398,11 +18396,13 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="n">
-        <v>1234</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
@@ -18416,12 +18416,12 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
+          <t>LiRA medio=0.5002807; Yeom medio=0.5002761736218346; Shadow medio=0.49890680000000004; LiRA composto=0.504216</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M233" s="4" t="inlineStr">
@@ -18465,7 +18465,7 @@
     <row r="234" ht="90" customHeight="1">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
+          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -18475,11 +18475,11 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
+          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr">
@@ -18542,7 +18542,7 @@
     <row r="235" ht="90" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
+          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D235" s="3" t="n">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
+          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M235" s="4" t="inlineStr">
@@ -18619,7 +18619,7 @@
     <row r="236" ht="90" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
+          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
+          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr">
@@ -18696,7 +18696,7 @@
     <row r="237" ht="90" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
+          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -18710,7 +18710,7 @@
         </is>
       </c>
       <c r="D237" s="3" t="n">
-        <v>456</v>
+        <v>1234</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
+          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M237" s="4" t="inlineStr">
@@ -18773,7 +18773,7 @@
     <row r="238" ht="90" customHeight="1">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
+          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -18787,7 +18787,7 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
+          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M238" s="4" t="inlineStr">
@@ -18850,7 +18850,7 @@
     <row r="239" ht="90" customHeight="1">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
+          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -18860,11 +18860,11 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D239" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
@@ -18893,7 +18893,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
+          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M239" s="4" t="inlineStr">
@@ -18927,7 +18927,7 @@
     <row r="240" ht="90" customHeight="1">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
+          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -18937,11 +18937,11 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H240" s="3" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
+          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M240" s="4" t="inlineStr">
@@ -19004,7 +19004,7 @@
     <row r="241" ht="90" customHeight="1">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_183148.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
+          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
         </is>
       </c>
       <c r="K241" s="3" t="inlineStr">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M241" s="4" t="inlineStr">
@@ -19081,7 +19081,7 @@
     <row r="242" ht="90" customHeight="1">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_203243.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -19091,11 +19091,11 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I242" s="3" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
+          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
         </is>
       </c>
       <c r="K242" s="3" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M242" s="4" t="inlineStr">
@@ -19158,7 +19158,7 @@
     <row r="243" ht="90" customHeight="1">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_223219.json</t>
+          <t>rq1-eps16/experiment_20260923_183148.json</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -19172,7 +19172,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
+          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
         </is>
       </c>
       <c r="K243" s="3" t="inlineStr">
@@ -19235,7 +19235,7 @@
     <row r="244" ht="90" customHeight="1">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260924_003215.json</t>
+          <t>rq1-eps16/experiment_20260923_203243.json</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -19249,7 +19249,7 @@
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
+          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr">
@@ -19312,7 +19312,7 @@
     <row r="245" ht="90" customHeight="1">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260924_023219.json</t>
+          <t>rq1-eps16/experiment_20260923_223219.json</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -19326,7 +19326,7 @@
         </is>
       </c>
       <c r="D245" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
+          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr">
@@ -19389,7 +19389,7 @@
     <row r="246" ht="90" customHeight="1">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_134148.json</t>
+          <t>rq1-eps16/experiment_20260924_003215.json</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -19399,11 +19399,11 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I246" s="3" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
+          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
         </is>
       </c>
       <c r="K246" s="3" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M246" s="4" t="inlineStr">
@@ -19466,7 +19466,7 @@
     <row r="247" ht="90" customHeight="1">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_154640.json</t>
+          <t>rq1-eps16/experiment_20260924_023219.json</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -19476,11 +19476,11 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
+          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M247" s="4" t="inlineStr">
@@ -19543,7 +19543,7 @@
     <row r="248" ht="90" customHeight="1">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_175039.json</t>
+          <t>rq1-eps2/experiment_20260922_134148.json</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -19557,7 +19557,7 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
+          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
@@ -19620,7 +19620,7 @@
     <row r="249" ht="90" customHeight="1">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_180414.json</t>
+          <t>rq1-eps2/experiment_20260922_154640.json</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -19634,7 +19634,7 @@
         </is>
       </c>
       <c r="D249" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
+          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr">
@@ -19676,9 +19676,9 @@
           <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
-      <c r="M249" s="5" t="inlineStr">
-        <is>
-          <t>incompleta</t>
+      <c r="M249" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="O249" s="3" t="inlineStr">
         <is>
-          <t>nessuna metrica MIA nel JSON</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P249" s="3" t="n"/>
@@ -19697,7 +19697,7 @@
     <row r="250" ht="90" customHeight="1">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_200439.json</t>
+          <t>rq1-eps2/experiment_20260922_175039.json</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -19711,7 +19711,7 @@
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
+          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
         </is>
       </c>
       <c r="K250" s="3" t="inlineStr">
@@ -19774,7 +19774,7 @@
     <row r="251" ht="90" customHeight="1">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260924_102430.json</t>
+          <t>rq1-eps2/experiment_20260922_180414.json</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
         </is>
       </c>
       <c r="K251" s="3" t="inlineStr">
@@ -19830,9 +19830,9 @@
           <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
-      <c r="M251" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+      <c r="M251" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="O251" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessuna metrica MIA nel JSON</t>
         </is>
       </c>
       <c r="P251" s="3" t="n"/>
@@ -19851,7 +19851,7 @@
     <row r="252" ht="90" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260922_220310.json</t>
+          <t>rq1-eps2/experiment_20260922_200439.json</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -19861,11 +19861,11 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I252" s="3" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
+          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
         </is>
       </c>
       <c r="K252" s="3" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M252" s="4" t="inlineStr">
@@ -19928,7 +19928,7 @@
     <row r="253" ht="90" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_000138.json</t>
+          <t>rq1-eps2/experiment_20260924_102430.json</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -19938,11 +19938,11 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
+          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
         </is>
       </c>
       <c r="K253" s="3" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M253" s="4" t="inlineStr">
@@ -20005,7 +20005,7 @@
     <row r="254" ht="90" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_020058.json</t>
+          <t>rq1-eps4/experiment_20260922_220310.json</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -20019,7 +20019,7 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
+          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
@@ -20082,7 +20082,7 @@
     <row r="255" ht="90" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_040025.json</t>
+          <t>rq1-eps4/experiment_20260923_000138.json</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -20096,7 +20096,7 @@
         </is>
       </c>
       <c r="D255" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
+          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
@@ -20159,7 +20159,7 @@
     <row r="256" ht="90" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_055955.json</t>
+          <t>rq1-eps4/experiment_20260923_020058.json</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -20173,7 +20173,7 @@
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
+          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="257" ht="90" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_080158.json</t>
+          <t>rq1-eps4/experiment_20260923_040025.json</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -20246,11 +20246,11 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D257" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
+          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
         </is>
       </c>
       <c r="K257" s="3" t="inlineStr">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="L257" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M257" s="4" t="inlineStr">
@@ -20313,7 +20313,7 @@
     <row r="258" ht="90" customHeight="1">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_100736.json</t>
+          <t>rq1-eps4/experiment_20260923_055955.json</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -20323,11 +20323,11 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
+          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
         </is>
       </c>
       <c r="K258" s="3" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M258" s="4" t="inlineStr">
@@ -20390,7 +20390,7 @@
     <row r="259" ht="90" customHeight="1">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_121447.json</t>
+          <t>rq1-eps8/experiment_20260923_080158.json</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
+          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
         </is>
       </c>
       <c r="K259" s="3" t="inlineStr">
@@ -20467,7 +20467,7 @@
     <row r="260" ht="90" customHeight="1">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_142154.json</t>
+          <t>rq1-eps8/experiment_20260923_100736.json</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -20481,7 +20481,7 @@
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr">
@@ -20544,7 +20544,7 @@
     <row r="261" ht="90" customHeight="1">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_162834.json</t>
+          <t>rq1-eps8/experiment_20260923_121447.json</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -20558,7 +20558,7 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
         </is>
       </c>
       <c r="K261" s="3" t="inlineStr">
@@ -20617,6 +20617,160 @@
       </c>
       <c r="P261" s="3" t="n"/>
       <c r="Q261" s="3" t="n"/>
+    </row>
+    <row r="262" ht="90" customHeight="1">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_142154.json</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J262" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M262" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O262" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P262" s="3" t="n"/>
+      <c r="Q262" s="3" t="n"/>
+    </row>
+    <row r="263" ht="90" customHeight="1">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_162834.json</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I263" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J263" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M263" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O263" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P263" s="3" t="n"/>
+      <c r="Q263" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q263"/>
+  <dimension ref="A1:Q269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10060,7 +10060,7 @@
     <row r="125" ht="90" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>_op_eps64/experiment_20260924_212917.json</t>
+          <t>_op_C0.25_eps256/experiment_20260925_072650.json</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=256.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=2560.0; eps_avanzata=3.869254822410505e+114; eps_migliore=2560.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -10103,17 +10103,17 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49855; Yeom medio=0.4992467157518548; Shadow medio=0.4996785; LiRA composto=0.499981</t>
+          <t>LiRA medio=0.5012149000000001; Yeom medio=0.49683876766725527; Shadow medio=0.49366509999999997; LiRA composto=0.50528</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>logs/op_eps64.log</t>
+          <t>logs/op_C0.25_eps256.log</t>
         </is>
       </c>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>experiments/_op_eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/_op_C0.25_eps256/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
@@ -10137,7 +10137,7 @@
     <row r="126" ht="90" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>_prova_recorddp/experiment_20260924_144713.json</t>
+          <t>_op_C0.25_eps64/experiment_20260924_232900.json</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=0.9936577181915225</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -10160,17 +10160,17 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP (diagnostico)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
@@ -10180,22 +10180,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
+          <t>LiRA medio=0.4989031; Yeom medio=0.4973501604726366; Shadow medio=0.49457129999999994; LiRA composto=0.498545</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>logs/prova_recorddp_s42_attacchi_saltati.log</t>
+          <t>logs/op_C0.25_eps64.log</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>experiments/_prova_recorddp/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M126" s="5" t="inlineStr">
-        <is>
-          <t>incompleta</t>
+          <t>experiments/_op_C0.25_eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>nessuna metrica MIA nel JSON</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P126" s="3" t="n"/>
@@ -10214,17 +10214,17 @@
     <row r="127" ht="90" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>_rdp_balanced_recorddp_fast/experiment_20260917_064655.json</t>
+          <t>_op_C0.5_eps16/experiment_20260925_032814.json</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D127" s="3" t="n">
@@ -10237,37 +10237,37 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3886876666666666; Yeom medio=0.5163276180775616; Shadow medio=0.5461393333333333; LiRA composto=0.35769; canary raw=0.435</t>
+          <t>LiRA medio=0.5001431000000001; Yeom medio=0.49847015049216353; Shadow medio=0.4986929; LiRA composto=0.498221</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/op_C0.5_eps16.log</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_balanced_recorddp_fast/ (JSON + xlsx + history/)</t>
+          <t>experiments/_op_C0.5_eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P127" s="3" t="n"/>
@@ -10291,17 +10291,17 @@
     <row r="128" ht="90" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>_rdp_e1000_s5_s42/experiment_20260917_081852.json</t>
+          <t>_op_C0.5_eps256/experiment_20260925_092618.json</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=256.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -10314,37 +10314,37 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=2560.0; eps_avanzata=3.869254822410505e+114; eps_migliore=2560.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
+          <t>LiRA medio=0.4999955; Yeom medio=0.4973187423267123; Shadow medio=0.49495880000000003; LiRA composto=0.505845</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>logs/rdp_e1000_s5.log</t>
+          <t>logs/op_C0.5_eps256.log</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_e1000_s5_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_op_C0.5_eps256/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P128" s="3" t="n"/>
@@ -10368,17 +10368,17 @@
     <row r="129" ht="90" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>_rdp_eps163_s42/experiment_20260917_072712.json</t>
+          <t>_op_C0.5_eps64/experiment_20260925_052718.json</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
@@ -10391,37 +10391,37 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.38548333333333334; Yeom medio=0.5171245473064735; Shadow medio=0.5352726666666667; LiRA composto=0.297562; canary raw=0.54</t>
+          <t>LiRA medio=0.4992666; Yeom medio=0.4982146592450144; Shadow medio=0.49783599999999995; LiRA composto=0.5007</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/op_C0.5_eps64.log</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_eps163_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_op_C0.5_eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P129" s="3" t="n"/>
@@ -10445,17 +10445,17 @@
     <row r="130" ht="90" customHeight="1">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>_rdp_eps474_s42/experiment_20260917_072736.json</t>
+          <t>_op_eps256/experiment_20260925_012834.json</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=256.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -10468,37 +10468,37 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=2560.0; eps_avanzata=3.869254822410505e+114; eps_migliore=2560.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4051313333333333; Yeom medio=0.5234622566772296; Shadow medio=0.551126; LiRA composto=0.337742; canary raw=0.56</t>
+          <t>LiRA medio=0.501195; Yeom medio=0.4994859779459112; Shadow medio=0.5007957000000001; LiRA composto=0.503538</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/op_eps256.log</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_eps474_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_op_eps256/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P130" s="3" t="n"/>
@@ -10522,17 +10522,17 @@
     <row r="131" ht="90" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>_rdp_nm005_swap_s42/experiment_20260917_071708.json</t>
+          <t>_op_eps64/experiment_20260924_212917.json</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
@@ -10545,37 +10545,37 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.40725966666666674; Yeom medio=0.5490818809416025; Shadow medio=0.59682; LiRA composto=0.406503; canary raw=0.675</t>
+          <t>LiRA medio=0.49855; Yeom medio=0.4992467157518548; Shadow medio=0.4996785; LiRA composto=0.499981</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/op_eps64.log</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_nm005_swap_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_op_eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P131" s="3" t="n"/>
@@ -10599,17 +10599,17 @@
     <row r="132" ht="90" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>_rdp_recorddp_nm005/experiment_20260917_065335.json</t>
+          <t>_prova_recorddp/experiment_20260924_144713.json</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=0.9936577181915225</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale — record-DP (diagnostico)</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -10637,27 +10637,27 @@
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3775196666666667; Yeom medio=0.5008205070167496; Shadow medio=0.5375216666666667; LiRA composto=0.343919; canary raw=0.4625</t>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/prova_recorddp_s42_attacchi_saltati.log</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_recorddp_nm005/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M132" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+          <t>experiments/_prova_recorddp/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessuna metrica MIA nel JSON</t>
         </is>
       </c>
       <c r="P132" s="3" t="n"/>
@@ -10676,7 +10676,7 @@
     <row r="133" ht="90" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>_rdp_recorddp_nm01/experiment_20260917_065015.json</t>
+          <t>_rdp_balanced_recorddp_fast/experiment_20260917_064655.json</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3853766666666667; Yeom medio=0.48447874226648563; Shadow medio=0.5364559999999999; LiRA composto=0.355141; canary raw=0.4675</t>
+          <t>LiRA medio=0.3886876666666666; Yeom medio=0.5163276180775616; Shadow medio=0.5461393333333333; LiRA composto=0.35769; canary raw=0.435</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_recorddp_nm01/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_balanced_recorddp_fast/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
@@ -10753,7 +10753,7 @@
     <row r="134" ht="90" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>_rdp_ref_e10_s42/experiment_20260917_072648.json</t>
+          <t>_rdp_e1000_s5_s42/experiment_20260917_081852.json</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -10796,17 +10796,17 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.611027; Yeom medio=0.49774360570393844; Shadow medio=0.525556; LiRA composto=0.669276; canary raw=0.4925</t>
+          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/rdp_e1000_s5.log</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_ref_e10_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_e1000_s5_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
@@ -10830,7 +10830,7 @@
     <row r="135" ht="90" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>_ref_e1000_group_s42/experiment_20260917_073820.json</t>
+          <t>_rdp_eps163_s42/experiment_20260917_072712.json</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D135" s="3" t="n">
@@ -10873,17 +10873,17 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
+          <t>LiRA medio=0.38548333333333334; Yeom medio=0.5171245473064735; Shadow medio=0.5352726666666667; LiRA composto=0.297562; canary raw=0.54</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>logs/ref_e1000_group.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>experiments/_ref_e1000_group_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_eps163_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
@@ -10907,17 +10907,17 @@
     <row r="136" ht="90" customHeight="1">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_135401.json</t>
+          <t>_rdp_eps474_s42/experiment_20260917_072736.json</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -10945,12 +10945,12 @@
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.4051313333333333; Yeom medio=0.5234622566772296; Shadow medio=0.551126; LiRA composto=0.337742; canary raw=0.56</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_eps474_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P136" s="3" t="n"/>
@@ -10984,17 +10984,17 @@
     <row r="137" ht="90" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_151156.json</t>
+          <t>_rdp_nm005_swap_s42/experiment_20260917_071708.json</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
         </is>
       </c>
       <c r="D137" s="3" t="n">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.40725966666666674; Yeom medio=0.5490818809416025; Shadow medio=0.59682; LiRA composto=0.406503; canary raw=0.675</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_nm005_swap_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P137" s="3" t="n"/>
@@ -11061,17 +11061,17 @@
     <row r="138" ht="90" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_181649.json</t>
+          <t>_rdp_recorddp_nm005/experiment_20260917_065335.json</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.3775196666666667; Yeom medio=0.5008205070167496; Shadow medio=0.5375216666666667; LiRA composto=0.343919; canary raw=0.4625</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_recorddp_nm005/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P138" s="3" t="n"/>
@@ -11138,17 +11138,17 @@
     <row r="139" ht="90" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>_smoke_centralized_control/experiment_20260901_141640.json</t>
+          <t>_rdp_recorddp_nm01/experiment_20260917_065015.json</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D139" s="3" t="n">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -11176,12 +11176,12 @@
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
+          <t>LiRA medio=0.3853766666666667; Yeom medio=0.48447874226648563; Shadow medio=0.5364559999999999; LiRA composto=0.355141; canary raw=0.4675</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_centralized_control/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_recorddp_nm01/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P139" s="3" t="n"/>
@@ -11215,17 +11215,17 @@
     <row r="140" ht="90" customHeight="1">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260901_141146.json</t>
+          <t>_rdp_ref_e10_s42/experiment_20260917_072648.json</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -11253,12 +11253,12 @@
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
+          <t>LiRA medio=0.611027; Yeom medio=0.49774360570393844; Shadow medio=0.525556; LiRA composto=0.669276; canary raw=0.4925</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_ref_e10_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P140" s="3" t="n"/>
@@ -11292,17 +11292,17 @@
     <row r="141" ht="90" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260901_191839.json</t>
+          <t>_ref_e1000_group_s42/experiment_20260917_073820.json</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D141" s="3" t="n">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/ref_e1000_group.log</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_ref_e1000_group_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P141" s="3" t="n"/>
@@ -11369,7 +11369,7 @@
     <row r="142" ht="90" customHeight="1">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260902_062136.json</t>
+          <t>_robustness_entity_split/experiment_20260831_135401.json</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -11407,12 +11407,12 @@
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -11446,7 +11446,7 @@
     <row r="143" ht="90" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260902_131018.json</t>
+          <t>_robustness_entity_split/experiment_20260831_151156.json</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D143" s="3" t="n">
@@ -11484,12 +11484,12 @@
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
@@ -11523,7 +11523,7 @@
     <row r="144" ht="90" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_n16/experiment_20260901_143530.json</t>
+          <t>_robustness_entity_split/experiment_20260831_181649.json</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_n16/ (JSON + xlsx + history/)</t>
+          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
@@ -11600,7 +11600,7 @@
     <row r="145" ht="90" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_n16_v2/experiment_20260901_150314.json</t>
+          <t>_smoke_centralized_control/experiment_20260901_141640.json</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
+          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_n16_v2/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_centralized_control/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
@@ -11677,7 +11677,7 @@
     <row r="146" ht="90" customHeight="1">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_normalized/experiment_20260902_140132.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260901_141146.json</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_normalized/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr">
@@ -11754,7 +11754,7 @@
     <row r="147" ht="90" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>_smoke_sb2_dp-fedavg/experiment_20260917_210602.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260901_191839.json</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D147" s="3" t="n">
@@ -11782,22 +11782,22 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>1 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.494587; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.494587</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_sb2_dp-fedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
     <row r="148" ht="90" customHeight="1">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>_smoke_sb2_local/experiment_20260917_210627.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260902_062136.json</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -11859,22 +11859,22 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>1 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.491745; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.491745</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_sb2_local/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="149" ht="90" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>_smoke_stradaB_dp-fedavg/experiment_20260917_205626.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260902_131018.json</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
@@ -11936,22 +11936,22 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>1 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.499264; Yeom medio=0.4981025148508319; Shadow medio=0.497864; LiRA composto=0.499264</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_stradaB_dp-fedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
@@ -11985,7 +11985,7 @@
     <row r="150" ht="90" customHeight="1">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>_verify_10rounds_central/experiment_20260826_150039.json</t>
+          <t>_smoke_fedmia_gradient_n16/experiment_20260901_143530.json</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -12013,22 +12013,22 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013407; Yeom medio=0.49943881126863526; Shadow medio=0.49939399999999995; LiRA composto=0.501579</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_10rounds_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_n16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -12062,7 +12062,7 @@
     <row r="151" ht="90" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>_verify_10rounds_nodp/experiment_20260826_121351.json</t>
+          <t>_smoke_fedmia_gradient_n16_v2/experiment_20260901_150314.json</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D151" s="3" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_10rounds_nodp/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_n16_v2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="152" ht="90" customHeight="1">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>_verify_mu_anchor/experiment_20260821_045041.json</t>
+          <t>_smoke_fedmia_gradient_normalized/experiment_20260902_140132.json</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_mu_anchor/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_normalized/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
@@ -12216,7 +12216,7 @@
     <row r="153" ht="90" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>_verify_outlier_fix/experiment_20260821_030556.json</t>
+          <t>_smoke_sb2_dp-fedavg/experiment_20260917_210602.json</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D153" s="3" t="n">
@@ -12244,22 +12244,22 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>1 round valutati</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.436568; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.30242</t>
+          <t>LiRA medio=0.494587; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.494587</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_outlier_fix/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_sb2_dp-fedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -12293,7 +12293,7 @@
     <row r="154" ht="90" customHeight="1">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>_verify_shadow_universe_central/experiment_20260825_142623.json</t>
+          <t>_smoke_sb2_local/experiment_20260917_210627.json</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -12321,22 +12321,22 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>1 round valutati</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.501707; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.500864</t>
+          <t>LiRA medio=0.491745; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.491745</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_shadow_universe_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_sb2_local/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
@@ -12370,7 +12370,7 @@
     <row r="155" ht="90" customHeight="1">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>_verify_shadow_universe_nodp/experiment_20260825_123128.json</t>
+          <t>_smoke_stradaB_dp-fedavg/experiment_20260917_205626.json</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D155" s="3" t="n">
@@ -12398,22 +12398,22 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>1 round valutati</t>
         </is>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.502457; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.498992</t>
+          <t>LiRA medio=0.499264; Yeom medio=0.4981025148508319; Shadow medio=0.497864; LiRA composto=0.499264</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_shadow_universe_nodp/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_stradaB_dp-fedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
@@ -12447,7 +12447,7 @@
     <row r="156" ht="90" customHeight="1">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_101722.json</t>
+          <t>_verify_10rounds_central/experiment_20260826_150039.json</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005919; Yeom medio=0.49896493538774356; Shadow medio=0.49793459999999995; LiRA composto=0.50205</t>
+          <t>LiRA medio=0.5013407; Yeom medio=0.49943881126863526; Shadow medio=0.49939399999999995; LiRA composto=0.501579</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_10rounds_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="157" ht="90" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_132410.json</t>
+          <t>_verify_10rounds_nodp/experiment_20260826_121351.json</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -12534,11 +12534,11 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007217; Yeom medio=0.4973242024691359; Shadow medio=0.49804750000000003; LiRA composto=0.5011</t>
+          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_10rounds_nodp/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -12601,7 +12601,7 @@
     <row r="158" ht="90" customHeight="1">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_152449.json</t>
+          <t>_verify_mu_anchor/experiment_20260821_045041.json</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -12611,11 +12611,11 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -12629,22 +12629,22 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003599999999999; Yeom medio=0.500791060952068; Shadow medio=0.5014752; LiRA composto=0.503782</t>
+          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
         </is>
       </c>
       <c r="K158" s="3" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_mu_anchor/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
@@ -12678,7 +12678,7 @@
     <row r="159" ht="90" customHeight="1">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_172351.json</t>
+          <t>_verify_outlier_fix/experiment_20260821_030556.json</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -12688,11 +12688,11 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -12706,22 +12706,22 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49905990000000006; Yeom medio=0.500571496779277; Shadow medio=0.500362; LiRA composto=0.495431</t>
+          <t>LiRA medio=0.436568; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.30242</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_outlier_fix/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
@@ -12755,7 +12755,7 @@
     <row r="160" ht="90" customHeight="1">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_192220.json</t>
+          <t>_verify_shadow_universe_central/experiment_20260825_142623.json</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -12765,11 +12765,11 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>1234</v>
+        <v>42</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987811; Yeom medio=0.5031364589234597; Shadow medio=0.5001119; LiRA composto=0.498958</t>
+          <t>LiRA medio=0.501707; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.500864</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_shadow_universe_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
@@ -12832,7 +12832,7 @@
     <row r="161" ht="90" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_125850.json</t>
+          <t>_verify_shadow_universe_nodp/experiment_20260825_123128.json</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D161" s="3" t="n">
@@ -12860,22 +12860,22 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5011854000000001; Yeom medio=0.49965422177892016; Shadow medio=0.4990378000000001; LiRA composto=0.502787</t>
+          <t>LiRA medio=0.502457; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.498992</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="L161" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_shadow_universe_nodp/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="162" ht="90" customHeight="1">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_191408.json</t>
+          <t>central-sweep5/experiment_20260904_101722.json</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -12919,11 +12919,11 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009991000000001; Yeom medio=0.4972590761864777; Shadow medio=0.4984662999999999; LiRA composto=0.505951</t>
+          <t>LiRA medio=0.5005919; Yeom medio=0.49896493538774356; Shadow medio=0.49793459999999995; LiRA composto=0.50205</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -12986,7 +12986,7 @@
     <row r="163" ht="90" customHeight="1">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_211234.json</t>
+          <t>central-sweep5/experiment_20260904_132410.json</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -12996,11 +12996,11 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4992345; Yeom medio=0.500988430412608; Shadow medio=0.5016581; LiRA composto=0.496234</t>
+          <t>LiRA medio=0.5007217; Yeom medio=0.4973242024691359; Shadow medio=0.49804750000000003; LiRA composto=0.5011</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="L163" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <row r="164" ht="90" customHeight="1">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_231027.json</t>
+          <t>central-sweep5/experiment_20260904_152449.json</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -13073,11 +13073,11 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5017716000000001; Yeom medio=0.5013164942039221; Shadow medio=0.5005728; LiRA composto=0.50808</t>
+          <t>LiRA medio=0.5003599999999999; Yeom medio=0.500791060952068; Shadow medio=0.5014752; LiRA composto=0.503782</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
@@ -13140,7 +13140,7 @@
     <row r="165" ht="90" customHeight="1">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260907_010817.json</t>
+          <t>central-sweep5/experiment_20260904_172351.json</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -13150,11 +13150,11 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49917149999999993; Yeom medio=0.5037495900610333; Shadow medio=0.500691; LiRA composto=0.49906</t>
+          <t>LiRA medio=0.49905990000000006; Yeom medio=0.500571496779277; Shadow medio=0.500362; LiRA composto=0.495431</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="L165" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="166" ht="90" customHeight="1">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_030628.json</t>
+          <t>central-sweep5/experiment_20260904_192220.json</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -13227,11 +13227,11 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49977089999999996; Yeom medio=0.49805428686925496; Shadow medio=0.49676210000000004; LiRA composto=0.498855</t>
+          <t>LiRA medio=0.4987811; Yeom medio=0.5031364589234597; Shadow medio=0.5001119; LiRA composto=0.498958</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="167" ht="90" customHeight="1">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_050525.json</t>
+          <t>central-sweep6/experiment_20260906_125850.json</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -13304,11 +13304,11 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996276; Yeom medio=0.4971502873000452; Shadow medio=0.49816270000000007; LiRA composto=0.50023</t>
+          <t>LiRA medio=0.5011854000000001; Yeom medio=0.49965422177892016; Shadow medio=0.4990378000000001; LiRA composto=0.502787</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M167" s="4" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="168" ht="90" customHeight="1">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_070400.json</t>
+          <t>central-sweep6/experiment_20260906_191408.json</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -13381,11 +13381,11 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002849; Yeom medio=0.5002013692212844; Shadow medio=0.4996085; LiRA composto=0.503648</t>
+          <t>LiRA medio=0.5009991000000001; Yeom medio=0.4972590761864777; Shadow medio=0.4984662999999999; LiRA composto=0.505951</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr">
@@ -13448,7 +13448,7 @@
     <row r="169" ht="90" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_090208.json</t>
+          <t>central-sweep6/experiment_20260906_211234.json</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -13458,11 +13458,11 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006189; Yeom medio=0.5009834468601285; Shadow medio=0.5005473; LiRA composto=0.502658</t>
+          <t>LiRA medio=0.4992345; Yeom medio=0.500988430412608; Shadow medio=0.5016581; LiRA composto=0.496234</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M169" s="4" t="inlineStr">
@@ -13525,7 +13525,7 @@
     <row r="170" ht="90" customHeight="1">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_110100.json</t>
+          <t>central-sweep6/experiment_20260906_231027.json</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -13535,11 +13535,11 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5020007000000001; Yeom medio=0.5036042090648936; Shadow medio=0.5011106; LiRA composto=0.50446</t>
+          <t>LiRA medio=0.5017716000000001; Yeom medio=0.5013164942039221; Shadow medio=0.5005728; LiRA composto=0.50808</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
@@ -13602,7 +13602,7 @@
     <row r="171" ht="90" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_071625.json</t>
+          <t>central-sweep6/experiment_20260907_010817.json</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -13612,11 +13612,11 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
+          <t>LiRA medio=0.49917149999999993; Yeom medio=0.5037495900610333; Shadow medio=0.500691; LiRA composto=0.49906</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M171" s="4" t="inlineStr">
@@ -13679,7 +13679,7 @@
     <row r="172" ht="90" customHeight="1">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_091555.json</t>
+          <t>central-sweep7/experiment_20260907_030628.json</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -13689,11 +13689,11 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -13707,12 +13707,12 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
+          <t>LiRA medio=0.49977089999999996; Yeom medio=0.49805428686925496; Shadow medio=0.49676210000000004; LiRA composto=0.498855</t>
         </is>
       </c>
       <c r="K172" s="3" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
@@ -13756,7 +13756,7 @@
     <row r="173" ht="90" customHeight="1">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_111424.json</t>
+          <t>central-sweep7/experiment_20260907_050525.json</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -13766,11 +13766,11 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -13784,12 +13784,12 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
+          <t>LiRA medio=0.4996276; Yeom medio=0.4971502873000452; Shadow medio=0.49816270000000007; LiRA composto=0.50023</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M173" s="4" t="inlineStr">
@@ -13833,7 +13833,7 @@
     <row r="174" ht="90" customHeight="1">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_131307.json</t>
+          <t>central-sweep7/experiment_20260907_070400.json</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -13843,11 +13843,11 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -13861,12 +13861,12 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
+          <t>LiRA medio=0.5002849; Yeom medio=0.5002013692212844; Shadow medio=0.4996085; LiRA composto=0.503648</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr">
@@ -13910,7 +13910,7 @@
     <row r="175" ht="90" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_151128.json</t>
+          <t>central-sweep7/experiment_20260907_090208.json</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -13920,11 +13920,11 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -13938,12 +13938,12 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
+          <t>LiRA medio=0.5006189; Yeom medio=0.5009834468601285; Shadow medio=0.5005473; LiRA composto=0.502658</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M175" s="4" t="inlineStr">
@@ -13987,7 +13987,7 @@
     <row r="176" ht="90" customHeight="1">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_171005.json</t>
+          <t>central-sweep7/experiment_20260907_110100.json</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -13997,11 +13997,11 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -14015,12 +14015,12 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
+          <t>LiRA medio=0.5020007000000001; Yeom medio=0.5036042090648936; Shadow medio=0.5011106; LiRA composto=0.50446</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
@@ -14064,7 +14064,7 @@
     <row r="177" ht="90" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_190905.json</t>
+          <t>dp-sweep4/experiment_20260905_071625.json</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -14074,11 +14074,11 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
+          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
         </is>
       </c>
       <c r="K177" s="3" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
@@ -14141,7 +14141,7 @@
     <row r="178" ht="90" customHeight="1">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_210838.json</t>
+          <t>dp-sweep4/experiment_20260905_091555.json</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -14151,11 +14151,11 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
+          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
         </is>
       </c>
       <c r="K178" s="3" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
@@ -14218,7 +14218,7 @@
     <row r="179" ht="90" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_230738.json</t>
+          <t>dp-sweep4/experiment_20260905_111424.json</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -14228,11 +14228,11 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
+          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
         </is>
       </c>
       <c r="K179" s="3" t="inlineStr">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
@@ -14295,7 +14295,7 @@
     <row r="180" ht="90" customHeight="1">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260906_010556.json</t>
+          <t>dp-sweep4/experiment_20260905_131307.json</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -14305,11 +14305,11 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
+          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
         </is>
       </c>
       <c r="K180" s="3" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
@@ -14372,7 +14372,7 @@
     <row r="181" ht="90" customHeight="1">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_030425.json</t>
+          <t>dp-sweep4/experiment_20260905_151128.json</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -14382,11 +14382,11 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
+          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr">
@@ -14449,7 +14449,7 @@
     <row r="182" ht="90" customHeight="1">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_050301.json</t>
+          <t>dp-sweep5/experiment_20260905_171005.json</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -14459,11 +14459,11 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
+          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
         </is>
       </c>
       <c r="K182" s="3" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
@@ -14526,7 +14526,7 @@
     <row r="183" ht="90" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_070124.json</t>
+          <t>dp-sweep5/experiment_20260905_190905.json</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -14536,11 +14536,11 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
+          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr">
@@ -14603,7 +14603,7 @@
     <row r="184" ht="90" customHeight="1">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_090022.json</t>
+          <t>dp-sweep5/experiment_20260905_210838.json</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -14613,11 +14613,11 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
+          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="185" ht="90" customHeight="1">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_105941.json</t>
+          <t>dp-sweep5/experiment_20260905_230738.json</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -14690,11 +14690,11 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
+          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr">
@@ -14757,7 +14757,7 @@
     <row r="186" ht="90" customHeight="1">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260917_230655.json</t>
+          <t>dp-sweep5/experiment_20260906_010556.json</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -14767,11 +14767,11 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.498673; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.497625</t>
+          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
         </is>
       </c>
       <c r="K186" s="3" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
@@ -14834,7 +14834,7 @@
     <row r="187" ht="90" customHeight="1">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_010547.json</t>
+          <t>dp-sweep6/experiment_20260906_030425.json</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -14844,11 +14844,11 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5008796; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.499315</t>
+          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
         </is>
       </c>
       <c r="K187" s="3" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
@@ -14911,7 +14911,7 @@
     <row r="188" ht="90" customHeight="1">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_030414.json</t>
+          <t>dp-sweep6/experiment_20260906_050301.json</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -14921,11 +14921,11 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49872580000000005; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498937</t>
+          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
         </is>
       </c>
       <c r="K188" s="3" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr">
@@ -14988,7 +14988,7 @@
     <row r="189" ht="90" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_050226.json</t>
+          <t>dp-sweep6/experiment_20260906_070124.json</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -14998,11 +14998,11 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991087; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.4982</t>
+          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
@@ -15065,7 +15065,7 @@
     <row r="190" ht="90" customHeight="1">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_070126.json</t>
+          <t>dp-sweep6/experiment_20260906_090022.json</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -15075,11 +15075,11 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5012004000000001; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.503942</t>
+          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
@@ -15142,7 +15142,7 @@
     <row r="191" ht="90" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_090012.json</t>
+          <t>dp-sweep6/experiment_20260906_105941.json</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -15152,11 +15152,11 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991078; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.497224</t>
+          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="L191" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
@@ -15219,7 +15219,7 @@
     <row r="192" ht="90" customHeight="1">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_110316.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260917_230655.json</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -15229,11 +15229,11 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49917960000000006; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.494169</t>
+          <t>LiRA medio=0.498673; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.497625</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
@@ -15296,7 +15296,7 @@
     <row r="193" ht="90" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_130646.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_010547.json</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -15306,11 +15306,11 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49895890000000004; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.49704</t>
+          <t>LiRA medio=0.5008796; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.499315</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
@@ -15373,7 +15373,7 @@
     <row r="194" ht="90" customHeight="1">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_152053.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_030414.json</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -15383,11 +15383,11 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987621; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.49875</t>
+          <t>LiRA medio=0.49872580000000005; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498937</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
@@ -15450,7 +15450,7 @@
     <row r="195" ht="90" customHeight="1">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_172416.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_050226.json</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -15460,11 +15460,11 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500696; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.503045</t>
+          <t>LiRA medio=0.4991087; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.4982</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
@@ -15527,7 +15527,7 @@
     <row r="196" ht="90" customHeight="1">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_192336.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_070126.json</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -15537,11 +15537,11 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4981084; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.496392</t>
+          <t>LiRA medio=0.5012004000000001; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.503942</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
@@ -15580,7 +15580,7 @@
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
@@ -15604,7 +15604,7 @@
     <row r="197" ht="90" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_212202.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_090012.json</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -15614,11 +15614,11 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991732000000001; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.494029</t>
+          <t>LiRA medio=0.4991078; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.497224</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
@@ -15681,7 +15681,7 @@
     <row r="198" ht="90" customHeight="1">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_232046.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_110316.json</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -15691,11 +15691,11 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="H198" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933639999999996; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.497262</t>
+          <t>LiRA medio=0.49917960000000006; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.494169</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr">
@@ -15758,7 +15758,7 @@
     <row r="199" ht="90" customHeight="1">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_011840.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_130646.json</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -15768,11 +15768,11 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991316; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.497253</t>
+          <t>LiRA medio=0.49895890000000004; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.49704</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
@@ -15835,7 +15835,7 @@
     <row r="200" ht="90" customHeight="1">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_031737.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_152053.json</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -15845,11 +15845,11 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002686000000001; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.500625</t>
+          <t>LiRA medio=0.4987621; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.49875</t>
         </is>
       </c>
       <c r="K200" s="3" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M200" s="4" t="inlineStr">
@@ -15912,7 +15912,7 @@
     <row r="201" ht="90" customHeight="1">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260831_184338.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_172416.json</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -15922,11 +15922,11 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -15940,12 +15940,12 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.500696; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.503045</t>
         </is>
       </c>
       <c r="K201" s="3" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M201" s="4" t="inlineStr">
@@ -15989,7 +15989,7 @@
     <row r="202" ht="90" customHeight="1">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260831_213159.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_192336.json</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -15999,11 +15999,11 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -16017,12 +16017,12 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009480999999999; Yeom medio=0.497243057057373; Shadow medio=0.5001202; LiRA composto=0.501827</t>
+          <t>LiRA medio=0.4981084; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.496392</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M202" s="4" t="inlineStr">
@@ -16066,7 +16066,7 @@
     <row r="203" ht="90" customHeight="1">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_071856.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_212202.json</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -16076,11 +16076,11 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
@@ -16094,12 +16094,12 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000713999999999; Yeom medio=0.4869039249495624; Shadow medio=0.4864776; LiRA composto=0.500347</t>
+          <t>LiRA medio=0.4991732000000001; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.494029</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M203" s="4" t="inlineStr">
@@ -16143,7 +16143,7 @@
     <row r="204" ht="90" customHeight="1">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_093057.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_232046.json</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -16153,11 +16153,11 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
@@ -16171,12 +16171,12 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I204" s="3" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5044566; Yeom medio=0.5396062512497303; Shadow medio=0.5344805; LiRA composto=0.509723</t>
+          <t>LiRA medio=0.49933639999999996; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.497262</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr">
@@ -16220,7 +16220,7 @@
     <row r="205" ht="90" customHeight="1">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_113947.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_011840.json</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -16230,11 +16230,11 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -16248,12 +16248,12 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I205" s="3" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5024798; Yeom medio=0.521343607391918; Shadow medio=0.5159754999999999; LiRA composto=0.507003</t>
+          <t>LiRA medio=0.4991316; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.497253</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
@@ -16297,7 +16297,7 @@
     <row r="206" ht="90" customHeight="1">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260904_212056.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_031737.json</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -16307,11 +16307,11 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -16325,12 +16325,12 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
+          <t>LiRA medio=0.5002686000000001; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.500625</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="207" ht="90" customHeight="1">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260904_231951.json</t>
+          <t>entity-split-sweep1/experiment_20260831_184338.json</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -16384,11 +16384,11 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -16402,12 +16402,12 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M207" s="4" t="inlineStr">
@@ -16451,7 +16451,7 @@
     <row r="208" ht="90" customHeight="1">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_011919.json</t>
+          <t>entity-split-sweep1/experiment_20260831_213159.json</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -16461,11 +16461,11 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -16479,12 +16479,12 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
+          <t>LiRA medio=0.5009480999999999; Yeom medio=0.497243057057373; Shadow medio=0.5001202; LiRA composto=0.501827</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M208" s="4" t="inlineStr">
@@ -16528,7 +16528,7 @@
     <row r="209" ht="90" customHeight="1">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_031832.json</t>
+          <t>entity-split-sweep1/experiment_20260901_071856.json</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -16538,11 +16538,11 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -16556,12 +16556,12 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
+          <t>LiRA medio=0.5000713999999999; Yeom medio=0.4869039249495624; Shadow medio=0.4864776; LiRA composto=0.500347</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M209" s="4" t="inlineStr">
@@ -16605,7 +16605,7 @@
     <row r="210" ht="90" customHeight="1">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_051744.json</t>
+          <t>entity-split-sweep1/experiment_20260901_093057.json</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -16615,11 +16615,11 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -16633,12 +16633,12 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
+          <t>LiRA medio=0.5044566; Yeom medio=0.5396062512497303; Shadow medio=0.5344805; LiRA composto=0.509723</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr">
@@ -16682,7 +16682,7 @@
     <row r="211" ht="90" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_131024.json</t>
+          <t>entity-split-sweep1/experiment_20260901_113947.json</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -16692,11 +16692,11 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -16710,12 +16710,12 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
+          <t>LiRA medio=0.5024798; Yeom medio=0.521343607391918; Shadow medio=0.5159754999999999; LiRA composto=0.507003</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M211" s="4" t="inlineStr">
@@ -16759,7 +16759,7 @@
     <row r="212" ht="90" customHeight="1">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_151044.json</t>
+          <t>local-sweep3/experiment_20260904_212056.json</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -16769,11 +16769,11 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
+          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr">
@@ -16836,7 +16836,7 @@
     <row r="213" ht="90" customHeight="1">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_200759.json</t>
+          <t>local-sweep3/experiment_20260904_231951.json</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -16846,11 +16846,11 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
+          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M213" s="4" t="inlineStr">
@@ -16913,7 +16913,7 @@
     <row r="214" ht="90" customHeight="1">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_220601.json</t>
+          <t>local-sweep3/experiment_20260905_011919.json</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -16923,11 +16923,11 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
+          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M214" s="4" t="inlineStr">
@@ -16990,7 +16990,7 @@
     <row r="215" ht="90" customHeight="1">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260908_000358.json</t>
+          <t>local-sweep3/experiment_20260905_031832.json</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -17000,11 +17000,11 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
+          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
@@ -17067,7 +17067,7 @@
     <row r="216" ht="90" customHeight="1">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_020230.json</t>
+          <t>local-sweep3/experiment_20260905_051744.json</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -17077,11 +17077,11 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I216" s="3" t="inlineStr">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
+          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
         </is>
       </c>
       <c r="K216" s="3" t="inlineStr">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M216" s="4" t="inlineStr">
@@ -17144,7 +17144,7 @@
     <row r="217" ht="90" customHeight="1">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_040043.json</t>
+          <t>local-sweep4/experiment_20260907_131024.json</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -17154,11 +17154,11 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
+          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M217" s="4" t="inlineStr">
@@ -17221,7 +17221,7 @@
     <row r="218" ht="90" customHeight="1">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_055925.json</t>
+          <t>local-sweep4/experiment_20260907_151044.json</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -17231,11 +17231,11 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I218" s="3" t="inlineStr">
@@ -17264,7 +17264,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
+          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M218" s="4" t="inlineStr">
@@ -17298,7 +17298,7 @@
     <row r="219" ht="90" customHeight="1">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_075822.json</t>
+          <t>local-sweep4/experiment_20260907_200759.json</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -17308,11 +17308,11 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I219" s="3" t="inlineStr">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
+          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M219" s="4" t="inlineStr">
@@ -17375,7 +17375,7 @@
     <row r="220" ht="90" customHeight="1">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_100349.json</t>
+          <t>local-sweep4/experiment_20260907_220601.json</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -17385,11 +17385,11 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I220" s="3" t="inlineStr">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
+          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
@@ -17428,7 +17428,7 @@
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M220" s="4" t="inlineStr">
@@ -17452,7 +17452,7 @@
     <row r="221" ht="90" customHeight="1">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_121719.json</t>
+          <t>local-sweep4/experiment_20260908_000358.json</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -17462,11 +17462,11 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -17480,12 +17480,12 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr">
@@ -17495,17 +17495,17 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
+          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
         </is>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M221" s="4" t="inlineStr">
@@ -17529,7 +17529,7 @@
     <row r="222" ht="90" customHeight="1">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_142331.json</t>
+          <t>local-sweep5/experiment_20260908_020230.json</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -17539,11 +17539,11 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -17557,12 +17557,12 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I222" s="3" t="inlineStr">
@@ -17572,17 +17572,17 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001166; Yeom medio=0.4977689383995224; Shadow medio=0.5013555000000001; LiRA composto=0.496078</t>
+          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M222" s="4" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="223" ht="90" customHeight="1">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_162411.json</t>
+          <t>local-sweep5/experiment_20260908_040043.json</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -17616,11 +17616,11 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -17634,12 +17634,12 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr">
@@ -17649,17 +17649,17 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49979699999999994; Yeom medio=0.5012321998500424; Shadow medio=0.5028671; LiRA composto=0.503626</t>
+          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M223" s="4" t="inlineStr">
@@ -17683,7 +17683,7 @@
     <row r="224" ht="90" customHeight="1">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_182356.json</t>
+          <t>local-sweep5/experiment_20260908_055925.json</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -17693,11 +17693,11 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -17711,12 +17711,12 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I224" s="3" t="inlineStr">
@@ -17726,17 +17726,17 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994059999999999; Yeom medio=0.5037555029217773; Shadow medio=0.5027257; LiRA composto=0.498701</t>
+          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
         </is>
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M224" s="4" t="inlineStr">
@@ -17760,7 +17760,7 @@
     <row r="225" ht="90" customHeight="1">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_202354.json</t>
+          <t>local-sweep5/experiment_20260908_075822.json</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -17770,11 +17770,11 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -17788,12 +17788,12 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr">
@@ -17803,17 +17803,17 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007714; Yeom medio=0.5004956024284777; Shadow medio=0.5029101; LiRA composto=0.501679</t>
+          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M225" s="4" t="inlineStr">
@@ -17837,7 +17837,7 @@
     <row r="226" ht="90" customHeight="1">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed123-eps0.5/experiment_20260914_152619.json</t>
+          <t>local-sweep5/experiment_20260908_100349.json</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -17847,11 +17847,11 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
@@ -17865,12 +17865,12 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010704; Yeom medio=0.49885817165752017; Shadow medio=0.49721390000000004; LiRA composto=0.505366</t>
+          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
         </is>
       </c>
       <c r="K226" s="3" t="inlineStr">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed123-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M226" s="4" t="inlineStr">
@@ -17914,7 +17914,7 @@
     <row r="227" ht="90" customHeight="1">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed123/experiment_20260910_172634.json</t>
+          <t>nodp-sweep2/experiment_20260908_121719.json</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -17924,13 +17924,11 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 123: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>42</v>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
@@ -17944,12 +17942,12 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -17959,17 +17957,17 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000368; Yeom medio=0.49981732394504885; Shadow medio=0.49837070000000006; LiRA composto=0.500623</t>
+          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M227" s="4" t="inlineStr">
@@ -17993,7 +17991,7 @@
     <row r="228" ht="90" customHeight="1">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed1234/experiment_20260911_122836.json</t>
+          <t>nodp-sweep2/experiment_20260908_142331.json</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -18003,13 +18001,11 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 1234: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>123</v>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
@@ -18023,12 +18019,12 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I228" s="3" t="inlineStr">
@@ -18038,17 +18034,17 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5012264; Yeom medio=0.5012137493317419; Shadow medio=0.5008147000000001; LiRA composto=0.506321</t>
+          <t>LiRA medio=0.5001166; Yeom medio=0.4977689383995224; Shadow medio=0.5013555000000001; LiRA composto=0.496078</t>
         </is>
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M228" s="4" t="inlineStr">
@@ -18072,7 +18068,7 @@
     <row r="229" ht="90" customHeight="1">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed42-eps0.5/experiment_20260914_130854.json</t>
+          <t>nodp-sweep2/experiment_20260908_162411.json</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -18082,11 +18078,11 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D229" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
@@ -18100,12 +18096,12 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
@@ -18115,17 +18111,17 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994279; Yeom medio=0.49465245749743075; Shadow medio=0.4958531; LiRA composto=0.500887</t>
+          <t>LiRA medio=0.49979699999999994; Yeom medio=0.5012321998500424; Shadow medio=0.5028671; LiRA composto=0.503626</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed42-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M229" s="4" t="inlineStr">
@@ -18149,7 +18145,7 @@
     <row r="230" ht="90" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed456-eps0.5/experiment_20260914_175355.json</t>
+          <t>nodp-sweep2/experiment_20260908_182356.json</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -18159,13 +18155,11 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>789</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
@@ -18179,12 +18173,12 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr">
@@ -18194,17 +18188,17 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5011443; Yeom medio=0.49762605437521107; Shadow medio=0.4992915; LiRA composto=0.504601</t>
+          <t>LiRA medio=0.4994059999999999; Yeom medio=0.5037555029217773; Shadow medio=0.5027257; LiRA composto=0.498701</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed456-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr">
@@ -18228,7 +18222,7 @@
     <row r="231" ht="90" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed456/experiment_20260910_222515.json</t>
+          <t>nodp-sweep2/experiment_20260908_202354.json</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -18238,13 +18232,11 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>1234</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -18258,12 +18250,12 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I231" s="3" t="inlineStr">
@@ -18273,17 +18265,17 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5015437; Yeom medio=0.4976337915896831; Shadow medio=0.5007618; LiRA composto=0.505552</t>
+          <t>LiRA medio=0.5007714; Yeom medio=0.5004956024284777; Shadow medio=0.5029101; LiRA composto=0.501679</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M231" s="4" t="inlineStr">
@@ -18307,7 +18299,7 @@
     <row r="232" ht="90" customHeight="1">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed789-eps0.5/experiment_20260914_205551.json</t>
+          <t>nvflare-central-seed123-eps0.5/experiment_20260914_152619.json</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -18320,10 +18312,8 @@
           <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
-        </is>
+      <c r="D232" s="3" t="n">
+        <v>123</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -18342,7 +18332,7 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr">
@@ -18352,7 +18342,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005679; Yeom medio=0.49992255315113887; Shadow medio=0.4980574; LiRA composto=0.502025</t>
+          <t>LiRA medio=0.5010704; Yeom medio=0.49885817165752017; Shadow medio=0.49721390000000004; LiRA composto=0.505366</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
@@ -18362,7 +18352,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed789-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed123-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr">
@@ -18386,7 +18376,7 @@
     <row r="233" ht="90" customHeight="1">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed789/experiment_20260911_095435.json</t>
+          <t>nvflare-central-seed123/experiment_20260910_172634.json</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -18401,7 +18391,7 @@
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 123: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
@@ -18431,7 +18421,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002807; Yeom medio=0.5002761736218346; Shadow medio=0.49890680000000004; LiRA composto=0.504216</t>
+          <t>LiRA medio=0.5000368; Yeom medio=0.49981732394504885; Shadow medio=0.49837070000000006; LiRA composto=0.500623</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr">
@@ -18441,7 +18431,7 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M233" s="4" t="inlineStr">
@@ -18465,7 +18455,7 @@
     <row r="234" ht="90" customHeight="1">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
+          <t>nvflare-central-seed1234/experiment_20260911_122836.json</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -18475,11 +18465,13 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D234" s="3" t="n">
-        <v>1234</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 1234: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -18493,12 +18485,12 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr">
@@ -18508,7 +18500,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
+          <t>LiRA medio=0.5012264; Yeom medio=0.5012137493317419; Shadow medio=0.5008147000000001; LiRA composto=0.506321</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
@@ -18518,7 +18510,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr">
@@ -18542,7 +18534,7 @@
     <row r="235" ht="90" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
+          <t>nvflare-central-seed42-eps0.5/experiment_20260914_130854.json</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -18552,11 +18544,11 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>1234</v>
+        <v>42</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -18570,12 +18562,12 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr">
@@ -18585,7 +18577,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
+          <t>LiRA medio=0.4994279; Yeom medio=0.49465245749743075; Shadow medio=0.4958531; LiRA composto=0.500887</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
@@ -18595,7 +18587,7 @@
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed42-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M235" s="4" t="inlineStr">
@@ -18619,7 +18611,7 @@
     <row r="236" ht="90" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
+          <t>nvflare-central-seed456-eps0.5/experiment_20260914_175355.json</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -18629,11 +18621,13 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D236" s="3" t="n">
-        <v>123</v>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -18647,12 +18641,12 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I236" s="3" t="inlineStr">
@@ -18662,7 +18656,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
+          <t>LiRA medio=0.5011443; Yeom medio=0.49762605437521107; Shadow medio=0.4992915; LiRA composto=0.504601</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr">
@@ -18672,7 +18666,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed456-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr">
@@ -18696,7 +18690,7 @@
     <row r="237" ht="90" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
+          <t>nvflare-central-seed456/experiment_20260910_222515.json</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -18706,11 +18700,13 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="n">
-        <v>1234</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -18724,7 +18720,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H237" s="3" t="inlineStr">
@@ -18739,7 +18735,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
+          <t>LiRA medio=0.5015437; Yeom medio=0.4976337915896831; Shadow medio=0.5007618; LiRA composto=0.505552</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr">
@@ -18749,7 +18745,7 @@
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M237" s="4" t="inlineStr">
@@ -18773,7 +18769,7 @@
     <row r="238" ht="90" customHeight="1">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
+          <t>nvflare-central-seed789-eps0.5/experiment_20260914_205551.json</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -18783,11 +18779,13 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D238" s="3" t="n">
-        <v>42</v>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
@@ -18801,12 +18799,12 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr">
@@ -18816,7 +18814,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
+          <t>LiRA medio=0.5005679; Yeom medio=0.49992255315113887; Shadow medio=0.4980574; LiRA composto=0.502025</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr">
@@ -18826,7 +18824,7 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed789-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M238" s="4" t="inlineStr">
@@ -18850,7 +18848,7 @@
     <row r="239" ht="90" customHeight="1">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
+          <t>nvflare-central-seed789/experiment_20260911_095435.json</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -18860,11 +18858,13 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="n">
-        <v>456</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
@@ -18893,7 +18893,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
+          <t>LiRA medio=0.5002807; Yeom medio=0.5002761736218346; Shadow medio=0.49890680000000004; LiRA composto=0.504216</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M239" s="4" t="inlineStr">
@@ -18927,7 +18927,7 @@
     <row r="240" ht="90" customHeight="1">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
+          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -18937,11 +18937,11 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>789</v>
+        <v>1234</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
+          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M240" s="4" t="inlineStr">
@@ -19004,7 +19004,7 @@
     <row r="241" ht="90" customHeight="1">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
+          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -19014,11 +19014,11 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
@@ -19032,12 +19032,12 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
+          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
         </is>
       </c>
       <c r="K241" s="3" t="inlineStr">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M241" s="4" t="inlineStr">
@@ -19081,7 +19081,7 @@
     <row r="242" ht="90" customHeight="1">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
+          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -19091,11 +19091,11 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
+          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
         </is>
       </c>
       <c r="K242" s="3" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M242" s="4" t="inlineStr">
@@ -19158,7 +19158,7 @@
     <row r="243" ht="90" customHeight="1">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_183148.json</t>
+          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -19168,11 +19168,11 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
@@ -19186,12 +19186,12 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
+          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
         </is>
       </c>
       <c r="K243" s="3" t="inlineStr">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M243" s="4" t="inlineStr">
@@ -19235,7 +19235,7 @@
     <row r="244" ht="90" customHeight="1">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_203243.json</t>
+          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -19245,11 +19245,11 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -19263,12 +19263,12 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
+          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M244" s="4" t="inlineStr">
@@ -19312,7 +19312,7 @@
     <row r="245" ht="90" customHeight="1">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_223219.json</t>
+          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D245" s="3" t="n">
@@ -19340,12 +19340,12 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
+          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M245" s="4" t="inlineStr">
@@ -19389,7 +19389,7 @@
     <row r="246" ht="90" customHeight="1">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260924_003215.json</t>
+          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -19399,7 +19399,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -19417,12 +19417,12 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I246" s="3" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
+          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
         </is>
       </c>
       <c r="K246" s="3" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M246" s="4" t="inlineStr">
@@ -19466,7 +19466,7 @@
     <row r="247" ht="90" customHeight="1">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260924_023219.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -19476,11 +19476,11 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>1234</v>
+        <v>42</v>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
+          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M247" s="4" t="inlineStr">
@@ -19543,7 +19543,7 @@
     <row r="248" ht="90" customHeight="1">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_134148.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -19553,7 +19553,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
+          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M248" s="4" t="inlineStr">
@@ -19620,7 +19620,7 @@
     <row r="249" ht="90" customHeight="1">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_154640.json</t>
+          <t>rq1-eps16/experiment_20260923_183148.json</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -19630,11 +19630,11 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D249" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
+          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="L249" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M249" s="4" t="inlineStr">
@@ -19697,7 +19697,7 @@
     <row r="250" ht="90" customHeight="1">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_175039.json</t>
+          <t>rq1-eps16/experiment_20260923_203243.json</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -19707,11 +19707,11 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I250" s="3" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
+          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
         </is>
       </c>
       <c r="K250" s="3" t="inlineStr">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M250" s="4" t="inlineStr">
@@ -19774,7 +19774,7 @@
     <row r="251" ht="90" customHeight="1">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_180414.json</t>
+          <t>rq1-eps16/experiment_20260923_223219.json</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -19784,11 +19784,11 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
+          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
         </is>
       </c>
       <c r="K251" s="3" t="inlineStr">
@@ -19827,12 +19827,12 @@
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M251" s="5" t="inlineStr">
-        <is>
-          <t>incompleta</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M251" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="O251" s="3" t="inlineStr">
         <is>
-          <t>nessuna metrica MIA nel JSON</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P251" s="3" t="n"/>
@@ -19851,7 +19851,7 @@
     <row r="252" ht="90" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_200439.json</t>
+          <t>rq1-eps16/experiment_20260924_003215.json</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -19861,11 +19861,11 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I252" s="3" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
+          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
         </is>
       </c>
       <c r="K252" s="3" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M252" s="4" t="inlineStr">
@@ -19928,7 +19928,7 @@
     <row r="253" ht="90" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260924_102430.json</t>
+          <t>rq1-eps16/experiment_20260924_023219.json</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -19938,11 +19938,11 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>789</v>
+        <v>1234</v>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
+          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
         </is>
       </c>
       <c r="K253" s="3" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M253" s="4" t="inlineStr">
@@ -20005,7 +20005,7 @@
     <row r="254" ht="90" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260922_220310.json</t>
+          <t>rq1-eps2/experiment_20260922_134148.json</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -20015,7 +20015,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
+          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M254" s="4" t="inlineStr">
@@ -20082,7 +20082,7 @@
     <row r="255" ht="90" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_000138.json</t>
+          <t>rq1-eps2/experiment_20260922_154640.json</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D255" s="3" t="n">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
+          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M255" s="4" t="inlineStr">
@@ -20159,7 +20159,7 @@
     <row r="256" ht="90" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_020058.json</t>
+          <t>rq1-eps2/experiment_20260922_175039.json</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -20169,7 +20169,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I256" s="3" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
+          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M256" s="4" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="257" ht="90" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_040025.json</t>
+          <t>rq1-eps2/experiment_20260922_180414.json</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D257" s="3" t="n">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
         </is>
       </c>
       <c r="K257" s="3" t="inlineStr">
@@ -20289,12 +20289,12 @@
       </c>
       <c r="L257" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M257" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M257" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -20304,7 +20304,7 @@
       </c>
       <c r="O257" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessuna metrica MIA nel JSON</t>
         </is>
       </c>
       <c r="P257" s="3" t="n"/>
@@ -20313,7 +20313,7 @@
     <row r="258" ht="90" customHeight="1">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_055955.json</t>
+          <t>rq1-eps2/experiment_20260922_200439.json</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -20346,7 +20346,7 @@
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
+          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
         </is>
       </c>
       <c r="K258" s="3" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M258" s="4" t="inlineStr">
@@ -20390,7 +20390,7 @@
     <row r="259" ht="90" customHeight="1">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_080158.json</t>
+          <t>rq1-eps2/experiment_20260924_102430.json</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -20400,11 +20400,11 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
+          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
         </is>
       </c>
       <c r="K259" s="3" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M259" s="4" t="inlineStr">
@@ -20467,7 +20467,7 @@
     <row r="260" ht="90" customHeight="1">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_100736.json</t>
+          <t>rq1-eps4/experiment_20260922_220310.json</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -20477,11 +20477,11 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
+          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr">
@@ -20520,7 +20520,7 @@
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M260" s="4" t="inlineStr">
@@ -20544,7 +20544,7 @@
     <row r="261" ht="90" customHeight="1">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_121447.json</t>
+          <t>rq1-eps4/experiment_20260923_000138.json</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -20554,11 +20554,11 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
+          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
         </is>
       </c>
       <c r="K261" s="3" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M261" s="4" t="inlineStr">
@@ -20621,7 +20621,7 @@
     <row r="262" ht="90" customHeight="1">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_142154.json</t>
+          <t>rq1-eps4/experiment_20260923_020058.json</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -20631,11 +20631,11 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
         </is>
       </c>
       <c r="K262" s="3" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M262" s="4" t="inlineStr">
@@ -20698,7 +20698,7 @@
     <row r="263" ht="90" customHeight="1">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_162834.json</t>
+          <t>rq1-eps4/experiment_20260923_040025.json</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -20708,11 +20708,11 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D263" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
         </is>
       </c>
       <c r="K263" s="3" t="inlineStr">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M263" s="4" t="inlineStr">
@@ -20771,6 +20771,468 @@
       </c>
       <c r="P263" s="3" t="n"/>
       <c r="Q263" s="3" t="n"/>
+    </row>
+    <row r="264" ht="90" customHeight="1">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps4/experiment_20260923_055955.json</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I264" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L264" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M264" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O264" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P264" s="3" t="n"/>
+      <c r="Q264" s="3" t="n"/>
+    </row>
+    <row r="265" ht="90" customHeight="1">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_080158.json</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I265" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J265" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L265" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M265" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O265" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P265" s="3" t="n"/>
+      <c r="Q265" s="3" t="n"/>
+    </row>
+    <row r="266" ht="90" customHeight="1">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_100736.json</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I266" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J266" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M266" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O266" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P266" s="3" t="n"/>
+      <c r="Q266" s="3" t="n"/>
+    </row>
+    <row r="267" ht="90" customHeight="1">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_121447.json</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I267" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M267" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O267" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P267" s="3" t="n"/>
+      <c r="Q267" s="3" t="n"/>
+    </row>
+    <row r="268" ht="90" customHeight="1">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_142154.json</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J268" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M268" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O268" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P268" s="3" t="n"/>
+      <c r="Q268" s="3" t="n"/>
+    </row>
+    <row r="269" ht="90" customHeight="1">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_162834.json</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I269" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J269" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+        </is>
+      </c>
+      <c r="K269" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L269" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M269" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O269" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P269" s="3" t="n"/>
+      <c r="Q269" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q269"/>
+  <dimension ref="A1:Q275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10522,7 +10522,7 @@
     <row r="131" ht="90" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>_op_eps64/experiment_20260924_212917.json</t>
+          <t>_op_eps32/experiment_20260925_234753.json</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=32.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=320.0; eps_avanzata=2.5268147258457984e+16; eps_migliore=320.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49855; Yeom medio=0.4992467157518548; Shadow medio=0.4996785; LiRA composto=0.499981</t>
+          <t>LiRA medio=0.5003711; Yeom medio=0.49913871069720434; Shadow medio=0.5004153; LiRA composto=0.501813</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>logs/op_eps64.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>experiments/_op_eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/_op_eps32/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -10599,7 +10599,7 @@
     <row r="132" ht="90" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>_prova_recorddp/experiment_20260924_144713.json</t>
+          <t>_op_eps64/experiment_20260924_212917.json</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=0.9936577181915225</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -10622,17 +10622,17 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP (diagnostico)</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -10642,22 +10642,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
+          <t>LiRA medio=0.49855; Yeom medio=0.4992467157518548; Shadow medio=0.4996785; LiRA composto=0.499981</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>logs/prova_recorddp_s42_attacchi_saltati.log</t>
+          <t>logs/op_eps64.log</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>experiments/_prova_recorddp/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M132" s="5" t="inlineStr">
-        <is>
-          <t>incompleta</t>
+          <t>experiments/_op_eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>nessuna metrica MIA nel JSON</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P132" s="3" t="n"/>
@@ -10676,17 +10676,17 @@
     <row r="133" ht="90" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>_rdp_balanced_recorddp_fast/experiment_20260917_064655.json</t>
+          <t>_prova_recorddp/experiment_20260924_144713.json</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>CTRL — validazione dello strumento, non una RQ</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=0.9936577181915225</t>
         </is>
       </c>
       <c r="D133" s="3" t="n">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>canary (indotto)</t>
+          <t>naturale — record-DP (diagnostico)</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -10714,27 +10714,27 @@
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3886876666666666; Yeom medio=0.5163276180775616; Shadow medio=0.5461393333333333; LiRA composto=0.35769; canary raw=0.435</t>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/prova_recorddp_s42_attacchi_saltati.log</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_balanced_recorddp_fast/ (JSON + xlsx + history/)</t>
-        </is>
-      </c>
-      <c r="M133" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+          <t>experiments/_prova_recorddp/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
+          <t>nessuna metrica MIA nel JSON</t>
         </is>
       </c>
       <c r="P133" s="3" t="n"/>
@@ -10753,7 +10753,7 @@
     <row r="134" ht="90" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>_rdp_e1000_s5_s42/experiment_20260917_081852.json</t>
+          <t>_rdp_balanced_recorddp_fast/experiment_20260917_064655.json</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -10796,17 +10796,17 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
+          <t>LiRA medio=0.3886876666666666; Yeom medio=0.5163276180775616; Shadow medio=0.5461393333333333; LiRA composto=0.35769; canary raw=0.435</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>logs/rdp_e1000_s5.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_e1000_s5_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_balanced_recorddp_fast/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
@@ -10830,7 +10830,7 @@
     <row r="135" ht="90" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>_rdp_eps163_s42/experiment_20260917_072712.json</t>
+          <t>_rdp_e1000_s5_s42/experiment_20260917_081852.json</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D135" s="3" t="n">
@@ -10873,17 +10873,17 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.38548333333333334; Yeom medio=0.5171245473064735; Shadow medio=0.5352726666666667; LiRA composto=0.297562; canary raw=0.54</t>
+          <t>LiRA medio=0.4357473333333333; Yeom medio=0.5169359250037725; Shadow medio=0.5488696666666666; LiRA composto=0.425689; canary raw=0.49</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/rdp_e1000_s5.log</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_eps163_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_e1000_s5_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
@@ -10907,7 +10907,7 @@
     <row r="136" ht="90" customHeight="1">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>_rdp_eps474_s42/experiment_20260917_072736.json</t>
+          <t>_rdp_eps163_s42/experiment_20260917_072712.json</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4051313333333333; Yeom medio=0.5234622566772296; Shadow medio=0.551126; LiRA composto=0.337742; canary raw=0.56</t>
+          <t>LiRA medio=0.38548333333333334; Yeom medio=0.5171245473064735; Shadow medio=0.5352726666666667; LiRA composto=0.297562; canary raw=0.54</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_eps474_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_eps163_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
@@ -10984,7 +10984,7 @@
     <row r="137" ht="90" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>_rdp_nm005_swap_s42/experiment_20260917_071708.json</t>
+          <t>_rdp_eps474_s42/experiment_20260917_072736.json</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D137" s="3" t="n">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.40725966666666674; Yeom medio=0.5490818809416025; Shadow medio=0.59682; LiRA composto=0.406503; canary raw=0.675</t>
+          <t>LiRA medio=0.4051313333333333; Yeom medio=0.5234622566772296; Shadow medio=0.551126; LiRA composto=0.337742; canary raw=0.56</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_nm005_swap_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_eps474_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="138" ht="90" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>_rdp_recorddp_nm005/experiment_20260917_065335.json</t>
+          <t>_rdp_nm005_swap_s42/experiment_20260917_071708.json</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=True</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3775196666666667; Yeom medio=0.5008205070167496; Shadow medio=0.5375216666666667; LiRA composto=0.343919; canary raw=0.4625</t>
+          <t>LiRA medio=0.40725966666666674; Yeom medio=0.5490818809416025; Shadow medio=0.59682; LiRA composto=0.406503; canary raw=0.675</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_recorddp_nm005/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_nm005_swap_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row r="139" ht="90" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>_rdp_recorddp_nm01/experiment_20260917_065015.json</t>
+          <t>_rdp_recorddp_nm005/experiment_20260917_065335.json</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.3853766666666667; Yeom medio=0.48447874226648563; Shadow medio=0.5364559999999999; LiRA composto=0.355141; canary raw=0.4675</t>
+          <t>LiRA medio=0.3775196666666667; Yeom medio=0.5008205070167496; Shadow medio=0.5375216666666667; LiRA composto=0.343919; canary raw=0.4625</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_recorddp_nm01/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_recorddp_nm005/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="140" ht="90" customHeight="1">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>_rdp_ref_e10_s42/experiment_20260917_072648.json</t>
+          <t>_rdp_recorddp_nm01/experiment_20260917_065015.json</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=100; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.611027; Yeom medio=0.49774360570393844; Shadow medio=0.525556; LiRA composto=0.669276; canary raw=0.4925</t>
+          <t>LiRA medio=0.3853766666666667; Yeom medio=0.48447874226648563; Shadow medio=0.5364559999999999; LiRA composto=0.355141; canary raw=0.4675</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>experiments/_rdp_ref_e10_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_recorddp_nm01/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -11292,7 +11292,7 @@
     <row r="141" ht="90" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>_ref_e1000_group_s42/experiment_20260917_073820.json</t>
+          <t>_rdp_ref_e10_s42/experiment_20260917_072648.json</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=10; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D141" s="3" t="n">
@@ -11335,17 +11335,17 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
+          <t>LiRA medio=0.611027; Yeom medio=0.49774360570393844; Shadow medio=0.525556; LiRA composto=0.669276; canary raw=0.4925</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>logs/ref_e1000_group.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>experiments/_ref_e1000_group_s42/ (JSON + xlsx + history/)</t>
+          <t>experiments/_rdp_ref_e10_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
@@ -11369,17 +11369,17 @@
     <row r="142" ht="90" customHeight="1">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_135401.json</t>
+          <t>_ref_e1000_group_s42/experiment_20260917_073820.json</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>RQ1</t>
+          <t>CTRL — validazione dello strumento, non una RQ</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=1000; batch=None; feature=7; hidden=[32, 16]; latent=8; canary k=20/20, dup=30, swap=False</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>canary (indotto)</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -11407,22 +11407,22 @@
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.5784996666666666; Yeom medio=0.6094622378149993; Shadow medio=0.48618100000000003; LiRA composto=0.577269; canary raw=0.705</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/ref_e1000_group.log</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
+          <t>experiments/_ref_e1000_group_s42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>cella di ablation post-fix: il dato e' pulito ma non e' stato sottoposto alla stessa verifica numerica della campagna principale</t>
         </is>
       </c>
       <c r="P142" s="3" t="n"/>
@@ -11446,7 +11446,7 @@
     <row r="143" ht="90" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_151156.json</t>
+          <t>_robustness_entity_split/experiment_20260831_135401.json</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -11523,7 +11523,7 @@
     <row r="144" ht="90" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>_robustness_entity_split/experiment_20260831_181649.json</t>
+          <t>_robustness_entity_split/experiment_20260831_151156.json</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -11600,7 +11600,7 @@
     <row r="145" ht="90" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>_smoke_centralized_control/experiment_20260901_141640.json</t>
+          <t>_robustness_entity_split/experiment_20260831_181649.json</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
@@ -11638,12 +11638,12 @@
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>2 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_centralized_control/ (JSON + xlsx + history/)</t>
+          <t>experiments/_robustness_entity_split/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
@@ -11677,7 +11677,7 @@
     <row r="146" ht="90" customHeight="1">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260901_141146.json</t>
+          <t>_smoke_centralized_control/experiment_20260901_141640.json</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_centralized_control/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr">
@@ -11754,7 +11754,7 @@
     <row r="147" ht="90" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260901_191839.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260901_141146.json</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4969305; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.497248</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
@@ -11831,7 +11831,7 @@
     <row r="148" ht="90" customHeight="1">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260902_062136.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260901_191839.json</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="149" ht="90" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient/experiment_20260902_131018.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260902_062136.json</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -11985,7 +11985,7 @@
     <row r="150" ht="90" customHeight="1">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_n16/experiment_20260901_143530.json</t>
+          <t>_smoke_fedmia_gradient/experiment_20260902_131018.json</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_n16/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -12062,7 +12062,7 @@
     <row r="151" ht="90" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_n16_v2/experiment_20260901_150314.json</t>
+          <t>_smoke_fedmia_gradient_n16/experiment_20260901_143530.json</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_n16_v2/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_n16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="152" ht="90" customHeight="1">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>_smoke_fedmia_gradient_normalized/experiment_20260902_140132.json</t>
+          <t>_smoke_fedmia_gradient_n16_v2/experiment_20260901_150314.json</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.502705</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_fedmia_gradient_normalized/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_n16_v2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
@@ -12216,7 +12216,7 @@
     <row r="153" ht="90" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>_smoke_sb2_dp-fedavg/experiment_20260917_210602.json</t>
+          <t>_smoke_fedmia_gradient_normalized/experiment_20260902_140132.json</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=2; epoche=10; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D153" s="3" t="n">
@@ -12244,22 +12244,22 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>1 round valutati</t>
+          <t>2 round valutati</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.494587; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.494587</t>
+          <t>LiRA medio=0.5007545; Yeom medio=0.498890614036518; Shadow medio=0.498757; LiRA composto=0.500062</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_sb2_dp-fedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_fedmia_gradient_normalized/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -12293,7 +12293,7 @@
     <row r="154" ht="90" customHeight="1">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>_smoke_sb2_local/experiment_20260917_210627.json</t>
+          <t>_smoke_sb2_dp-fedavg/experiment_20260917_210602.json</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.491745; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.491745</t>
+          <t>LiRA medio=0.494587; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.494587</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_sb2_local/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_sb2_dp-fedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
@@ -12370,7 +12370,7 @@
     <row r="155" ht="90" customHeight="1">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>_smoke_stradaB_dp-fedavg/experiment_20260917_205626.json</t>
+          <t>_smoke_sb2_local/experiment_20260917_210627.json</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=2; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D155" s="3" t="n">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.499264; Yeom medio=0.4981025148508319; Shadow medio=0.497864; LiRA composto=0.499264</t>
+          <t>LiRA medio=0.491745; Yeom medio=0.4977973006967835; Shadow medio=0.49847; LiRA composto=0.491745</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>experiments/_smoke_stradaB_dp-fedavg/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_sb2_local/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
@@ -12447,7 +12447,7 @@
     <row r="156" ht="90" customHeight="1">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>_verify_10rounds_central/experiment_20260826_150039.json</t>
+          <t>_smoke_stradaB_dp-fedavg/experiment_20260917_205626.json</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=1; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -12475,22 +12475,22 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=6.516807740647126; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>1 round valutati</t>
         </is>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013407; Yeom medio=0.49943881126863526; Shadow medio=0.49939399999999995; LiRA composto=0.501579</t>
+          <t>LiRA medio=0.499264; Yeom medio=0.4981025148508319; Shadow medio=0.497864; LiRA composto=0.499264</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_10rounds_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_smoke_stradaB_dp-fedavg/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="157" ht="90" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>_verify_10rounds_nodp/experiment_20260826_121351.json</t>
+          <t>_verify_10rounds_central/experiment_20260826_150039.json</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D157" s="3" t="n">
@@ -12552,12 +12552,12 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
+          <t>LiRA medio=0.5013407; Yeom medio=0.49943881126863526; Shadow medio=0.49939399999999995; LiRA composto=0.501579</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_10rounds_nodp/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_10rounds_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -12601,7 +12601,7 @@
     <row r="158" ht="90" customHeight="1">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>_verify_mu_anchor/experiment_20260821_045041.json</t>
+          <t>_verify_10rounds_nodp/experiment_20260826_121351.json</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>3 round valutati</t>
+          <t>10 round valutati</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
+          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
         </is>
       </c>
       <c r="K158" s="3" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_mu_anchor/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_10rounds_nodp/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
@@ -12678,7 +12678,7 @@
     <row r="159" ht="90" customHeight="1">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>_verify_outlier_fix/experiment_20260821_030556.json</t>
+          <t>_verify_mu_anchor/experiment_20260821_045041.json</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.436568; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.30242</t>
+          <t>LiRA medio=0.7247979999999999; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.818711</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_outlier_fix/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_mu_anchor/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
@@ -12755,7 +12755,7 @@
     <row r="160" ht="90" customHeight="1">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>_verify_shadow_universe_central/experiment_20260825_142623.json</t>
+          <t>_verify_outlier_fix/experiment_20260821_030556.json</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -12783,12 +12783,12 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.501707; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.500864</t>
+          <t>LiRA medio=0.436568; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.30242</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_shadow_universe_central/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_outlier_fix/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
@@ -12832,7 +12832,7 @@
     <row r="161" ht="90" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>_verify_shadow_universe_nodp/experiment_20260825_123128.json</t>
+          <t>_verify_shadow_universe_central/experiment_20260825_142623.json</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D161" s="3" t="n">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=3.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.502457; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.498992</t>
+          <t>LiRA medio=0.501707; Yeom medio=0.49826814460063557; Shadow medio=0.497678; LiRA composto=0.500864</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="L161" s="3" t="inlineStr">
         <is>
-          <t>experiments/_verify_shadow_universe_nodp/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_shadow_universe_central/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="162" ht="90" customHeight="1">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_101722.json</t>
+          <t>_verify_shadow_universe_nodp/experiment_20260825_123128.json</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=3; epoche=None; batch=None; feature=n.d.; hidden=None; latent=None</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -12937,22 +12937,22 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>10 round valutati</t>
+          <t>3 round valutati</t>
         </is>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005919; Yeom medio=0.49896493538774356; Shadow medio=0.49793459999999995; LiRA composto=0.50205</t>
+          <t>LiRA medio=0.502457; Yeom medio=0.4974027411405304; Shadow medio=0.496322; LiRA composto=0.498992</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/_verify_shadow_universe_nodp/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -12986,7 +12986,7 @@
     <row r="163" ht="90" customHeight="1">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_132410.json</t>
+          <t>central-sweep5/experiment_20260904_101722.json</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -13000,7 +13000,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007217; Yeom medio=0.4973242024691359; Shadow medio=0.49804750000000003; LiRA composto=0.5011</t>
+          <t>LiRA medio=0.5005919; Yeom medio=0.49896493538774356; Shadow medio=0.49793459999999995; LiRA composto=0.50205</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <row r="164" ht="90" customHeight="1">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_152449.json</t>
+          <t>central-sweep5/experiment_20260904_132410.json</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -13077,7 +13077,7 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003599999999999; Yeom medio=0.500791060952068; Shadow medio=0.5014752; LiRA composto=0.503782</t>
+          <t>LiRA medio=0.5007217; Yeom medio=0.4973242024691359; Shadow medio=0.49804750000000003; LiRA composto=0.5011</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
@@ -13140,7 +13140,7 @@
     <row r="165" ht="90" customHeight="1">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_172351.json</t>
+          <t>central-sweep5/experiment_20260904_152449.json</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49905990000000006; Yeom medio=0.500571496779277; Shadow medio=0.500362; LiRA composto=0.495431</t>
+          <t>LiRA medio=0.5003599999999999; Yeom medio=0.500791060952068; Shadow medio=0.5014752; LiRA composto=0.503782</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="166" ht="90" customHeight="1">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>central-sweep5/experiment_20260904_192220.json</t>
+          <t>central-sweep5/experiment_20260904_172351.json</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -13231,7 +13231,7 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987811; Yeom medio=0.5031364589234597; Shadow medio=0.5001119; LiRA composto=0.498958</t>
+          <t>LiRA medio=0.49905990000000006; Yeom medio=0.500571496779277; Shadow medio=0.500362; LiRA composto=0.495431</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="167" ht="90" customHeight="1">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_125850.json</t>
+          <t>central-sweep5/experiment_20260904_192220.json</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -13304,11 +13304,11 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5011854000000001; Yeom medio=0.49965422177892016; Shadow medio=0.4990378000000001; LiRA composto=0.502787</t>
+          <t>LiRA medio=0.4987811; Yeom medio=0.5031364589234597; Shadow medio=0.5001119; LiRA composto=0.498958</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M167" s="4" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="168" ht="90" customHeight="1">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_191408.json</t>
+          <t>central-sweep6/experiment_20260906_125850.json</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009991000000001; Yeom medio=0.4972590761864777; Shadow medio=0.4984662999999999; LiRA composto=0.505951</t>
+          <t>LiRA medio=0.5011854000000001; Yeom medio=0.49965422177892016; Shadow medio=0.4990378000000001; LiRA composto=0.502787</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
@@ -13448,7 +13448,7 @@
     <row r="169" ht="90" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_211234.json</t>
+          <t>central-sweep6/experiment_20260906_191408.json</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4992345; Yeom medio=0.500988430412608; Shadow medio=0.5016581; LiRA composto=0.496234</t>
+          <t>LiRA medio=0.5009991000000001; Yeom medio=0.4972590761864777; Shadow medio=0.4984662999999999; LiRA composto=0.505951</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr">
@@ -13525,7 +13525,7 @@
     <row r="170" ht="90" customHeight="1">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260906_231027.json</t>
+          <t>central-sweep6/experiment_20260906_211234.json</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5017716000000001; Yeom medio=0.5013164942039221; Shadow medio=0.5005728; LiRA composto=0.50808</t>
+          <t>LiRA medio=0.4992345; Yeom medio=0.500988430412608; Shadow medio=0.5016581; LiRA composto=0.496234</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
@@ -13602,7 +13602,7 @@
     <row r="171" ht="90" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>central-sweep6/experiment_20260907_010817.json</t>
+          <t>central-sweep6/experiment_20260906_231027.json</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49917149999999993; Yeom medio=0.5037495900610333; Shadow medio=0.500691; LiRA composto=0.49906</t>
+          <t>LiRA medio=0.5017716000000001; Yeom medio=0.5013164942039221; Shadow medio=0.5005728; LiRA composto=0.50808</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr">
@@ -13679,7 +13679,7 @@
     <row r="172" ht="90" customHeight="1">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_030628.json</t>
+          <t>central-sweep6/experiment_20260907_010817.json</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -13689,11 +13689,11 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49977089999999996; Yeom medio=0.49805428686925496; Shadow medio=0.49676210000000004; LiRA composto=0.498855</t>
+          <t>LiRA medio=0.49917149999999993; Yeom medio=0.5037495900610333; Shadow medio=0.500691; LiRA composto=0.49906</t>
         </is>
       </c>
       <c r="K172" s="3" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
@@ -13756,7 +13756,7 @@
     <row r="173" ht="90" customHeight="1">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_050525.json</t>
+          <t>central-sweep7/experiment_20260907_030628.json</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -13770,7 +13770,7 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996276; Yeom medio=0.4971502873000452; Shadow medio=0.49816270000000007; LiRA composto=0.50023</t>
+          <t>LiRA medio=0.49977089999999996; Yeom medio=0.49805428686925496; Shadow medio=0.49676210000000004; LiRA composto=0.498855</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr">
@@ -13833,7 +13833,7 @@
     <row r="174" ht="90" customHeight="1">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_070400.json</t>
+          <t>central-sweep7/experiment_20260907_050525.json</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -13847,7 +13847,7 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002849; Yeom medio=0.5002013692212844; Shadow medio=0.4996085; LiRA composto=0.503648</t>
+          <t>LiRA medio=0.4996276; Yeom medio=0.4971502873000452; Shadow medio=0.49816270000000007; LiRA composto=0.50023</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
@@ -13910,7 +13910,7 @@
     <row r="175" ht="90" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_090208.json</t>
+          <t>central-sweep7/experiment_20260907_070400.json</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006189; Yeom medio=0.5009834468601285; Shadow medio=0.5005473; LiRA composto=0.502658</t>
+          <t>LiRA medio=0.5002849; Yeom medio=0.5002013692212844; Shadow medio=0.4996085; LiRA composto=0.503648</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
@@ -13987,7 +13987,7 @@
     <row r="176" ht="90" customHeight="1">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>central-sweep7/experiment_20260907_110100.json</t>
+          <t>central-sweep7/experiment_20260907_090208.json</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5020007000000001; Yeom medio=0.5036042090648936; Shadow medio=0.5011106; LiRA composto=0.50446</t>
+          <t>LiRA medio=0.5006189; Yeom medio=0.5009834468601285; Shadow medio=0.5005473; LiRA composto=0.502658</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr">
@@ -14064,7 +14064,7 @@
     <row r="177" ht="90" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_071625.json</t>
+          <t>central-sweep7/experiment_20260907_110100.json</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -14074,11 +14074,11 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -14092,12 +14092,12 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
+          <t>LiRA medio=0.5020007000000001; Yeom medio=0.5036042090648936; Shadow medio=0.5011106; LiRA composto=0.50446</t>
         </is>
       </c>
       <c r="K177" s="3" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/central-sweep7/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
@@ -14141,7 +14141,7 @@
     <row r="178" ht="90" customHeight="1">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_091555.json</t>
+          <t>dp-sweep4/experiment_20260905_071625.json</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
+          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
         </is>
       </c>
       <c r="K178" s="3" t="inlineStr">
@@ -14218,7 +14218,7 @@
     <row r="179" ht="90" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_111424.json</t>
+          <t>dp-sweep4/experiment_20260905_091555.json</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -14232,7 +14232,7 @@
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
+          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
         </is>
       </c>
       <c r="K179" s="3" t="inlineStr">
@@ -14295,7 +14295,7 @@
     <row r="180" ht="90" customHeight="1">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_131307.json</t>
+          <t>dp-sweep4/experiment_20260905_111424.json</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -14309,7 +14309,7 @@
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
+          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
         </is>
       </c>
       <c r="K180" s="3" t="inlineStr">
@@ -14372,7 +14372,7 @@
     <row r="181" ht="90" customHeight="1">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep4/experiment_20260905_151128.json</t>
+          <t>dp-sweep4/experiment_20260905_131307.json</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -14386,7 +14386,7 @@
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
+          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr">
@@ -14449,7 +14449,7 @@
     <row r="182" ht="90" customHeight="1">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_171005.json</t>
+          <t>dp-sweep4/experiment_20260905_151128.json</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -14459,11 +14459,11 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
+          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
         </is>
       </c>
       <c r="K182" s="3" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
@@ -14526,7 +14526,7 @@
     <row r="183" ht="90" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_190905.json</t>
+          <t>dp-sweep5/experiment_20260905_171005.json</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -14540,7 +14540,7 @@
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
+          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr">
@@ -14603,7 +14603,7 @@
     <row r="184" ht="90" customHeight="1">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_210838.json</t>
+          <t>dp-sweep5/experiment_20260905_190905.json</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -14617,7 +14617,7 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
+          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="185" ht="90" customHeight="1">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260905_230738.json</t>
+          <t>dp-sweep5/experiment_20260905_210838.json</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
+          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
@@ -14757,7 +14757,7 @@
     <row r="186" ht="90" customHeight="1">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep5/experiment_20260906_010556.json</t>
+          <t>dp-sweep5/experiment_20260905_230738.json</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
+          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
         </is>
       </c>
       <c r="K186" s="3" t="inlineStr">
@@ -14834,7 +14834,7 @@
     <row r="187" ht="90" customHeight="1">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_030425.json</t>
+          <t>dp-sweep5/experiment_20260906_010556.json</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -14844,11 +14844,11 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
+          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
         </is>
       </c>
       <c r="K187" s="3" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
@@ -14911,7 +14911,7 @@
     <row r="188" ht="90" customHeight="1">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_050301.json</t>
+          <t>dp-sweep6/experiment_20260906_030425.json</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -14925,7 +14925,7 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
+          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
         </is>
       </c>
       <c r="K188" s="3" t="inlineStr">
@@ -14988,7 +14988,7 @@
     <row r="189" ht="90" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_070124.json</t>
+          <t>dp-sweep6/experiment_20260906_050301.json</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
+          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
@@ -15065,7 +15065,7 @@
     <row r="190" ht="90" customHeight="1">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_090022.json</t>
+          <t>dp-sweep6/experiment_20260906_070124.json</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
+          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr">
@@ -15142,7 +15142,7 @@
     <row r="191" ht="90" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>dp-sweep6/experiment_20260906_105941.json</t>
+          <t>dp-sweep6/experiment_20260906_090022.json</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
+          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
@@ -15219,7 +15219,7 @@
     <row r="192" ht="90" customHeight="1">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260917_230655.json</t>
+          <t>dp-sweep6/experiment_20260906_105941.json</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -15229,11 +15229,11 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.498673; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.497625</t>
+          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dp-sweep6/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
@@ -15296,7 +15296,7 @@
     <row r="193" ht="90" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_010547.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260917_230655.json</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -15310,7 +15310,7 @@
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5008796; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.499315</t>
+          <t>LiRA medio=0.498673; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.497625</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
@@ -15373,7 +15373,7 @@
     <row r="194" ht="90" customHeight="1">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_030414.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_010547.json</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -15387,7 +15387,7 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49872580000000005; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498937</t>
+          <t>LiRA medio=0.5008796; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.499315</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
@@ -15450,7 +15450,7 @@
     <row r="195" ht="90" customHeight="1">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_050226.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_030414.json</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991087; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.4982</t>
+          <t>LiRA medio=0.49872580000000005; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498937</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
@@ -15527,7 +15527,7 @@
     <row r="196" ht="90" customHeight="1">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_070126.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_050226.json</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -15541,7 +15541,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5012004000000001; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.503942</t>
+          <t>LiRA medio=0.4991087; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.4982</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
@@ -15604,7 +15604,7 @@
     <row r="197" ht="90" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_090012.json</t>
+          <t>dpfedavg-stradaB-eps0.1/experiment_20260918_070126.json</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -15614,11 +15614,11 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991078; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.497224</t>
+          <t>LiRA medio=0.5012004000000001; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.503942</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
@@ -15681,7 +15681,7 @@
     <row r="198" ht="90" customHeight="1">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_110316.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_090012.json</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -15695,7 +15695,7 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49917960000000006; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.494169</t>
+          <t>LiRA medio=0.4991078; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.497224</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
@@ -15758,7 +15758,7 @@
     <row r="199" ht="90" customHeight="1">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_130646.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_110316.json</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -15772,7 +15772,7 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49895890000000004; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.49704</t>
+          <t>LiRA medio=0.49917960000000006; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.494169</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr">
@@ -15835,7 +15835,7 @@
     <row r="200" ht="90" customHeight="1">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_152053.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_130646.json</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -15849,7 +15849,7 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987621; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.49875</t>
+          <t>LiRA medio=0.49895890000000004; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.49704</t>
         </is>
       </c>
       <c r="K200" s="3" t="inlineStr">
@@ -15912,7 +15912,7 @@
     <row r="201" ht="90" customHeight="1">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_172416.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_152053.json</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500696; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.503045</t>
+          <t>LiRA medio=0.4987621; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.49875</t>
         </is>
       </c>
       <c r="K201" s="3" t="inlineStr">
@@ -15989,7 +15989,7 @@
     <row r="202" ht="90" customHeight="1">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_192336.json</t>
+          <t>dpfedavg-stradaB-eps0.5/experiment_20260918_172416.json</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -15999,11 +15999,11 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4981084; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.496392</t>
+          <t>LiRA medio=0.500696; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.503045</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M202" s="4" t="inlineStr">
@@ -16066,7 +16066,7 @@
     <row r="203" ht="90" customHeight="1">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_212202.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_192336.json</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991732000000001; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.494029</t>
+          <t>LiRA medio=0.4981084; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.496392</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr">
@@ -16143,7 +16143,7 @@
     <row r="204" ht="90" customHeight="1">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_232046.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_212202.json</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933639999999996; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.497262</t>
+          <t>LiRA medio=0.4991732000000001; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.494029</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
@@ -16220,7 +16220,7 @@
     <row r="205" ht="90" customHeight="1">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_011840.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260918_232046.json</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -16234,7 +16234,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991316; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.497253</t>
+          <t>LiRA medio=0.49933639999999996; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.497262</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
@@ -16297,7 +16297,7 @@
     <row r="206" ht="90" customHeight="1">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_031737.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_011840.json</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002686000000001; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.500625</t>
+          <t>LiRA medio=0.4991316; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.497253</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="207" ht="90" customHeight="1">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260831_184338.json</t>
+          <t>dpfedavg-stradaB-eps1.0/experiment_20260919_031737.json</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -16384,11 +16384,11 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -16402,12 +16402,12 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=32.357089578441915; eps_migliore=10.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
+          <t>LiRA medio=0.5002686000000001; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.500625</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
+          <t>experiments/dpfedavg-stradaB-eps1.0/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M207" s="4" t="inlineStr">
@@ -16451,7 +16451,7 @@
     <row r="208" ht="90" customHeight="1">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260831_213159.json</t>
+          <t>entity-split-sweep1/experiment_20260831_184338.json</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009480999999999; Yeom medio=0.497243057057373; Shadow medio=0.5001202; LiRA composto=0.501827</t>
+          <t>LiRA medio=0.49978059999999996; Yeom medio=0.49893680009216573; Shadow medio=0.5002679; LiRA composto=0.498261</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
@@ -16528,7 +16528,7 @@
     <row r="209" ht="90" customHeight="1">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_071856.json</t>
+          <t>entity-split-sweep1/experiment_20260831_213159.json</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -16542,7 +16542,7 @@
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000713999999999; Yeom medio=0.4869039249495624; Shadow medio=0.4864776; LiRA composto=0.500347</t>
+          <t>LiRA medio=0.5009480999999999; Yeom medio=0.497243057057373; Shadow medio=0.5001202; LiRA composto=0.501827</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr">
@@ -16605,7 +16605,7 @@
     <row r="210" ht="90" customHeight="1">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_093057.json</t>
+          <t>entity-split-sweep1/experiment_20260901_071856.json</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -16619,7 +16619,7 @@
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5044566; Yeom medio=0.5396062512497303; Shadow medio=0.5344805; LiRA composto=0.509723</t>
+          <t>LiRA medio=0.5000713999999999; Yeom medio=0.4869039249495624; Shadow medio=0.4864776; LiRA composto=0.500347</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
@@ -16682,7 +16682,7 @@
     <row r="211" ht="90" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>entity-split-sweep1/experiment_20260901_113947.json</t>
+          <t>entity-split-sweep1/experiment_20260901_093057.json</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -16696,7 +16696,7 @@
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5024798; Yeom medio=0.521343607391918; Shadow medio=0.5159754999999999; LiRA composto=0.507003</t>
+          <t>LiRA medio=0.5044566; Yeom medio=0.5396062512497303; Shadow medio=0.5344805; LiRA composto=0.509723</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr">
@@ -16759,7 +16759,7 @@
     <row r="212" ht="90" customHeight="1">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260904_212056.json</t>
+          <t>entity-split-sweep1/experiment_20260901_113947.json</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -16769,11 +16769,11 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -16787,12 +16787,12 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
+          <t>LiRA medio=0.5024798; Yeom medio=0.521343607391918; Shadow medio=0.5159754999999999; LiRA composto=0.507003</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
+          <t>experiments/entity-split-sweep1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr">
@@ -16836,7 +16836,7 @@
     <row r="213" ht="90" customHeight="1">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260904_231951.json</t>
+          <t>local-sweep3/experiment_20260904_212056.json</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -16850,7 +16850,7 @@
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
+          <t>LiRA medio=0.5009166; Yeom medio=0.498959138515006; Shadow medio=0.4964105; LiRA composto=0.500388</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
@@ -16913,7 +16913,7 @@
     <row r="214" ht="90" customHeight="1">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_011919.json</t>
+          <t>local-sweep3/experiment_20260904_231951.json</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -16927,7 +16927,7 @@
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
+          <t>LiRA medio=0.49971329999999997; Yeom medio=0.4948573563488961; Shadow medio=0.4985628999999999; LiRA composto=0.492814</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr">
@@ -16990,7 +16990,7 @@
     <row r="215" ht="90" customHeight="1">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_031832.json</t>
+          <t>local-sweep3/experiment_20260905_011919.json</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -17004,7 +17004,7 @@
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
+          <t>LiRA medio=0.4983899; Yeom medio=0.5011648636167243; Shadow medio=0.5007532; LiRA composto=0.494558</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">
@@ -17067,7 +17067,7 @@
     <row r="216" ht="90" customHeight="1">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>local-sweep3/experiment_20260905_051744.json</t>
+          <t>local-sweep3/experiment_20260905_031832.json</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -17081,7 +17081,7 @@
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
+          <t>LiRA medio=0.4994991; Yeom medio=0.5015888084863274; Shadow medio=0.5008338; LiRA composto=0.499552</t>
         </is>
       </c>
       <c r="K216" s="3" t="inlineStr">
@@ -17144,7 +17144,7 @@
     <row r="217" ht="90" customHeight="1">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_131024.json</t>
+          <t>local-sweep3/experiment_20260905_051744.json</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -17154,11 +17154,11 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
+          <t>LiRA medio=0.49877200000000005; Yeom medio=0.5025192471424641; Shadow medio=0.4999583; LiRA composto=0.500251</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep3/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M217" s="4" t="inlineStr">
@@ -17221,7 +17221,7 @@
     <row r="218" ht="90" customHeight="1">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_151044.json</t>
+          <t>local-sweep4/experiment_20260907_131024.json</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -17235,7 +17235,7 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
+          <t>LiRA medio=0.5001675; Yeom medio=0.49923290250707036; Shadow medio=0.497507; LiRA composto=0.500565</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr">
@@ -17298,7 +17298,7 @@
     <row r="219" ht="90" customHeight="1">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_200759.json</t>
+          <t>local-sweep4/experiment_20260907_151044.json</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
+          <t>LiRA medio=0.5003084; Yeom medio=0.49627904661947786; Shadow medio=0.499372; LiRA composto=0.495048</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
@@ -17375,7 +17375,7 @@
     <row r="220" ht="90" customHeight="1">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260907_220601.json</t>
+          <t>local-sweep4/experiment_20260907_200759.json</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -17389,7 +17389,7 @@
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
+          <t>LiRA medio=0.4996353; Yeom medio=0.5009445967756716; Shadow medio=0.5009916000000001; LiRA composto=0.498551</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
@@ -17452,7 +17452,7 @@
     <row r="221" ht="90" customHeight="1">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>local-sweep4/experiment_20260908_000358.json</t>
+          <t>local-sweep4/experiment_20260907_220601.json</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
+          <t>LiRA medio=0.4993415; Yeom medio=0.5020590008352765; Shadow medio=0.5021119; LiRA composto=0.494031</t>
         </is>
       </c>
       <c r="K221" s="3" t="inlineStr">
@@ -17529,7 +17529,7 @@
     <row r="222" ht="90" customHeight="1">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_020230.json</t>
+          <t>local-sweep4/experiment_20260908_000358.json</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -17539,11 +17539,11 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I222" s="3" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
+          <t>LiRA medio=0.5003461; Yeom medio=0.5022906676403893; Shadow medio=0.4998901; LiRA composto=0.503429</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M222" s="4" t="inlineStr">
@@ -17606,7 +17606,7 @@
     <row r="223" ht="90" customHeight="1">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_040043.json</t>
+          <t>local-sweep5/experiment_20260908_020230.json</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -17620,7 +17620,7 @@
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
+          <t>LiRA medio=0.5013113; Yeom medio=0.49887861868608124; Shadow medio=0.49631040000000004; LiRA composto=0.501067</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr">
@@ -17683,7 +17683,7 @@
     <row r="224" ht="90" customHeight="1">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_055925.json</t>
+          <t>local-sweep5/experiment_20260908_040043.json</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -17697,7 +17697,7 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
+          <t>LiRA medio=0.5002125000000001; Yeom medio=0.4952805954609686; Shadow medio=0.49882970000000004; LiRA composto=0.493113</t>
         </is>
       </c>
       <c r="K224" s="3" t="inlineStr">
@@ -17760,7 +17760,7 @@
     <row r="225" ht="90" customHeight="1">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_075822.json</t>
+          <t>local-sweep5/experiment_20260908_055925.json</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -17774,7 +17774,7 @@
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
+          <t>LiRA medio=0.49929949999999995; Yeom medio=0.501020778428482; Shadow medio=0.5011772999999999; LiRA composto=0.498752</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr">
@@ -17837,7 +17837,7 @@
     <row r="226" ht="90" customHeight="1">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>local-sweep5/experiment_20260908_100349.json</t>
+          <t>local-sweep5/experiment_20260908_075822.json</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -17851,7 +17851,7 @@
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
+          <t>LiRA medio=0.4998771999999999; Yeom medio=0.500165694905294; Shadow medio=0.5007746; LiRA composto=0.503339</t>
         </is>
       </c>
       <c r="K226" s="3" t="inlineStr">
@@ -17914,7 +17914,7 @@
     <row r="227" ht="90" customHeight="1">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_121719.json</t>
+          <t>local-sweep5/experiment_20260908_100349.json</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -17924,11 +17924,11 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
@@ -17942,12 +17942,12 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -17957,17 +17957,17 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
+          <t>LiRA medio=0.4988395; Yeom medio=0.5022099385837047; Shadow medio=0.49971509999999997; LiRA composto=0.496486</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>logs/nodp-sweep.log</t>
+          <t>nessun log associabile per nome</t>
         </is>
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
+          <t>experiments/local-sweep5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M227" s="4" t="inlineStr">
@@ -17991,7 +17991,7 @@
     <row r="228" ht="90" customHeight="1">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_142331.json</t>
+          <t>nodp-sweep2/experiment_20260908_121719.json</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001166; Yeom medio=0.4977689383995224; Shadow medio=0.5013555000000001; LiRA composto=0.496078</t>
+          <t>LiRA medio=0.5014166; Yeom medio=0.4980563134296772; Shadow medio=0.4981477999999999; LiRA composto=0.501751</t>
         </is>
       </c>
       <c r="K228" s="3" t="inlineStr">
@@ -18068,7 +18068,7 @@
     <row r="229" ht="90" customHeight="1">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_162411.json</t>
+          <t>nodp-sweep2/experiment_20260908_142331.json</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -18082,7 +18082,7 @@
         </is>
       </c>
       <c r="D229" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49979699999999994; Yeom medio=0.5012321998500424; Shadow medio=0.5028671; LiRA composto=0.503626</t>
+          <t>LiRA medio=0.5001166; Yeom medio=0.4977689383995224; Shadow medio=0.5013555000000001; LiRA composto=0.496078</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr">
@@ -18145,7 +18145,7 @@
     <row r="230" ht="90" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_182356.json</t>
+          <t>nodp-sweep2/experiment_20260908_162411.json</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994059999999999; Yeom medio=0.5037555029217773; Shadow medio=0.5027257; LiRA composto=0.498701</t>
+          <t>LiRA medio=0.49979699999999994; Yeom medio=0.5012321998500424; Shadow medio=0.5028671; LiRA composto=0.503626</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
@@ -18222,7 +18222,7 @@
     <row r="231" ht="90" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>nodp-sweep2/experiment_20260908_202354.json</t>
+          <t>nodp-sweep2/experiment_20260908_182356.json</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -18236,7 +18236,7 @@
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007714; Yeom medio=0.5004956024284777; Shadow medio=0.5029101; LiRA composto=0.501679</t>
+          <t>LiRA medio=0.4994059999999999; Yeom medio=0.5037555029217773; Shadow medio=0.5027257; LiRA composto=0.498701</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
@@ -18299,7 +18299,7 @@
     <row r="232" ht="90" customHeight="1">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed123-eps0.5/experiment_20260914_152619.json</t>
+          <t>nodp-sweep2/experiment_20260908_202354.json</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -18309,11 +18309,11 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -18327,12 +18327,12 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>A2 — update clippato g_bar (Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr">
@@ -18342,17 +18342,17 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010704; Yeom medio=0.49885817165752017; Shadow medio=0.49721390000000004; LiRA composto=0.505366</t>
+          <t>LiRA medio=0.5007714; Yeom medio=0.5004956024284777; Shadow medio=0.5029101; LiRA composto=0.501679</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>nessun log associabile per nome</t>
+          <t>logs/nodp-sweep.log</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed123-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nodp-sweep2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr">
@@ -18376,7 +18376,7 @@
     <row r="233" ht="90" customHeight="1">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed123/experiment_20260910_172634.json</t>
+          <t>nvflare-central-seed123-eps0.5/experiment_20260914_152619.json</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -18386,13 +18386,11 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 123: DISCORDE, usare il nome cartella)</t>
-        </is>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>123</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
@@ -18411,7 +18409,7 @@
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr">
@@ -18421,7 +18419,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000368; Yeom medio=0.49981732394504885; Shadow medio=0.49837070000000006; LiRA composto=0.500623</t>
+          <t>LiRA medio=0.5010704; Yeom medio=0.49885817165752017; Shadow medio=0.49721390000000004; LiRA composto=0.505366</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr">
@@ -18431,7 +18429,7 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed123-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M233" s="4" t="inlineStr">
@@ -18455,7 +18453,7 @@
     <row r="234" ht="90" customHeight="1">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed1234/experiment_20260911_122836.json</t>
+          <t>nvflare-central-seed123/experiment_20260910_172634.json</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -18470,7 +18468,7 @@
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 1234: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 123: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
@@ -18500,7 +18498,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5012264; Yeom medio=0.5012137493317419; Shadow medio=0.5008147000000001; LiRA composto=0.506321</t>
+          <t>LiRA medio=0.5000368; Yeom medio=0.49981732394504885; Shadow medio=0.49837070000000006; LiRA composto=0.500623</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
@@ -18510,7 +18508,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr">
@@ -18534,7 +18532,7 @@
     <row r="235" ht="90" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed42-eps0.5/experiment_20260914_130854.json</t>
+          <t>nvflare-central-seed1234/experiment_20260911_122836.json</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -18544,11 +18542,13 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D235" s="3" t="n">
-        <v>42</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 1234: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4994279; Yeom medio=0.49465245749743075; Shadow medio=0.4958531; LiRA composto=0.500887</t>
+          <t>LiRA medio=0.5012264; Yeom medio=0.5012137493317419; Shadow medio=0.5008147000000001; LiRA composto=0.506321</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed42-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M235" s="4" t="inlineStr">
@@ -18611,7 +18611,7 @@
     <row r="236" ht="90" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed456-eps0.5/experiment_20260914_175355.json</t>
+          <t>nvflare-central-seed42-eps0.5/experiment_20260914_130854.json</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -18624,10 +18624,8 @@
           <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
-        </is>
+      <c r="D236" s="3" t="n">
+        <v>42</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -18656,7 +18654,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5011443; Yeom medio=0.49762605437521107; Shadow medio=0.4992915; LiRA composto=0.504601</t>
+          <t>LiRA medio=0.4994279; Yeom medio=0.49465245749743075; Shadow medio=0.4958531; LiRA composto=0.500887</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr">
@@ -18666,7 +18664,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed456-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed42-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr">
@@ -18690,7 +18688,7 @@
     <row r="237" ht="90" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed456/experiment_20260910_222515.json</t>
+          <t>nvflare-central-seed456-eps0.5/experiment_20260914_175355.json</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -18700,7 +18698,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -18725,7 +18723,7 @@
       </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I237" s="3" t="inlineStr">
@@ -18735,7 +18733,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5015437; Yeom medio=0.4976337915896831; Shadow medio=0.5007618; LiRA composto=0.505552</t>
+          <t>LiRA medio=0.5011443; Yeom medio=0.49762605437521107; Shadow medio=0.4992915; LiRA composto=0.504601</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr">
@@ -18745,7 +18743,7 @@
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed456-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M237" s="4" t="inlineStr">
@@ -18769,7 +18767,7 @@
     <row r="238" ht="90" customHeight="1">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed789-eps0.5/experiment_20260914_205551.json</t>
+          <t>nvflare-central-seed456/experiment_20260910_222515.json</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -18779,12 +18777,12 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+          <t>42 (cartella dice 456: DISCORDE, usare il nome cartella)</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
@@ -18804,7 +18802,7 @@
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr">
@@ -18814,7 +18812,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5005679; Yeom medio=0.49992255315113887; Shadow medio=0.4980574; LiRA composto=0.502025</t>
+          <t>LiRA medio=0.5015437; Yeom medio=0.4976337915896831; Shadow medio=0.5007618; LiRA composto=0.505552</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr">
@@ -18824,7 +18822,7 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed789-eps0.5/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M238" s="4" t="inlineStr">
@@ -18848,7 +18846,7 @@
     <row r="239" ht="90" customHeight="1">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>nvflare-central-seed789/experiment_20260911_095435.json</t>
+          <t>nvflare-central-seed789-eps0.5/experiment_20260914_205551.json</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -18858,7 +18856,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=central; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -18883,7 +18881,7 @@
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr">
@@ -18893,7 +18891,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002807; Yeom medio=0.5002761736218346; Shadow medio=0.49890680000000004; LiRA composto=0.504216</t>
+          <t>LiRA medio=0.5005679; Yeom medio=0.49992255315113887; Shadow medio=0.4980574; LiRA composto=0.502025</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr">
@@ -18903,7 +18901,7 @@
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-central-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed789-eps0.5/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M239" s="4" t="inlineStr">
@@ -18927,7 +18925,7 @@
     <row r="240" ht="90" customHeight="1">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
+          <t>nvflare-central-seed789/experiment_20260911_095435.json</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -18937,11 +18935,13 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="n">
-        <v>1234</v>
+          <t>dp_mode=central; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>42 (cartella dice 789: DISCORDE, usare il nome cartella)</t>
+        </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
@@ -18955,12 +18955,12 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
+          <t>A2 — update clippato g_bar (Scenario 1)</t>
         </is>
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
+          <t>LiRA medio=0.5002807; Yeom medio=0.5002761736218346; Shadow medio=0.49890680000000004; LiRA composto=0.504216</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-central-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M240" s="4" t="inlineStr">
@@ -19004,7 +19004,7 @@
     <row r="241" ht="90" customHeight="1">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
+          <t>nvflare-local-eps0.1-seed1234/experiment_20260922_042247.json</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D241" s="3" t="n">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=1.0; eps_avanzata=1.6225980474607942; eps_migliore=1.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
+          <t>LiRA medio=0.4991009999999999; Yeom medio=0.498463309727368; Shadow medio=0.4986541; LiRA composto=0.499449</t>
         </is>
       </c>
       <c r="K241" s="3" t="inlineStr">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.1-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M241" s="4" t="inlineStr">
@@ -19081,7 +19081,7 @@
     <row r="242" ht="90" customHeight="1">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
+          <t>nvflare-local-eps0.5-seed1234/experiment_20260922_023720.json</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -19091,11 +19091,11 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=5.0; eps_avanzata=10.830742000426373; eps_migliore=5.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I242" s="3" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
+          <t>LiRA medio=0.500784; Yeom medio=0.49968268349447253; Shadow medio=0.5005478; LiRA composto=0.499246</t>
         </is>
       </c>
       <c r="K242" s="3" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-eps0.5-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M242" s="4" t="inlineStr">
@@ -19158,7 +19158,7 @@
     <row r="243" ht="90" customHeight="1">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
+          <t>nvflare-local-seed123/experiment_20260912_124038.json</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -19172,7 +19172,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
+          <t>LiRA medio=0.5007023; Yeom medio=0.49776869378559124; Shadow medio=0.49707929999999995; LiRA composto=0.500178</t>
         </is>
       </c>
       <c r="K243" s="3" t="inlineStr">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed123/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M243" s="4" t="inlineStr">
@@ -19235,7 +19235,7 @@
     <row r="244" ht="90" customHeight="1">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
+          <t>nvflare-local-seed1234/experiment_20260913_123027.json</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -19249,7 +19249,7 @@
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
+          <t>LiRA medio=0.5006782999999999; Yeom medio=0.5004680380051301; Shadow medio=0.5010886999999999; LiRA composto=0.502131</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed1234/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M244" s="4" t="inlineStr">
@@ -19312,7 +19312,7 @@
     <row r="245" ht="90" customHeight="1">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
+          <t>nvflare-local-seed42/experiment_20260911_221630.json</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -19326,7 +19326,7 @@
         </is>
       </c>
       <c r="D245" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
+          <t>LiRA medio=0.49926259999999995; Yeom medio=0.4953191604901555; Shadow medio=0.4956479; LiRA composto=0.497653</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed42/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M245" s="4" t="inlineStr">
@@ -19389,7 +19389,7 @@
     <row r="246" ht="90" customHeight="1">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
+          <t>nvflare-local-seed456/experiment_20260912_164940.json</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -19403,7 +19403,7 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
+          <t>LiRA medio=0.4990612; Yeom medio=0.5030154039542946; Shadow medio=0.5028134000000001; LiRA composto=0.496285</t>
         </is>
       </c>
       <c r="K246" s="3" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed456/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M246" s="4" t="inlineStr">
@@ -19466,7 +19466,7 @@
     <row r="247" ht="90" customHeight="1">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
+          <t>nvflare-local-seed789/experiment_20260912_205847.json</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -19476,11 +19476,11 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=local; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A3 — update clippato e rumorizzato g_tilde (Scenario 1)</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
+          <t>LiRA medio=0.5002934; Yeom medio=0.5002666634478355; Shadow medio=0.49910560000000004; LiRA composto=0.503215</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-local-seed789/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M247" s="4" t="inlineStr">
@@ -19543,7 +19543,7 @@
     <row r="248" ht="90" customHeight="1">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260909_184236.json</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
+          <t>LiRA medio=0.49900160000000005; Yeom medio=0.49923908525758226; Shadow medio=0.4989686000000001; LiRA composto=0.496977</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
@@ -19620,7 +19620,7 @@
     <row r="249" ht="90" customHeight="1">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_183148.json</t>
+          <t>nvflare-stepb-dpfedavg-eps1/experiment_20260910_091241.json</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -19630,7 +19630,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0; delta=1e-05; round=10; epoche=50; batch=None; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D249" s="3" t="n">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=10.0; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
+          <t>LiRA medio=0.49933069999999996; Yeom medio=0.49586357084024224; Shadow medio=0.4987838; LiRA composto=0.496487</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="L249" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
+          <t>experiments/nvflare-stepb-dpfedavg-eps1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M249" s="4" t="inlineStr">
@@ -19697,7 +19697,7 @@
     <row r="250" ht="90" customHeight="1">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_203243.json</t>
+          <t>rq1-eps16/experiment_20260923_183148.json</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -19711,7 +19711,7 @@
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
+          <t>LiRA medio=0.501382; Yeom medio=0.4993044665453491; Shadow medio=0.4996347; LiRA composto=0.505203</t>
         </is>
       </c>
       <c r="K250" s="3" t="inlineStr">
@@ -19774,7 +19774,7 @@
     <row r="251" ht="90" customHeight="1">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260923_223219.json</t>
+          <t>rq1-eps16/experiment_20260923_203243.json</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
+          <t>LiRA medio=0.5002546000000001; Yeom medio=0.5022016559728439; Shadow medio=0.5014429999999999; LiRA composto=0.500876</t>
         </is>
       </c>
       <c r="K251" s="3" t="inlineStr">
@@ -19851,7 +19851,7 @@
     <row r="252" ht="90" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260924_003215.json</t>
+          <t>rq1-eps16/experiment_20260923_223219.json</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -19865,7 +19865,7 @@
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
+          <t>LiRA medio=0.5000473000000001; Yeom medio=0.5015947758305417; Shadow medio=0.5016767; LiRA composto=0.498949</t>
         </is>
       </c>
       <c r="K252" s="3" t="inlineStr">
@@ -19928,7 +19928,7 @@
     <row r="253" ht="90" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps16/experiment_20260924_023219.json</t>
+          <t>rq1-eps16/experiment_20260924_003215.json</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -19942,7 +19942,7 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
+          <t>LiRA medio=0.4981596; Yeom medio=0.5010103319251529; Shadow medio=0.5016226000000001; LiRA composto=0.495731</t>
         </is>
       </c>
       <c r="K253" s="3" t="inlineStr">
@@ -20005,7 +20005,7 @@
     <row r="254" ht="90" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_134148.json</t>
+          <t>rq1-eps16/experiment_20260924_023219.json</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -20015,11 +20015,11 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=160.0; eps_avanzata=1421777766.0696003; eps_migliore=160.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
+          <t>LiRA medio=0.4988328999999999; Yeom medio=0.503226829026809; Shadow medio=0.5011254; LiRA composto=0.495068</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps16/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M254" s="4" t="inlineStr">
@@ -20082,7 +20082,7 @@
     <row r="255" ht="90" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_154640.json</t>
+          <t>rq1-eps2/experiment_20260922_134148.json</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -20096,7 +20096,7 @@
         </is>
       </c>
       <c r="D255" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
+          <t>LiRA medio=0.5008978999999999; Yeom medio=0.49920459553580754; Shadow medio=0.4988175; LiRA composto=0.497475</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
@@ -20159,7 +20159,7 @@
     <row r="256" ht="90" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_175039.json</t>
+          <t>rq1-eps2/experiment_20260922_154640.json</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -20173,7 +20173,7 @@
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
+          <t>LiRA medio=0.49698469999999995; Yeom medio=0.4974788723352816; Shadow medio=0.500403; LiRA composto=0.489759</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="257" ht="90" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_180414.json</t>
+          <t>rq1-eps2/experiment_20260922_175039.json</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="D257" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
+          <t>LiRA medio=0.49771210000000005; Yeom medio=0.5008818247967856; Shadow medio=0.5008399000000001; LiRA composto=0.494085</t>
         </is>
       </c>
       <c r="K257" s="3" t="inlineStr">
@@ -20292,9 +20292,9 @@
           <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
-      <c r="M257" s="5" t="inlineStr">
-        <is>
-          <t>incompleta</t>
+      <c r="M257" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -20304,7 +20304,7 @@
       </c>
       <c r="O257" s="3" t="inlineStr">
         <is>
-          <t>nessuna metrica MIA nel JSON</t>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
         </is>
       </c>
       <c r="P257" s="3" t="n"/>
@@ -20313,7 +20313,7 @@
     <row r="258" ht="90" customHeight="1">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260922_200439.json</t>
+          <t>rq1-eps2/experiment_20260922_180414.json</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
+          <t>LiRA medio=None; Yeom medio=None; Shadow medio=None; LiRA composto=None</t>
         </is>
       </c>
       <c r="K258" s="3" t="inlineStr">
@@ -20369,9 +20369,9 @@
           <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
-      <c r="M258" s="4" t="inlineStr">
-        <is>
-          <t>completata da verificare</t>
+      <c r="M258" s="5" t="inlineStr">
+        <is>
+          <t>incompleta</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="O258" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessuna metrica MIA nel JSON</t>
         </is>
       </c>
       <c r="P258" s="3" t="n"/>
@@ -20390,7 +20390,7 @@
     <row r="259" ht="90" customHeight="1">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps2/experiment_20260924_102430.json</t>
+          <t>rq1-eps2/experiment_20260922_200439.json</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>789</v>
+        <v>1234</v>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
+          <t>LiRA medio=0.4997895; Yeom medio=0.502411532198251; Shadow medio=0.5004227; LiRA composto=0.499413</t>
         </is>
       </c>
       <c r="K259" s="3" t="inlineStr">
@@ -20467,7 +20467,7 @@
     <row r="260" ht="90" customHeight="1">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260922_220310.json</t>
+          <t>rq1-eps2/experiment_20260924_102430.json</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -20477,11 +20477,11 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=20.0; eps_avanzata=158.12966456631594; eps_migliore=20.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
+          <t>LiRA medio=0.4989243; Yeom medio=0.5021064138115394; Shadow medio=0.5020787999999999; LiRA composto=0.497784</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr">
@@ -20520,7 +20520,7 @@
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M260" s="4" t="inlineStr">
@@ -20544,7 +20544,7 @@
     <row r="261" ht="90" customHeight="1">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_000138.json</t>
+          <t>rq1-eps4/experiment_20260922_220310.json</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -20558,7 +20558,7 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
+          <t>LiRA medio=0.5013445000000001; Yeom medio=0.4984706408433965; Shadow medio=0.49830389999999997; LiRA composto=0.502434</t>
         </is>
       </c>
       <c r="K261" s="3" t="inlineStr">
@@ -20621,7 +20621,7 @@
     <row r="262" ht="90" customHeight="1">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_020058.json</t>
+          <t>rq1-eps4/experiment_20260923_000138.json</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -20635,7 +20635,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
+          <t>LiRA medio=0.4963656; Yeom medio=0.49735614916089077; Shadow medio=0.4998671; LiRA composto=0.488462</t>
         </is>
       </c>
       <c r="K262" s="3" t="inlineStr">
@@ -20698,7 +20698,7 @@
     <row r="263" ht="90" customHeight="1">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_040025.json</t>
+          <t>rq1-eps4/experiment_20260923_020058.json</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -20712,7 +20712,7 @@
         </is>
       </c>
       <c r="D263" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
+          <t>LiRA medio=0.49877469999999996; Yeom medio=0.5016356850531659; Shadow medio=0.5014784; LiRA composto=0.495937</t>
         </is>
       </c>
       <c r="K263" s="3" t="inlineStr">
@@ -20775,7 +20775,7 @@
     <row r="264" ht="90" customHeight="1">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps4/experiment_20260923_055955.json</t>
+          <t>rq1-eps4/experiment_20260923_040025.json</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -20789,7 +20789,7 @@
         </is>
       </c>
       <c r="D264" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
+          <t>LiRA medio=0.4987033; Yeom medio=0.500839703176525; Shadow medio=0.5014299; LiRA composto=0.495946</t>
         </is>
       </c>
       <c r="K264" s="3" t="inlineStr">
@@ -20852,7 +20852,7 @@
     <row r="265" ht="90" customHeight="1">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_080158.json</t>
+          <t>rq1-eps4/experiment_20260923_055955.json</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -20862,11 +20862,11 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D265" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=40.0; eps_avanzata=2204.6230865011753; eps_migliore=40.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I265" s="3" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
+          <t>LiRA medio=0.4988779; Yeom medio=0.5013099508514725; Shadow medio=0.4997813000000001; LiRA composto=0.496495</t>
         </is>
       </c>
       <c r="K265" s="3" t="inlineStr">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps4/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M265" s="4" t="inlineStr">
@@ -20929,7 +20929,7 @@
     <row r="266" ht="90" customHeight="1">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_100736.json</t>
+          <t>rq1-eps64/experiment_20260925_133527.json</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="H266" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I266" s="3" t="inlineStr">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
+          <t>LiRA medio=0.4994924; Yeom medio=0.500202847296049; Shadow medio=0.5016474; LiRA composto=0.501621</t>
         </is>
       </c>
       <c r="K266" s="3" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M266" s="4" t="inlineStr">
@@ -21006,7 +21006,7 @@
     <row r="267" ht="90" customHeight="1">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_121447.json</t>
+          <t>rq1-eps64/experiment_20260925_153659.json</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D267" s="3" t="n">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="H267" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I267" s="3" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
+          <t>LiRA medio=0.5007419000000001; Yeom medio=0.5018089537225212; Shadow medio=0.5021445; LiRA composto=0.505961</t>
         </is>
       </c>
       <c r="K267" s="3" t="inlineStr">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M267" s="4" t="inlineStr">
@@ -21083,7 +21083,7 @@
     <row r="268" ht="90" customHeight="1">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_142154.json</t>
+          <t>rq1-eps64/experiment_20260925_174648.json</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I268" s="3" t="inlineStr">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+          <t>LiRA medio=0.49927479999999996; Yeom medio=0.4993932574705867; Shadow medio=0.5007136000000001; LiRA composto=0.497913</t>
         </is>
       </c>
       <c r="K268" s="3" t="inlineStr">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M268" s="4" t="inlineStr">
@@ -21160,7 +21160,7 @@
     <row r="269" ht="90" customHeight="1">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>rq1-eps8/experiment_20260923_162834.json</t>
+          <t>rq1-eps64/experiment_20260925_194807.json</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -21170,7 +21170,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D269" s="3" t="n">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+          <t>LiRA medio=0.4997375999999999; Yeom medio=0.5012492500869867; Shadow medio=0.5020982999999999; LiRA composto=0.499963</t>
         </is>
       </c>
       <c r="K269" s="3" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M269" s="4" t="inlineStr">
@@ -21233,6 +21233,468 @@
       </c>
       <c r="P269" s="3" t="n"/>
       <c r="Q269" s="3" t="n"/>
+    </row>
+    <row r="270" ht="90" customHeight="1">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps64/experiment_20260925_214757.json</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I270" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J270" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49855; Yeom medio=0.4992467157518548; Shadow medio=0.4996785; LiRA composto=0.499981</t>
+        </is>
+      </c>
+      <c r="K270" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M270" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O270" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P270" s="3" t="n"/>
+      <c r="Q270" s="3" t="n"/>
+    </row>
+    <row r="271" ht="90" customHeight="1">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_080158.json</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5010125999999999; Yeom medio=0.4987721658486498; Shadow medio=0.4984134000000001; LiRA composto=0.500277</t>
+        </is>
+      </c>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L271" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M271" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O271" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P271" s="3" t="n"/>
+      <c r="Q271" s="3" t="n"/>
+    </row>
+    <row r="272" ht="90" customHeight="1">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_100736.json</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I272" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4983582999999999; Yeom medio=0.49812561808899297; Shadow medio=0.49932030000000005; LiRA composto=0.49701</t>
+        </is>
+      </c>
+      <c r="K272" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L272" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M272" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O272" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P272" s="3" t="n"/>
+      <c r="Q272" s="3" t="n"/>
+    </row>
+    <row r="273" ht="90" customHeight="1">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_121447.json</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J273" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4988588; Yeom medio=0.5000374068341784; Shadow medio=0.5012641; LiRA composto=0.494069</t>
+        </is>
+      </c>
+      <c r="K273" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L273" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M273" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O273" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P273" s="3" t="n"/>
+      <c r="Q273" s="3" t="n"/>
+    </row>
+    <row r="274" ht="90" customHeight="1">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_142154.json</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I274" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J274" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4996786999999999; Yeom medio=0.501743146958169; Shadow medio=0.5014206999999999; LiRA composto=0.496859</t>
+        </is>
+      </c>
+      <c r="K274" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L274" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M274" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O274" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P274" s="3" t="n"/>
+      <c r="Q274" s="3" t="n"/>
+    </row>
+    <row r="275" ht="90" customHeight="1">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>rq1-eps8/experiment_20260923_162834.json</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=80.0; eps_avanzata=238518.03313368908; eps_migliore=80.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I275" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J275" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.500563; Yeom medio=0.5018322743328781; Shadow medio=0.5004843999999999; LiRA composto=0.500729</t>
+        </is>
+      </c>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L275" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-eps8/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M275" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O275" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P275" s="3" t="n"/>
+      <c r="Q275" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q275"/>
+  <dimension ref="A1:Q276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -21696,6 +21696,83 @@
       <c r="P275" s="3" t="n"/>
       <c r="Q275" s="3" t="n"/>
     </row>
+    <row r="276" ht="90" customHeight="1">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>rq1-recorddp-nm1/experiment_20260926_115832.json</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.391161900463153</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>naturale — record-DP (diagnostico)</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I276" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J276" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5006242999999999; Yeom medio=0.5014409510198713; Shadow medio=0.5029617; LiRA composto=0.497648</t>
+        </is>
+      </c>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M276" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O276" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+        </is>
+      </c>
+      <c r="P276" s="3" t="n"/>
+      <c r="Q276" s="3" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q276"/>
+  <dimension ref="A1:Q298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -617,12 +617,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 3.792014934616144; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 3.792014934616144; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 3.792014934616144; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 0.21421011636007342; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 6d31e21 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P104" s="3" t="n"/>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 3.792014934616144; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = None; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 3.792014934616144; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 3.792014934616144; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 3.792014934616144; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 5.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 3.792014934616144; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 2c4a0f0 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P124" s="3" t="n"/>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P125" s="3" t="n"/>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P126" s="3" t="n"/>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P127" s="3" t="n"/>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P128" s="3" t="n"/>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P129" s="3" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P130" s="3" t="n"/>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit 8d44ae3 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P131" s="3" t="n"/>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 70562db registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P132" s="3" t="n"/>
@@ -10699,17 +10699,17 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP (diagnostico)</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 0.9936577181915225; per client None; limite con lo shuffle, adiacenza per sostituzione = None; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -19072,7 +19072,7 @@
       </c>
       <c r="O241" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit f89c1cc registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P241" s="3" t="n"/>
@@ -19149,7 +19149,7 @@
       </c>
       <c r="O242" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit f89c1cc registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P242" s="3" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="O250" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit ed0e1f9 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P250" s="3" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="O251" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit ed0e1f9 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P251" s="3" t="n"/>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="O252" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit ed0e1f9 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P252" s="3" t="n"/>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="O253" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit ed0e1f9 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P253" s="3" t="n"/>
@@ -20073,7 +20073,7 @@
       </c>
       <c r="O254" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit ed0e1f9 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P254" s="3" t="n"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="O255" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P255" s="3" t="n"/>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="O256" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P256" s="3" t="n"/>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="O257" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P257" s="3" t="n"/>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="O259" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P259" s="3" t="n"/>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 478d471 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P260" s="3" t="n"/>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="O261" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P261" s="3" t="n"/>
@@ -20689,7 +20689,7 @@
       </c>
       <c r="O262" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P262" s="3" t="n"/>
@@ -20766,7 +20766,7 @@
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P263" s="3" t="n"/>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="O264" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P264" s="3" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="O265" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P265" s="3" t="n"/>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="O266" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 8d44ae3 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P266" s="3" t="n"/>
@@ -21074,7 +21074,7 @@
       </c>
       <c r="O267" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit 8d44ae3 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P267" s="3" t="n"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="O268" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit 8d44ae3 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P268" s="3" t="n"/>
@@ -21228,7 +21228,7 @@
       </c>
       <c r="O269" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit 8d44ae3 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P269" s="3" t="n"/>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="O270" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit 8d44ae3 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P270" s="3" t="n"/>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="O271" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P271" s="3" t="n"/>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="O272" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P272" s="3" t="n"/>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="O273" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P273" s="3" t="n"/>
@@ -21613,7 +21613,7 @@
       </c>
       <c r="O274" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit f145b79 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P274" s="3" t="n"/>
@@ -21690,7 +21690,7 @@
       </c>
       <c r="O275" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>commit ed0e1f9 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P275" s="3" t="n"/>
@@ -21722,17 +21722,17 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP (diagnostico)</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H276" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.391161900463153; per client {'jpl': 4.827360389586961, 'caltech': 4.9961384863040035, 'office1': 30.391161900463153}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I276" s="3" t="inlineStr">
@@ -21767,11 +21767,1705 @@
       </c>
       <c r="O276" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto, ma commit e hash degli split non sono registrati: la tracciabilita' completa richiesta dalla Fase A non e' ricostruibile</t>
+          <t>nessun difetto noto; commit 0dedd34 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P276" s="3" t="n"/>
       <c r="Q276" s="3" t="n"/>
+    </row>
+    <row r="277" ht="90" customHeight="1">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>rq1-recorddp-nm1/experiment_20260926_151825.json</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.975180902516065</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>naturale — record-DP</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.975180902516065; per client {'jpl': 4.826504114513053, 'office1': 30.975180902516065, 'caltech': 4.996366486983374}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I277" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J277" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5002221; Yeom medio=0.5017294522289747; Shadow medio=0.5031289; LiRA composto=0.502612</t>
+        </is>
+      </c>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L277" s="3" t="inlineStr">
+        <is>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M277" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O277" s="3" t="inlineStr">
+        <is>
+          <t>commit 1519d16 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P277" s="3" t="n"/>
+      <c r="Q277" s="3" t="n"/>
+    </row>
+    <row r="278" ht="90" customHeight="1">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: _prova_recorddp_v2/experiment_20260924_211919.json</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>naturale — record-DP</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I278" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J278" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5002141000000001; Yeom medio=0.4970069971772901; Shadow medio=0.49694009999999994; LiRA composto=0.504325</t>
+        </is>
+      </c>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/_prova_recorddp_v2/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M278" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O278" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 2c4a0f0 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P278" s="3" t="n"/>
+      <c r="Q278" s="3" t="n"/>
+    </row>
+    <row r="279" ht="90" customHeight="1">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_153736.json</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I279" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J279" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4993168; Yeom medio=0.49919633623488513; Shadow medio=0.4999852000000001; LiRA composto=0.494312</t>
+        </is>
+      </c>
+      <c r="K279" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L279" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M279" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O279" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P279" s="3" t="n"/>
+      <c r="Q279" s="3" t="n"/>
+    </row>
+    <row r="280" ht="90" customHeight="1">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_181736.json</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I280" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J280" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5007422; Yeom medio=0.49949077445719875; Shadow medio=0.5016429; LiRA composto=0.500728</t>
+        </is>
+      </c>
+      <c r="K280" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L280" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M280" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O280" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P280" s="3" t="n"/>
+      <c r="Q280" s="3" t="n"/>
+    </row>
+    <row r="281" ht="90" customHeight="1">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_205828.json</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I281" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J281" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5024474999999999; Yeom medio=0.500957717462529; Shadow medio=0.5006991999999999; LiRA composto=0.510864</t>
+        </is>
+      </c>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L281" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M281" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O281" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P281" s="3" t="n"/>
+      <c r="Q281" s="3" t="n"/>
+    </row>
+    <row r="282" ht="90" customHeight="1">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_233900.json</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I282" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J282" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4988184000000001; Yeom medio=0.5006017002808242; Shadow medio=0.5012987000000001; LiRA composto=0.49605</t>
+        </is>
+      </c>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L282" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M282" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O282" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P282" s="3" t="n"/>
+      <c r="Q282" s="3" t="n"/>
+    </row>
+    <row r="283" ht="90" customHeight="1">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260926_021820.json</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J283" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4990908; Yeom medio=0.5012730588018359; Shadow medio=0.5016101; LiRA composto=0.49656</t>
+        </is>
+      </c>
+      <c r="K283" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L283" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M283" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O283" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P283" s="3" t="n"/>
+      <c r="Q283" s="3" t="n"/>
+    </row>
+    <row r="284" ht="90" customHeight="1">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid/experiment_20260923_125958.json</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J284" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5000165000000001; Yeom medio=0.49860830175646453; Shadow medio=0.49871509999999997; LiRA composto=0.501325</t>
+        </is>
+      </c>
+      <c r="K284" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M284" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O284" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P284" s="3" t="n"/>
+      <c r="Q284" s="3" t="n"/>
+    </row>
+    <row r="285" ht="90" customHeight="1">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid/experiment_20260923_154115.json</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J285" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49547470000000005; Yeom medio=0.4998060941716229; Shadow medio=0.5016756000000001; LiRA composto=0.493375</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L285" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M285" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O285" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P285" s="3" t="n"/>
+      <c r="Q285" s="3" t="n"/>
+    </row>
+    <row r="286" ht="90" customHeight="1">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid/experiment_20260923_182128.json</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J286" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49985480000000004; Yeom medio=0.5061390053404418; Shadow medio=0.5038358; LiRA composto=0.500351</t>
+        </is>
+      </c>
+      <c r="K286" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M286" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O286" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P286" s="3" t="n"/>
+      <c r="Q286" s="3" t="n"/>
+    </row>
+    <row r="287" ht="90" customHeight="1">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid/experiment_20260923_210136.json</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I287" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J287" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4991365; Yeom medio=0.5003720274583884; Shadow medio=0.5009321000000001; LiRA composto=0.496163</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M287" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O287" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P287" s="3" t="n"/>
+      <c r="Q287" s="3" t="n"/>
+    </row>
+    <row r="288" ht="90" customHeight="1">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-iid/experiment_20260923_234138.json</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J288" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5021373; Yeom medio=0.5007196890101487; Shadow medio=0.5010036; LiRA composto=0.505533</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M288" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O288" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P288" s="3" t="n"/>
+      <c r="Q288" s="3" t="n"/>
+    </row>
+    <row r="289" ht="90" customHeight="1">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_021212.json</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I289" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J289" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49871699999999997; Yeom medio=0.4992244148810894; Shadow medio=0.49964450000000016; LiRA composto=0.501071</t>
+        </is>
+      </c>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L289" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M289" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O289" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P289" s="3" t="n"/>
+      <c r="Q289" s="3" t="n"/>
+    </row>
+    <row r="290" ht="90" customHeight="1">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_045650.json</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J290" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4997273; Yeom medio=0.5001001052322953; Shadow medio=0.5016489; LiRA composto=0.502277</t>
+        </is>
+      </c>
+      <c r="K290" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M290" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O290" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P290" s="3" t="n"/>
+      <c r="Q290" s="3" t="n"/>
+    </row>
+    <row r="291" ht="90" customHeight="1">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_073952.json</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I291" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J291" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4985705; Yeom medio=0.5027887367096913; Shadow medio=0.5029678000000001; LiRA composto=0.503597</t>
+        </is>
+      </c>
+      <c r="K291" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L291" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M291" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O291" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P291" s="3" t="n"/>
+      <c r="Q291" s="3" t="n"/>
+    </row>
+    <row r="292" ht="90" customHeight="1">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_101906.json</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J292" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5000697; Yeom medio=0.4992625830796393; Shadow medio=0.5006257; LiRA composto=0.50064</t>
+        </is>
+      </c>
+      <c r="K292" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L292" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M292" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O292" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P292" s="3" t="n"/>
+      <c r="Q292" s="3" t="n"/>
+    </row>
+    <row r="293" ht="90" customHeight="1">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_125758.json</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I293" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J293" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5010308; Yeom medio=0.5012359131513038; Shadow medio=0.5019937999999999; LiRA composto=0.499856</t>
+        </is>
+      </c>
+      <c r="K293" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L293" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M293" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O293" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P293" s="3" t="n"/>
+      <c r="Q293" s="3" t="n"/>
+    </row>
+    <row r="294" ht="90" customHeight="1">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260922_234305.json</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I294" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J294" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5001295; Yeom medio=0.49683259053359585; Shadow medio=0.49730420000000003; LiRA composto=0.49799</t>
+        </is>
+      </c>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M294" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O294" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P294" s="3" t="n"/>
+      <c r="Q294" s="3" t="n"/>
+    </row>
+    <row r="295" ht="90" customHeight="1">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_022133.json</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I295" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J295" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5002134; Yeom medio=0.4992528097560955; Shadow medio=0.5018565999999999; LiRA composto=0.496275</t>
+        </is>
+      </c>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L295" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M295" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O295" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P295" s="3" t="n"/>
+      <c r="Q295" s="3" t="n"/>
+    </row>
+    <row r="296" ht="90" customHeight="1">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_045959.json</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I296" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J296" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49730750000000007; Yeom medio=0.5013561115504457; Shadow medio=0.502413; LiRA composto=0.494383</t>
+        </is>
+      </c>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M296" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O296" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P296" s="3" t="n"/>
+      <c r="Q296" s="3" t="n"/>
+    </row>
+    <row r="297" ht="90" customHeight="1">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_073901.json</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I297" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J297" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5003536000000001; Yeom medio=0.5037016364627064; Shadow medio=0.5024371000000001; LiRA composto=0.500249</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L297" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M297" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O297" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P297" s="3" t="n"/>
+      <c r="Q297" s="3" t="n"/>
+    </row>
+    <row r="298" ht="90" customHeight="1">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_101922.json</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I298" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J298" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4997687; Yeom medio=0.5006942539356262; Shadow medio=0.5027999999999999; LiRA composto=0.502273</t>
+        </is>
+      </c>
+      <c r="K298" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L298" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M298" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N298" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O298" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P298" s="3" t="n"/>
+      <c r="Q298" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q298"/>
+  <dimension ref="A1:Q301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -21853,7 +21853,7 @@
     <row r="278" ht="90" customHeight="1">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: _prova_recorddp_v2/experiment_20260924_211919.json</t>
+          <t>rq1-recorddp-nm1/experiment_20260926_183757.json</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -21863,11 +21863,11 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.355490267392394</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.355490267392394; per client {'jpl': 4.817642925378795, 'caltech': 5.0071752295132805, 'office1': 30.355490267392394}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I278" s="3" t="inlineStr">
@@ -21896,7 +21896,7 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002141000000001; Yeom medio=0.4970069971772901; Shadow medio=0.49694009999999994; LiRA composto=0.504325</t>
+          <t>LiRA medio=0.499089; Yeom medio=0.5014118506681772; Shadow medio=0.5040574; LiRA composto=0.497402</t>
         </is>
       </c>
       <c r="K278" s="3" t="inlineStr">
@@ -21906,7 +21906,7 @@
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/_prova_recorddp_v2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M278" s="4" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="O278" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 2c4a0f0 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P278" s="3" t="n"/>
@@ -21930,7 +21930,7 @@
     <row r="279" ht="90" customHeight="1">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_153736.json</t>
+          <t>rq1-recorddp-nm1/experiment_20260926_215557.json</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -21940,11 +21940,11 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.355490267392394</t>
         </is>
       </c>
       <c r="D279" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
@@ -21953,17 +21953,17 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.355490267392394; per client {'jpl': 4.817862945887583, 'caltech': 5.006927312510939, 'office1': 30.355490267392394}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993168; Yeom medio=0.49919633623488513; Shadow medio=0.4999852000000001; LiRA composto=0.494312</t>
+          <t>LiRA medio=0.5016651; Yeom medio=0.5017909056517103; Shadow medio=0.5036755; LiRA composto=0.502849</t>
         </is>
       </c>
       <c r="K279" s="3" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M279" s="4" t="inlineStr">
@@ -21998,7 +21998,7 @@
       </c>
       <c r="O279" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P279" s="3" t="n"/>
@@ -22007,7 +22007,7 @@
     <row r="280" ht="90" customHeight="1">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_181736.json</t>
+          <t>rq1-recorddp-nm1/experiment_20260927_011250.json</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -22017,11 +22017,11 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
@@ -22030,17 +22030,17 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I280" s="3" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007422; Yeom medio=0.49949077445719875; Shadow medio=0.5016429; LiRA composto=0.500728</t>
+          <t>LiRA medio=0.5003566; Yeom medio=0.49700702441902517; Shadow medio=0.4969783; LiRA composto=0.502476</t>
         </is>
       </c>
       <c r="K280" s="3" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M280" s="4" t="inlineStr">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="O280" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P280" s="3" t="n"/>
@@ -22084,7 +22084,7 @@
     <row r="281" ht="90" customHeight="1">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_205828.json</t>
+          <t>altre_macchine: _prova_recorddp_v2/experiment_20260924_211919.json</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -22094,11 +22094,11 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
         </is>
       </c>
       <c r="D281" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
@@ -22107,17 +22107,17 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I281" s="3" t="inlineStr">
@@ -22127,7 +22127,7 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5024474999999999; Yeom medio=0.500957717462529; Shadow medio=0.5006991999999999; LiRA composto=0.510864</t>
+          <t>LiRA medio=0.5002141000000001; Yeom medio=0.4970069971772901; Shadow medio=0.49694009999999994; LiRA composto=0.504325</t>
         </is>
       </c>
       <c r="K281" s="3" t="inlineStr">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/_prova_recorddp_v2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M281" s="4" t="inlineStr">
@@ -22152,7 +22152,7 @@
       </c>
       <c r="O281" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 2c4a0f0 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P281" s="3" t="n"/>
@@ -22161,7 +22161,7 @@
     <row r="282" ht="90" customHeight="1">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_233900.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_153736.json</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="D282" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988184000000001; Yeom medio=0.5006017002808242; Shadow medio=0.5012987000000001; LiRA composto=0.49605</t>
+          <t>LiRA medio=0.4993168; Yeom medio=0.49919633623488513; Shadow medio=0.4999852000000001; LiRA composto=0.494312</t>
         </is>
       </c>
       <c r="K282" s="3" t="inlineStr">
@@ -22238,7 +22238,7 @@
     <row r="283" ht="90" customHeight="1">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260926_021820.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_181736.json</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -22252,7 +22252,7 @@
         </is>
       </c>
       <c r="D283" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4990908; Yeom medio=0.5012730588018359; Shadow medio=0.5016101; LiRA composto=0.49656</t>
+          <t>LiRA medio=0.5007422; Yeom medio=0.49949077445719875; Shadow medio=0.5016429; LiRA composto=0.500728</t>
         </is>
       </c>
       <c r="K283" s="3" t="inlineStr">
@@ -22315,7 +22315,7 @@
     <row r="284" ht="90" customHeight="1">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_125958.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_205828.json</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -22325,11 +22325,11 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
@@ -22343,12 +22343,12 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I284" s="3" t="inlineStr">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000165000000001; Yeom medio=0.49860830175646453; Shadow medio=0.49871509999999997; LiRA composto=0.501325</t>
+          <t>LiRA medio=0.5024474999999999; Yeom medio=0.500957717462529; Shadow medio=0.5006991999999999; LiRA composto=0.510864</t>
         </is>
       </c>
       <c r="K284" s="3" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M284" s="4" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="O284" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P284" s="3" t="n"/>
@@ -22392,7 +22392,7 @@
     <row r="285" ht="90" customHeight="1">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_154115.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_233900.json</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -22402,11 +22402,11 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
@@ -22420,12 +22420,12 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I285" s="3" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49547470000000005; Yeom medio=0.4998060941716229; Shadow medio=0.5016756000000001; LiRA composto=0.493375</t>
+          <t>LiRA medio=0.4988184000000001; Yeom medio=0.5006017002808242; Shadow medio=0.5012987000000001; LiRA composto=0.49605</t>
         </is>
       </c>
       <c r="K285" s="3" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M285" s="4" t="inlineStr">
@@ -22460,7 +22460,7 @@
       </c>
       <c r="O285" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P285" s="3" t="n"/>
@@ -22469,7 +22469,7 @@
     <row r="286" ht="90" customHeight="1">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_182128.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260926_021820.json</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -22479,11 +22479,11 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
-        <v>456</v>
+        <v>1234</v>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
@@ -22497,12 +22497,12 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H286" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I286" s="3" t="inlineStr">
@@ -22512,7 +22512,7 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49985480000000004; Yeom medio=0.5061390053404418; Shadow medio=0.5038358; LiRA composto=0.500351</t>
+          <t>LiRA medio=0.4990908; Yeom medio=0.5012730588018359; Shadow medio=0.5016101; LiRA composto=0.49656</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M286" s="4" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="O286" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P286" s="3" t="n"/>
@@ -22546,7 +22546,7 @@
     <row r="287" ht="90" customHeight="1">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_210136.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_125958.json</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991365; Yeom medio=0.5003720274583884; Shadow medio=0.5009321000000001; LiRA composto=0.496163</t>
+          <t>LiRA medio=0.5000165000000001; Yeom medio=0.49860830175646453; Shadow medio=0.49871509999999997; LiRA composto=0.501325</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr">
@@ -22623,7 +22623,7 @@
     <row r="288" ht="90" customHeight="1">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_234138.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_154115.json</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -22637,7 +22637,7 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5021373; Yeom medio=0.5007196890101487; Shadow medio=0.5010036; LiRA composto=0.505533</t>
+          <t>LiRA medio=0.49547470000000005; Yeom medio=0.4998060941716229; Shadow medio=0.5016756000000001; LiRA composto=0.493375</t>
         </is>
       </c>
       <c r="K288" s="3" t="inlineStr">
@@ -22700,7 +22700,7 @@
     <row r="289" ht="90" customHeight="1">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_021212.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_182128.json</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -22710,11 +22710,11 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
@@ -22728,12 +22728,12 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I289" s="3" t="inlineStr">
@@ -22743,7 +22743,7 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49871699999999997; Yeom medio=0.4992244148810894; Shadow medio=0.49964450000000016; LiRA composto=0.501071</t>
+          <t>LiRA medio=0.49985480000000004; Yeom medio=0.5061390053404418; Shadow medio=0.5038358; LiRA composto=0.500351</t>
         </is>
       </c>
       <c r="K289" s="3" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M289" s="4" t="inlineStr">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="O289" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P289" s="3" t="n"/>
@@ -22777,7 +22777,7 @@
     <row r="290" ht="90" customHeight="1">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_045650.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_210136.json</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -22787,11 +22787,11 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
@@ -22805,12 +22805,12 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I290" s="3" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997273; Yeom medio=0.5001001052322953; Shadow medio=0.5016489; LiRA composto=0.502277</t>
+          <t>LiRA medio=0.4991365; Yeom medio=0.5003720274583884; Shadow medio=0.5009321000000001; LiRA composto=0.496163</t>
         </is>
       </c>
       <c r="K290" s="3" t="inlineStr">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M290" s="4" t="inlineStr">
@@ -22845,7 +22845,7 @@
       </c>
       <c r="O290" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P290" s="3" t="n"/>
@@ -22854,7 +22854,7 @@
     <row r="291" ht="90" customHeight="1">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_073952.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_234138.json</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -22864,11 +22864,11 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>456</v>
+        <v>1234</v>
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
@@ -22882,12 +22882,12 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I291" s="3" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.5027887367096913; Shadow medio=0.5029678000000001; LiRA composto=0.503597</t>
+          <t>LiRA medio=0.5021373; Yeom medio=0.5007196890101487; Shadow medio=0.5010036; LiRA composto=0.505533</t>
         </is>
       </c>
       <c r="K291" s="3" t="inlineStr">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="L291" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M291" s="4" t="inlineStr">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="O291" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P291" s="3" t="n"/>
@@ -22931,7 +22931,7 @@
     <row r="292" ht="90" customHeight="1">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_101906.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_021212.json</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000697; Yeom medio=0.4992625830796393; Shadow medio=0.5006257; LiRA composto=0.50064</t>
+          <t>LiRA medio=0.49871699999999997; Yeom medio=0.4992244148810894; Shadow medio=0.49964450000000016; LiRA composto=0.501071</t>
         </is>
       </c>
       <c r="K292" s="3" t="inlineStr">
@@ -23008,7 +23008,7 @@
     <row r="293" ht="90" customHeight="1">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_125758.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_045650.json</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -23022,7 +23022,7 @@
         </is>
       </c>
       <c r="D293" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010308; Yeom medio=0.5012359131513038; Shadow medio=0.5019937999999999; LiRA composto=0.499856</t>
+          <t>LiRA medio=0.4997273; Yeom medio=0.5001001052322953; Shadow medio=0.5016489; LiRA composto=0.502277</t>
         </is>
       </c>
       <c r="K293" s="3" t="inlineStr">
@@ -23085,7 +23085,7 @@
     <row r="294" ht="90" customHeight="1">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260922_234305.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_073952.json</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -23095,11 +23095,11 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
@@ -23113,12 +23113,12 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H294" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I294" s="3" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001295; Yeom medio=0.49683259053359585; Shadow medio=0.49730420000000003; LiRA composto=0.49799</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.5027887367096913; Shadow medio=0.5029678000000001; LiRA composto=0.503597</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
@@ -23138,7 +23138,7 @@
       </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M294" s="4" t="inlineStr">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="O294" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P294" s="3" t="n"/>
@@ -23162,7 +23162,7 @@
     <row r="295" ht="90" customHeight="1">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_022133.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_101906.json</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -23172,11 +23172,11 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D295" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
@@ -23190,12 +23190,12 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H295" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I295" s="3" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002134; Yeom medio=0.4992528097560955; Shadow medio=0.5018565999999999; LiRA composto=0.496275</t>
+          <t>LiRA medio=0.5000697; Yeom medio=0.4992625830796393; Shadow medio=0.5006257; LiRA composto=0.50064</t>
         </is>
       </c>
       <c r="K295" s="3" t="inlineStr">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="L295" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M295" s="4" t="inlineStr">
@@ -23230,7 +23230,7 @@
       </c>
       <c r="O295" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P295" s="3" t="n"/>
@@ -23239,7 +23239,7 @@
     <row r="296" ht="90" customHeight="1">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_045959.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_125758.json</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -23249,11 +23249,11 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>456</v>
+        <v>1234</v>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
@@ -23267,12 +23267,12 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H296" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I296" s="3" t="inlineStr">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49730750000000007; Yeom medio=0.5013561115504457; Shadow medio=0.502413; LiRA composto=0.494383</t>
+          <t>LiRA medio=0.5010308; Yeom medio=0.5012359131513038; Shadow medio=0.5019937999999999; LiRA composto=0.499856</t>
         </is>
       </c>
       <c r="K296" s="3" t="inlineStr">
@@ -23292,7 +23292,7 @@
       </c>
       <c r="L296" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M296" s="4" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="O296" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P296" s="3" t="n"/>
@@ -23316,7 +23316,7 @@
     <row r="297" ht="90" customHeight="1">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_073901.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260922_234305.json</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -23330,7 +23330,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003536000000001; Yeom medio=0.5037016364627064; Shadow medio=0.5024371000000001; LiRA composto=0.500249</t>
+          <t>LiRA medio=0.5001295; Yeom medio=0.49683259053359585; Shadow medio=0.49730420000000003; LiRA composto=0.49799</t>
         </is>
       </c>
       <c r="K297" s="3" t="inlineStr">
@@ -23393,7 +23393,7 @@
     <row r="298" ht="90" customHeight="1">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_101922.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_022133.json</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997687; Yeom medio=0.5006942539356262; Shadow medio=0.5027999999999999; LiRA composto=0.502273</t>
+          <t>LiRA medio=0.5002134; Yeom medio=0.4992528097560955; Shadow medio=0.5018565999999999; LiRA composto=0.496275</t>
         </is>
       </c>
       <c r="K298" s="3" t="inlineStr">
@@ -23466,6 +23466,237 @@
       </c>
       <c r="P298" s="3" t="n"/>
       <c r="Q298" s="3" t="n"/>
+    </row>
+    <row r="299" ht="90" customHeight="1">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_045959.json</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I299" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J299" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49730750000000007; Yeom medio=0.5013561115504457; Shadow medio=0.502413; LiRA composto=0.494383</t>
+        </is>
+      </c>
+      <c r="K299" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L299" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M299" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N299" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O299" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P299" s="3" t="n"/>
+      <c r="Q299" s="3" t="n"/>
+    </row>
+    <row r="300" ht="90" customHeight="1">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_073901.json</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I300" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J300" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5003536000000001; Yeom medio=0.5037016364627064; Shadow medio=0.5024371000000001; LiRA composto=0.500249</t>
+        </is>
+      </c>
+      <c r="K300" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L300" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M300" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N300" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O300" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P300" s="3" t="n"/>
+      <c r="Q300" s="3" t="n"/>
+    </row>
+    <row r="301" ht="90" customHeight="1">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_101922.json</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I301" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J301" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4997687; Yeom medio=0.5006942539356262; Shadow medio=0.5027999999999999; LiRA composto=0.502273</t>
+        </is>
+      </c>
+      <c r="K301" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L301" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M301" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N301" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O301" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P301" s="3" t="n"/>
+      <c r="Q301" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q301"/>
+  <dimension ref="A1:Q314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22084,7 +22084,7 @@
     <row r="281" ht="90" customHeight="1">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: _prova_recorddp_v2/experiment_20260924_211919.json</t>
+          <t>rq1-recorddp-nm2/experiment_20260927_125021.json</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.63230810316934</t>
         </is>
       </c>
       <c r="D281" s="3" t="n">
@@ -22112,12 +22112,12 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.63230810316934; per client {'caltech': 1.8109317519571746, 'jpl': 1.750471696160897, 'office1': 9.63230810316934}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I281" s="3" t="inlineStr">
@@ -22127,7 +22127,7 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002141000000001; Yeom medio=0.4970069971772901; Shadow medio=0.49694009999999994; LiRA composto=0.504325</t>
+          <t>LiRA medio=0.4977994; Yeom medio=0.49728623226464047; Shadow medio=0.4971867; LiRA composto=0.495858</t>
         </is>
       </c>
       <c r="K281" s="3" t="inlineStr">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/_prova_recorddp_v2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M281" s="4" t="inlineStr">
@@ -22152,7 +22152,7 @@
       </c>
       <c r="O281" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 2c4a0f0 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 4c0d0ae registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P281" s="3" t="n"/>
@@ -22161,7 +22161,7 @@
     <row r="282" ht="90" customHeight="1">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_153736.json</t>
+          <t>rq1-recorddp-nm2/experiment_20260927_160817.json</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -22171,11 +22171,11 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.693293393201937</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
@@ -22184,17 +22184,17 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H282" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.693293393201937; per client {'jpl': 1.7515915716837684, 'caltech': 1.8091145219783331, 'office1': 9.693293393201937}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I282" s="3" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993168; Yeom medio=0.49919633623488513; Shadow medio=0.4999852000000001; LiRA composto=0.494312</t>
+          <t>LiRA medio=0.4986994; Yeom medio=0.5001763868650823; Shadow medio=0.5020958999999999; LiRA composto=0.49809</t>
         </is>
       </c>
       <c r="K282" s="3" t="inlineStr">
@@ -22214,7 +22214,7 @@
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M282" s="4" t="inlineStr">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="O282" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 4c0d0ae registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P282" s="3" t="n"/>
@@ -22238,7 +22238,7 @@
     <row r="283" ht="90" customHeight="1">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_181736.json</t>
+          <t>rq1-recorddp-nm2/experiment_20260927_194314.json</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -22248,11 +22248,11 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.860816931004031</t>
         </is>
       </c>
       <c r="D283" s="3" t="n">
-        <v>123</v>
+        <v>456</v>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
@@ -22261,17 +22261,17 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H283" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.860816931004031; per client {'jpl': 1.751309421173937, 'office1': 9.860816931004031, 'caltech': 1.8091933482207765}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I283" s="3" t="inlineStr">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007422; Yeom medio=0.49949077445719875; Shadow medio=0.5016429; LiRA composto=0.500728</t>
+          <t>LiRA medio=0.4989871; Yeom medio=0.501025303926631; Shadow medio=0.5023925000000001; LiRA composto=0.498166</t>
         </is>
       </c>
       <c r="K283" s="3" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="L283" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M283" s="4" t="inlineStr">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="O283" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit fe22124 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P283" s="3" t="n"/>
@@ -22315,7 +22315,7 @@
     <row r="284" ht="90" customHeight="1">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_205828.json</t>
+          <t>altre_macchine: _prova_recorddp_v2/experiment_20260924_211919.json</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -22325,11 +22325,11 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
@@ -22338,17 +22338,17 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I284" s="3" t="inlineStr">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5024474999999999; Yeom medio=0.500957717462529; Shadow medio=0.5006991999999999; LiRA composto=0.510864</t>
+          <t>LiRA medio=0.5002141000000001; Yeom medio=0.4970069971772901; Shadow medio=0.49694009999999994; LiRA composto=0.504325</t>
         </is>
       </c>
       <c r="K284" s="3" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/_prova_recorddp_v2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M284" s="4" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="O284" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 2c4a0f0 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P284" s="3" t="n"/>
@@ -22392,7 +22392,7 @@
     <row r="285" ht="90" customHeight="1">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_233900.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_153736.json</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988184000000001; Yeom medio=0.5006017002808242; Shadow medio=0.5012987000000001; LiRA composto=0.49605</t>
+          <t>LiRA medio=0.4993168; Yeom medio=0.49919633623488513; Shadow medio=0.4999852000000001; LiRA composto=0.494312</t>
         </is>
       </c>
       <c r="K285" s="3" t="inlineStr">
@@ -22469,7 +22469,7 @@
     <row r="286" ht="90" customHeight="1">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260926_021820.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_181736.json</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -22483,7 +22483,7 @@
         </is>
       </c>
       <c r="D286" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4990908; Yeom medio=0.5012730588018359; Shadow medio=0.5016101; LiRA composto=0.49656</t>
+          <t>LiRA medio=0.5007422; Yeom medio=0.49949077445719875; Shadow medio=0.5016429; LiRA composto=0.500728</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr">
@@ -22546,7 +22546,7 @@
     <row r="287" ht="90" customHeight="1">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_125958.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_205828.json</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -22556,11 +22556,11 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
@@ -22574,12 +22574,12 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I287" s="3" t="inlineStr">
@@ -22589,7 +22589,7 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000165000000001; Yeom medio=0.49860830175646453; Shadow medio=0.49871509999999997; LiRA composto=0.501325</t>
+          <t>LiRA medio=0.5024474999999999; Yeom medio=0.500957717462529; Shadow medio=0.5006991999999999; LiRA composto=0.510864</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr">
@@ -22599,7 +22599,7 @@
       </c>
       <c r="L287" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M287" s="4" t="inlineStr">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="O287" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P287" s="3" t="n"/>
@@ -22623,7 +22623,7 @@
     <row r="288" ht="90" customHeight="1">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_154115.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_233900.json</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -22633,11 +22633,11 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
@@ -22651,12 +22651,12 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H288" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I288" s="3" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49547470000000005; Yeom medio=0.4998060941716229; Shadow medio=0.5016756000000001; LiRA composto=0.493375</t>
+          <t>LiRA medio=0.4988184000000001; Yeom medio=0.5006017002808242; Shadow medio=0.5012987000000001; LiRA composto=0.49605</t>
         </is>
       </c>
       <c r="K288" s="3" t="inlineStr">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M288" s="4" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="O288" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P288" s="3" t="n"/>
@@ -22700,7 +22700,7 @@
     <row r="289" ht="90" customHeight="1">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_182128.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260926_021820.json</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -22710,11 +22710,11 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>456</v>
+        <v>1234</v>
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
@@ -22728,12 +22728,12 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I289" s="3" t="inlineStr">
@@ -22743,7 +22743,7 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49985480000000004; Yeom medio=0.5061390053404418; Shadow medio=0.5038358; LiRA composto=0.500351</t>
+          <t>LiRA medio=0.4990908; Yeom medio=0.5012730588018359; Shadow medio=0.5016101; LiRA composto=0.49656</t>
         </is>
       </c>
       <c r="K289" s="3" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M289" s="4" t="inlineStr">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="O289" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P289" s="3" t="n"/>
@@ -22777,7 +22777,7 @@
     <row r="290" ht="90" customHeight="1">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_210136.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_125958.json</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -22791,7 +22791,7 @@
         </is>
       </c>
       <c r="D290" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991365; Yeom medio=0.5003720274583884; Shadow medio=0.5009321000000001; LiRA composto=0.496163</t>
+          <t>LiRA medio=0.5000165000000001; Yeom medio=0.49860830175646453; Shadow medio=0.49871509999999997; LiRA composto=0.501325</t>
         </is>
       </c>
       <c r="K290" s="3" t="inlineStr">
@@ -22854,7 +22854,7 @@
     <row r="291" ht="90" customHeight="1">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_234138.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_154115.json</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -22868,7 +22868,7 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5021373; Yeom medio=0.5007196890101487; Shadow medio=0.5010036; LiRA composto=0.505533</t>
+          <t>LiRA medio=0.49547470000000005; Yeom medio=0.4998060941716229; Shadow medio=0.5016756000000001; LiRA composto=0.493375</t>
         </is>
       </c>
       <c r="K291" s="3" t="inlineStr">
@@ -22931,7 +22931,7 @@
     <row r="292" ht="90" customHeight="1">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_021212.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_182128.json</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -22941,11 +22941,11 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
@@ -22959,12 +22959,12 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H292" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I292" s="3" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49871699999999997; Yeom medio=0.4992244148810894; Shadow medio=0.49964450000000016; LiRA composto=0.501071</t>
+          <t>LiRA medio=0.49985480000000004; Yeom medio=0.5061390053404418; Shadow medio=0.5038358; LiRA composto=0.500351</t>
         </is>
       </c>
       <c r="K292" s="3" t="inlineStr">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M292" s="4" t="inlineStr">
@@ -22999,7 +22999,7 @@
       </c>
       <c r="O292" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P292" s="3" t="n"/>
@@ -23008,7 +23008,7 @@
     <row r="293" ht="90" customHeight="1">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_045650.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_210136.json</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -23018,11 +23018,11 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D293" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
@@ -23036,12 +23036,12 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I293" s="3" t="inlineStr">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997273; Yeom medio=0.5001001052322953; Shadow medio=0.5016489; LiRA composto=0.502277</t>
+          <t>LiRA medio=0.4991365; Yeom medio=0.5003720274583884; Shadow medio=0.5009321000000001; LiRA composto=0.496163</t>
         </is>
       </c>
       <c r="K293" s="3" t="inlineStr">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="L293" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M293" s="4" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="O293" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P293" s="3" t="n"/>
@@ -23085,7 +23085,7 @@
     <row r="294" ht="90" customHeight="1">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_073952.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_234138.json</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -23095,11 +23095,11 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>456</v>
+        <v>1234</v>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
@@ -23113,12 +23113,12 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H294" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I294" s="3" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.5027887367096913; Shadow medio=0.5029678000000001; LiRA composto=0.503597</t>
+          <t>LiRA medio=0.5021373; Yeom medio=0.5007196890101487; Shadow medio=0.5010036; LiRA composto=0.505533</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
@@ -23138,7 +23138,7 @@
       </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M294" s="4" t="inlineStr">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="O294" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P294" s="3" t="n"/>
@@ -23162,7 +23162,7 @@
     <row r="295" ht="90" customHeight="1">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_101906.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_021212.json</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="D295" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000697; Yeom medio=0.4992625830796393; Shadow medio=0.5006257; LiRA composto=0.50064</t>
+          <t>LiRA medio=0.49871699999999997; Yeom medio=0.4992244148810894; Shadow medio=0.49964450000000016; LiRA composto=0.501071</t>
         </is>
       </c>
       <c r="K295" s="3" t="inlineStr">
@@ -23239,7 +23239,7 @@
     <row r="296" ht="90" customHeight="1">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_125758.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_045650.json</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -23253,7 +23253,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010308; Yeom medio=0.5012359131513038; Shadow medio=0.5019937999999999; LiRA composto=0.499856</t>
+          <t>LiRA medio=0.4997273; Yeom medio=0.5001001052322953; Shadow medio=0.5016489; LiRA composto=0.502277</t>
         </is>
       </c>
       <c r="K296" s="3" t="inlineStr">
@@ -23316,7 +23316,7 @@
     <row r="297" ht="90" customHeight="1">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260922_234305.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_073952.json</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -23326,11 +23326,11 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
@@ -23344,12 +23344,12 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H297" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I297" s="3" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001295; Yeom medio=0.49683259053359585; Shadow medio=0.49730420000000003; LiRA composto=0.49799</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.5027887367096913; Shadow medio=0.5029678000000001; LiRA composto=0.503597</t>
         </is>
       </c>
       <c r="K297" s="3" t="inlineStr">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="L297" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M297" s="4" t="inlineStr">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="O297" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P297" s="3" t="n"/>
@@ -23393,7 +23393,7 @@
     <row r="298" ht="90" customHeight="1">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_022133.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_101906.json</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -23403,11 +23403,11 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>123</v>
+        <v>789</v>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
@@ -23421,12 +23421,12 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H298" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I298" s="3" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002134; Yeom medio=0.4992528097560955; Shadow medio=0.5018565999999999; LiRA composto=0.496275</t>
+          <t>LiRA medio=0.5000697; Yeom medio=0.4992625830796393; Shadow medio=0.5006257; LiRA composto=0.50064</t>
         </is>
       </c>
       <c r="K298" s="3" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="L298" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="O298" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P298" s="3" t="n"/>
@@ -23470,7 +23470,7 @@
     <row r="299" ht="90" customHeight="1">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_045959.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_125758.json</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -23480,11 +23480,11 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>456</v>
+        <v>1234</v>
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
@@ -23498,12 +23498,12 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H299" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I299" s="3" t="inlineStr">
@@ -23513,7 +23513,7 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49730750000000007; Yeom medio=0.5013561115504457; Shadow medio=0.502413; LiRA composto=0.494383</t>
+          <t>LiRA medio=0.5010308; Yeom medio=0.5012359131513038; Shadow medio=0.5019937999999999; LiRA composto=0.499856</t>
         </is>
       </c>
       <c r="K299" s="3" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="L299" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="O299" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P299" s="3" t="n"/>
@@ -23547,7 +23547,7 @@
     <row r="300" ht="90" customHeight="1">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_073901.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260922_234305.json</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -23561,7 +23561,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>789</v>
+        <v>42</v>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003536000000001; Yeom medio=0.5037016364627064; Shadow medio=0.5024371000000001; LiRA composto=0.500249</t>
+          <t>LiRA medio=0.5001295; Yeom medio=0.49683259053359585; Shadow medio=0.49730420000000003; LiRA composto=0.49799</t>
         </is>
       </c>
       <c r="K300" s="3" t="inlineStr">
@@ -23624,7 +23624,7 @@
     <row r="301" ht="90" customHeight="1">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_101922.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_022133.json</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
@@ -23638,7 +23638,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>1234</v>
+        <v>123</v>
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997687; Yeom medio=0.5006942539356262; Shadow medio=0.5027999999999999; LiRA composto=0.502273</t>
+          <t>LiRA medio=0.5002134; Yeom medio=0.4992528097560955; Shadow medio=0.5018565999999999; LiRA composto=0.496275</t>
         </is>
       </c>
       <c r="K301" s="3" t="inlineStr">
@@ -23697,6 +23697,1007 @@
       </c>
       <c r="P301" s="3" t="n"/>
       <c r="Q301" s="3" t="n"/>
+    </row>
+    <row r="302" ht="90" customHeight="1">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_045959.json</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I302" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J302" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49730750000000007; Yeom medio=0.5013561115504457; Shadow medio=0.502413; LiRA composto=0.494383</t>
+        </is>
+      </c>
+      <c r="K302" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L302" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M302" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N302" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O302" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P302" s="3" t="n"/>
+      <c r="Q302" s="3" t="n"/>
+    </row>
+    <row r="303" ht="90" customHeight="1">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_073901.json</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I303" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J303" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5003536000000001; Yeom medio=0.5037016364627064; Shadow medio=0.5024371000000001; LiRA composto=0.500249</t>
+        </is>
+      </c>
+      <c r="K303" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L303" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M303" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N303" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O303" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P303" s="3" t="n"/>
+      <c r="Q303" s="3" t="n"/>
+    </row>
+    <row r="304" ht="90" customHeight="1">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_101922.json</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I304" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J304" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4997687; Yeom medio=0.5006942539356262; Shadow medio=0.5027999999999999; LiRA composto=0.502273</t>
+        </is>
+      </c>
+      <c r="K304" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L304" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M304" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N304" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O304" s="3" t="inlineStr">
+        <is>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P304" s="3" t="n"/>
+      <c r="Q304" s="3" t="n"/>
+    </row>
+    <row r="305" ht="90" customHeight="1">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260924_165648.json</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J305" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5015818; Yeom medio=0.4964074975793191; Shadow medio=0.49682729999999997; LiRA composto=0.503803</t>
+        </is>
+      </c>
+      <c r="K305" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L305" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M305" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N305" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O305" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P305" s="3" t="n"/>
+      <c r="Q305" s="3" t="n"/>
+    </row>
+    <row r="306" ht="90" customHeight="1">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260924_221235.json</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I306" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J306" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5004695; Yeom medio=0.4989074674027784; Shadow medio=0.5014131; LiRA composto=0.502175</t>
+        </is>
+      </c>
+      <c r="K306" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L306" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M306" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N306" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O306" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P306" s="3" t="n"/>
+      <c r="Q306" s="3" t="n"/>
+    </row>
+    <row r="307" ht="90" customHeight="1">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260925_032646.json</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I307" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J307" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49852079999999993; Yeom medio=0.5012063210441634; Shadow medio=0.5031516999999999; LiRA composto=0.499601</t>
+        </is>
+      </c>
+      <c r="K307" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L307" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M307" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N307" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O307" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P307" s="3" t="n"/>
+      <c r="Q307" s="3" t="n"/>
+    </row>
+    <row r="308" ht="90" customHeight="1">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260925_084437.json</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I308" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J308" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49975250000000004; Yeom medio=0.5038203772885959; Shadow medio=0.5022984; LiRA composto=0.501778</t>
+        </is>
+      </c>
+      <c r="K308" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L308" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M308" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N308" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O308" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P308" s="3" t="n"/>
+      <c r="Q308" s="3" t="n"/>
+    </row>
+    <row r="309" ht="90" customHeight="1">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260925_133815.json</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I309" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J309" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4984249; Yeom medio=0.5007472539951816; Shadow medio=0.5031239000000001; LiRA composto=0.50021</t>
+        </is>
+      </c>
+      <c r="K309" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L309" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M309" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N309" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O309" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P309" s="3" t="n"/>
+      <c r="Q309" s="3" t="n"/>
+    </row>
+    <row r="310" ht="90" customHeight="1">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260924_164137.json</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I310" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J310" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49936689999999995; Yeom medio=0.49896478232850994; Shadow medio=0.499537; LiRA composto=0.501141</t>
+        </is>
+      </c>
+      <c r="K310" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L310" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M310" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N310" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O310" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P310" s="3" t="n"/>
+      <c r="Q310" s="3" t="n"/>
+    </row>
+    <row r="311" ht="90" customHeight="1">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260924_214509.json</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I311" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J311" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5018366; Yeom medio=0.4994514143625247; Shadow medio=0.49923510000000004; LiRA composto=0.501229</t>
+        </is>
+      </c>
+      <c r="K311" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L311" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M311" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N311" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O311" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P311" s="3" t="n"/>
+      <c r="Q311" s="3" t="n"/>
+    </row>
+    <row r="312" ht="90" customHeight="1">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260925_024537.json</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I312" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J312" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49861310000000003; Yeom medio=0.500195309199002; Shadow medio=0.4969758000000001; LiRA composto=0.494877</t>
+        </is>
+      </c>
+      <c r="K312" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L312" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M312" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N312" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O312" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P312" s="3" t="n"/>
+      <c r="Q312" s="3" t="n"/>
+    </row>
+    <row r="313" ht="90" customHeight="1">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260925_074700.json</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H313" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I313" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J313" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5010486000000001; Yeom medio=0.5041437448294415; Shadow medio=0.5024178; LiRA composto=0.501158</t>
+        </is>
+      </c>
+      <c r="K313" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L313" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M313" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N313" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O313" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P313" s="3" t="n"/>
+      <c r="Q313" s="3" t="n"/>
+    </row>
+    <row r="314" ht="90" customHeight="1">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260925_124719.json</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J314" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5002865; Yeom medio=0.49920311493345915; Shadow medio=0.4992279; LiRA composto=0.505826</t>
+        </is>
+      </c>
+      <c r="K314" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L314" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M314" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N314" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O314" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P314" s="3" t="n"/>
+      <c r="Q314" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>

--- a/risultati/matrice_run_completati.xlsx
+++ b/risultati/matrice_run_completati.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q314"/>
+  <dimension ref="A1:Q321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -21699,7 +21699,7 @@
     <row r="276" ht="90" customHeight="1">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>rq1-recorddp-nm1/experiment_20260926_115832.json</t>
+          <t>rq1-nodp-groupnorm/experiment_20260928_035419.json</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -21709,11 +21709,11 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.391161900463153</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
@@ -21722,17 +21722,17 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H276" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.391161900463153; per client {'jpl': 4.827360389586961, 'caltech': 4.9961384863040035, 'office1': 30.391161900463153}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I276" s="3" t="inlineStr">
@@ -21742,7 +21742,7 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5006242999999999; Yeom medio=0.5014409510198713; Shadow medio=0.5029617; LiRA composto=0.497648</t>
+          <t>LiRA medio=0.4994884999999999; Yeom medio=0.49873058878225; Shadow medio=0.4968308; LiRA composto=0.495753</t>
         </is>
       </c>
       <c r="K276" s="3" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-nodp-groupnorm/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M276" s="4" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="O276" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 0dedd34 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 42b4561 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P276" s="3" t="n"/>
@@ -21776,7 +21776,7 @@
     <row r="277" ht="90" customHeight="1">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>rq1-recorddp-nm1/experiment_20260926_151825.json</t>
+          <t>rq1-nodp-groupnorm/experiment_20260928_052405.json</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -21786,11 +21786,11 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.975180902516065</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D277" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
@@ -21799,17 +21799,17 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.975180902516065; per client {'jpl': 4.826504114513053, 'office1': 30.975180902516065, 'caltech': 4.996366486983374}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I277" s="3" t="inlineStr">
@@ -21819,7 +21819,7 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002221; Yeom medio=0.5017294522289747; Shadow medio=0.5031289; LiRA composto=0.502612</t>
+          <t>LiRA medio=0.5013506000000001; Yeom medio=0.5008941827150585; Shadow medio=0.5034065; LiRA composto=0.503182</t>
         </is>
       </c>
       <c r="K277" s="3" t="inlineStr">
@@ -21829,7 +21829,7 @@
       </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-nodp-groupnorm/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M277" s="4" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="O277" s="3" t="inlineStr">
         <is>
-          <t>commit 1519d16 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 42b4561 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P277" s="3" t="n"/>
@@ -21853,7 +21853,7 @@
     <row r="278" ht="90" customHeight="1">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>rq1-recorddp-nm1/experiment_20260926_183757.json</t>
+          <t>rq1-nodp-groupnorm/experiment_20260928_065550.json</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -21863,11 +21863,11 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.355490267392394</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
@@ -21876,17 +21876,17 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.355490267392394; per client {'jpl': 4.817642925378795, 'caltech': 5.0071752295132805, 'office1': 30.355490267392394}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I278" s="3" t="inlineStr">
@@ -21896,7 +21896,7 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.499089; Yeom medio=0.5014118506681772; Shadow medio=0.5040574; LiRA composto=0.497402</t>
+          <t>LiRA medio=0.5006071000000001; Yeom medio=0.5013070584532202; Shadow medio=0.5037297; LiRA composto=0.499847</t>
         </is>
       </c>
       <c r="K278" s="3" t="inlineStr">
@@ -21906,7 +21906,7 @@
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-nodp-groupnorm/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M278" s="4" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="O278" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 42b4561 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P278" s="3" t="n"/>
@@ -21930,7 +21930,7 @@
     <row r="279" ht="90" customHeight="1">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>rq1-recorddp-nm1/experiment_20260926_215557.json</t>
+          <t>rq1-nodp-groupnorm/experiment_20260928_082939.json</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -21940,11 +21940,11 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.355490267392394</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D279" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
@@ -21953,17 +21953,17 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.355490267392394; per client {'jpl': 4.817862945887583, 'caltech': 5.006927312510939, 'office1': 30.355490267392394}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5016651; Yeom medio=0.5017909056517103; Shadow medio=0.5036755; LiRA composto=0.502849</t>
+          <t>LiRA medio=0.5013195; Yeom medio=0.5011417235881787; Shadow medio=0.5005981; LiRA composto=0.502711</t>
         </is>
       </c>
       <c r="K279" s="3" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-nodp-groupnorm/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M279" s="4" t="inlineStr">
@@ -21998,7 +21998,7 @@
       </c>
       <c r="O279" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 42b4561 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P279" s="3" t="n"/>
@@ -22007,7 +22007,7 @@
     <row r="280" ht="90" customHeight="1">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>rq1-recorddp-nm1/experiment_20260927_011250.json</t>
+          <t>rq1-nodp-groupnorm/experiment_20260928_100217.json</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -22017,11 +22017,11 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
@@ -22030,17 +22030,17 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>naturale — record-DP</t>
+          <t>naturale</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I280" s="3" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003566; Yeom medio=0.49700702441902517; Shadow medio=0.4969783; LiRA composto=0.502476</t>
+          <t>LiRA medio=0.49984540000000005; Yeom medio=0.4997220806603738; Shadow medio=0.5012742; LiRA composto=0.50181</t>
         </is>
       </c>
       <c r="K280" s="3" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-nodp-groupnorm/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M280" s="4" t="inlineStr">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="O280" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 42b4561 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P280" s="3" t="n"/>
@@ -22084,7 +22084,7 @@
     <row r="281" ht="90" customHeight="1">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>rq1-recorddp-nm2/experiment_20260927_125021.json</t>
+          <t>rq1-recorddp-nm1/experiment_20260926_115832.json</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -22094,11 +22094,11 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.63230810316934</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.391161900463153</t>
         </is>
       </c>
       <c r="D281" s="3" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
@@ -22112,12 +22112,12 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.63230810316934; per client {'caltech': 1.8109317519571746, 'jpl': 1.750471696160897, 'office1': 9.63230810316934}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.391161900463153; per client {'jpl': 4.827360389586961, 'caltech': 4.9961384863040035, 'office1': 30.391161900463153}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I281" s="3" t="inlineStr">
@@ -22127,7 +22127,7 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4977994; Yeom medio=0.49728623226464047; Shadow medio=0.4971867; LiRA composto=0.495858</t>
+          <t>LiRA medio=0.5006242999999999; Yeom medio=0.5014409510198713; Shadow medio=0.5029617; LiRA composto=0.497648</t>
         </is>
       </c>
       <c r="K281" s="3" t="inlineStr">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M281" s="4" t="inlineStr">
@@ -22152,7 +22152,7 @@
       </c>
       <c r="O281" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 4c0d0ae registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 0dedd34 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P281" s="3" t="n"/>
@@ -22161,7 +22161,7 @@
     <row r="282" ht="90" customHeight="1">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>rq1-recorddp-nm2/experiment_20260927_160817.json</t>
+          <t>rq1-recorddp-nm1/experiment_20260926_151825.json</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -22171,11 +22171,11 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.693293393201937</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.975180902516065</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
-        <v>123</v>
+        <v>456</v>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
@@ -22189,12 +22189,12 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H282" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.693293393201937; per client {'jpl': 1.7515915716837684, 'caltech': 1.8091145219783331, 'office1': 9.693293393201937}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.975180902516065; per client {'jpl': 4.826504114513053, 'office1': 30.975180902516065, 'caltech': 4.996366486983374}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I282" s="3" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4986994; Yeom medio=0.5001763868650823; Shadow medio=0.5020958999999999; LiRA composto=0.49809</t>
+          <t>LiRA medio=0.5002221; Yeom medio=0.5017294522289747; Shadow medio=0.5031289; LiRA composto=0.502612</t>
         </is>
       </c>
       <c r="K282" s="3" t="inlineStr">
@@ -22214,7 +22214,7 @@
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M282" s="4" t="inlineStr">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="O282" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 4c0d0ae registrato, hash degli split non registrato</t>
+          <t>commit 1519d16 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
         </is>
       </c>
       <c r="P282" s="3" t="n"/>
@@ -22238,7 +22238,7 @@
     <row r="283" ht="90" customHeight="1">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>rq1-recorddp-nm2/experiment_20260927_194314.json</t>
+          <t>rq1-recorddp-nm1/experiment_20260926_183757.json</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -22248,11 +22248,11 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.860816931004031</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.355490267392394</t>
         </is>
       </c>
       <c r="D283" s="3" t="n">
-        <v>456</v>
+        <v>789</v>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
@@ -22266,12 +22266,12 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H283" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.860816931004031; per client {'jpl': 1.751309421173937, 'office1': 9.860816931004031, 'caltech': 1.8091933482207765}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.355490267392394; per client {'jpl': 4.817642925378795, 'caltech': 5.0071752295132805, 'office1': 30.355490267392394}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I283" s="3" t="inlineStr">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4989871; Yeom medio=0.501025303926631; Shadow medio=0.5023925000000001; LiRA composto=0.498166</t>
+          <t>LiRA medio=0.499089; Yeom medio=0.5014118506681772; Shadow medio=0.5040574; LiRA composto=0.497402</t>
         </is>
       </c>
       <c r="K283" s="3" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="L283" s="3" t="inlineStr">
         <is>
-          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M283" s="4" t="inlineStr">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="O283" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit fe22124 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P283" s="3" t="n"/>
@@ -22315,7 +22315,7 @@
     <row r="284" ht="90" customHeight="1">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: _prova_recorddp_v2/experiment_20260924_211919.json</t>
+          <t>rq1-recorddp-nm1/experiment_20260926_215557.json</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -22325,11 +22325,11 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.355490267392394</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.355490267392394; per client {'jpl': 4.817862945887583, 'caltech': 5.006927312510939, 'office1': 30.355490267392394}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I284" s="3" t="inlineStr">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002141000000001; Yeom medio=0.4970069971772901; Shadow medio=0.49694009999999994; LiRA composto=0.504325</t>
+          <t>LiRA medio=0.5016651; Yeom medio=0.5017909056517103; Shadow medio=0.5036755; LiRA composto=0.502849</t>
         </is>
       </c>
       <c r="K284" s="3" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/_prova_recorddp_v2/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M284" s="4" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="O284" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 2c4a0f0 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P284" s="3" t="n"/>
@@ -22392,7 +22392,7 @@
     <row r="285" ht="90" customHeight="1">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_153736.json</t>
+          <t>rq1-recorddp-nm1/experiment_20260927_011250.json</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
         </is>
       </c>
       <c r="D285" s="3" t="n">
@@ -22415,17 +22415,17 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I285" s="3" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4993168; Yeom medio=0.49919633623488513; Shadow medio=0.4999852000000001; LiRA composto=0.494312</t>
+          <t>LiRA medio=0.5003566; Yeom medio=0.49700702441902517; Shadow medio=0.4969783; LiRA composto=0.502476</t>
         </is>
       </c>
       <c r="K285" s="3" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm1/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M285" s="4" t="inlineStr">
@@ -22460,7 +22460,7 @@
       </c>
       <c r="O285" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 943c795 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P285" s="3" t="n"/>
@@ -22469,7 +22469,7 @@
     <row r="286" ht="90" customHeight="1">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_181736.json</t>
+          <t>rq1-recorddp-nm2/experiment_20260927_125021.json</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -22479,11 +22479,11 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.63230810316934</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
@@ -22492,17 +22492,17 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H286" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.63230810316934; per client {'caltech': 1.8109317519571746, 'jpl': 1.750471696160897, 'office1': 9.63230810316934}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I286" s="3" t="inlineStr">
@@ -22512,7 +22512,7 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5007422; Yeom medio=0.49949077445719875; Shadow medio=0.5016429; LiRA composto=0.500728</t>
+          <t>LiRA medio=0.4977994; Yeom medio=0.49728623226464047; Shadow medio=0.4971867; LiRA composto=0.495858</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M286" s="4" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="O286" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 4c0d0ae registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P286" s="3" t="n"/>
@@ -22546,7 +22546,7 @@
     <row r="287" ht="90" customHeight="1">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_205828.json</t>
+          <t>rq1-recorddp-nm2/experiment_20260927_160817.json</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -22556,11 +22556,11 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.693293393201937</t>
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>456</v>
+        <v>123</v>
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
@@ -22569,17 +22569,17 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.693293393201937; per client {'jpl': 1.7515915716837684, 'caltech': 1.8091145219783331, 'office1': 9.693293393201937}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I287" s="3" t="inlineStr">
@@ -22589,7 +22589,7 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5024474999999999; Yeom medio=0.500957717462529; Shadow medio=0.5006991999999999; LiRA composto=0.510864</t>
+          <t>LiRA medio=0.4986994; Yeom medio=0.5001763868650823; Shadow medio=0.5020958999999999; LiRA composto=0.49809</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr">
@@ -22599,7 +22599,7 @@
       </c>
       <c r="L287" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M287" s="4" t="inlineStr">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="O287" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 4c0d0ae registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P287" s="3" t="n"/>
@@ -22623,7 +22623,7 @@
     <row r="288" ht="90" customHeight="1">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_233900.json</t>
+          <t>rq1-recorddp-nm2/experiment_20260927_194314.json</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -22633,11 +22633,11 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.860816931004031</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>789</v>
+        <v>456</v>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
@@ -22646,17 +22646,17 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H288" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.860816931004031; per client {'jpl': 1.751309421173937, 'office1': 9.860816931004031, 'caltech': 1.8091933482207765}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I288" s="3" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4988184000000001; Yeom medio=0.5006017002808242; Shadow medio=0.5012987000000001; LiRA composto=0.49605</t>
+          <t>LiRA medio=0.4989871; Yeom medio=0.501025303926631; Shadow medio=0.5023925000000001; LiRA composto=0.498166</t>
         </is>
       </c>
       <c r="K288" s="3" t="inlineStr">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M288" s="4" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="O288" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit fe22124 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P288" s="3" t="n"/>
@@ -22700,7 +22700,7 @@
     <row r="289" ht="90" customHeight="1">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid-eps64/experiment_20260926_021820.json</t>
+          <t>rq1-recorddp-nm2/experiment_20260927_230317.json</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -22710,11 +22710,11 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.683852357550279</t>
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>1234</v>
+        <v>789</v>
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
@@ -22723,17 +22723,17 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.683852357550279; per client {'jpl': 1.7483113834837356, 'caltech': 1.8129157287561077, 'office1': 9.683852357550279}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I289" s="3" t="inlineStr">
@@ -22743,7 +22743,7 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4990908; Yeom medio=0.5012730588018359; Shadow medio=0.5016101; LiRA composto=0.49656</t>
+          <t>LiRA medio=0.5002664; Yeom medio=0.5022091095362593; Shadow medio=0.5044535; LiRA composto=0.498205</t>
         </is>
       </c>
       <c r="K289" s="3" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M289" s="4" t="inlineStr">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="O289" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 42b4561 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P289" s="3" t="n"/>
@@ -22777,7 +22777,7 @@
     <row r="290" ht="90" customHeight="1">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_125958.json</t>
+          <t>rq1-recorddp-nm2/experiment_20260928_022227.json</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -22787,11 +22787,11 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=2.0, eps_record_dp=9.683852357550279</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
-        <v>42</v>
+        <v>1234</v>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
@@ -22800,17 +22800,17 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 2.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 9.683852357550279; per client {'jpl': 1.7483818947557892, 'caltech': 1.812834850636869, 'office1': 9.683852357550279}; limite con lo shuffle, adiacenza per sostituzione = 354.8612600716533; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I290" s="3" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000165000000001; Yeom medio=0.49860830175646453; Shadow medio=0.49871509999999997; LiRA composto=0.501325</t>
+          <t>LiRA medio=0.49847410000000003; Yeom medio=0.5010818998952283; Shadow medio=0.5034382000000001; LiRA composto=0.496983</t>
         </is>
       </c>
       <c r="K290" s="3" t="inlineStr">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments/rq1-recorddp-nm2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M290" s="4" t="inlineStr">
@@ -22845,7 +22845,7 @@
       </c>
       <c r="O290" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 42b4561 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P290" s="3" t="n"/>
@@ -22854,7 +22854,7 @@
     <row r="291" ht="90" customHeight="1">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_154115.json</t>
+          <t>altre_macchine: _prova_recorddp_v2/experiment_20260924_211919.json</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -22864,11 +22864,11 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4; record_dp: enabled=True, nm=1.0, eps_record_dp=30.174964645722884</t>
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
@@ -22877,17 +22877,17 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>naturale</t>
+          <t>naturale — record-DP</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>record-level — update da DP-SGD (clipping per esempio C = 1.0, sigma = 1.0), nessun meccanismo client-level</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>record-DP, accountant RDP (dp-accounting): eps per record di Poisson, massimo sui client = 30.174964645722884; per client {'caltech': 5.001408630147912, 'jpl': 4.82403488410546, 'office1': 30.174964645722884}; limite con lo shuffle, adiacenza per sostituzione = 1211.7782575788606; delta=1e-05; nessun enforcement</t>
         </is>
       </c>
       <c r="I291" s="3" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49547470000000005; Yeom medio=0.4998060941716229; Shadow medio=0.5016756000000001; LiRA composto=0.493375</t>
+          <t>LiRA medio=0.5002141000000001; Yeom medio=0.4970069971772901; Shadow medio=0.49694009999999994; LiRA composto=0.504325</t>
         </is>
       </c>
       <c r="K291" s="3" t="inlineStr">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="L291" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/_prova_recorddp_v2/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M291" s="4" t="inlineStr">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="O291" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 2c4a0f0 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P291" s="3" t="n"/>
@@ -22931,7 +22931,7 @@
     <row r="292" ht="90" customHeight="1">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_182128.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_153736.json</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -22941,11 +22941,11 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
@@ -22959,12 +22959,12 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H292" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I292" s="3" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49985480000000004; Yeom medio=0.5061390053404418; Shadow medio=0.5038358; LiRA composto=0.500351</t>
+          <t>LiRA medio=0.4993168; Yeom medio=0.49919633623488513; Shadow medio=0.4999852000000001; LiRA composto=0.494312</t>
         </is>
       </c>
       <c r="K292" s="3" t="inlineStr">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M292" s="4" t="inlineStr">
@@ -22999,7 +22999,7 @@
       </c>
       <c r="O292" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P292" s="3" t="n"/>
@@ -23008,7 +23008,7 @@
     <row r="293" ht="90" customHeight="1">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_210136.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_181736.json</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -23018,11 +23018,11 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D293" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
@@ -23036,12 +23036,12 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I293" s="3" t="inlineStr">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4991365; Yeom medio=0.5003720274583884; Shadow medio=0.5009321000000001; LiRA composto=0.496163</t>
+          <t>LiRA medio=0.5007422; Yeom medio=0.49949077445719875; Shadow medio=0.5016429; LiRA composto=0.500728</t>
         </is>
       </c>
       <c r="K293" s="3" t="inlineStr">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="L293" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M293" s="4" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="O293" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P293" s="3" t="n"/>
@@ -23085,7 +23085,7 @@
     <row r="294" ht="90" customHeight="1">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-iid/experiment_20260923_234138.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_205828.json</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -23095,11 +23095,11 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
@@ -23113,12 +23113,12 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H294" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I294" s="3" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5021373; Yeom medio=0.5007196890101487; Shadow medio=0.5010036; LiRA composto=0.505533</t>
+          <t>LiRA medio=0.5024474999999999; Yeom medio=0.500957717462529; Shadow medio=0.5006991999999999; LiRA composto=0.510864</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
@@ -23138,7 +23138,7 @@
       </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M294" s="4" t="inlineStr">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="O294" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P294" s="3" t="n"/>
@@ -23162,7 +23162,7 @@
     <row r="295" ht="90" customHeight="1">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_021212.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260925_233900.json</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="D295" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49871699999999997; Yeom medio=0.4992244148810894; Shadow medio=0.49964450000000016; LiRA composto=0.501071</t>
+          <t>LiRA medio=0.4988184000000001; Yeom medio=0.5006017002808242; Shadow medio=0.5012987000000001; LiRA composto=0.49605</t>
         </is>
       </c>
       <c r="K295" s="3" t="inlineStr">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="L295" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M295" s="4" t="inlineStr">
@@ -23239,7 +23239,7 @@
     <row r="296" ht="90" customHeight="1">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_045650.json</t>
+          <t>altre_macchine: rq2-iid-eps64/experiment_20260926_021820.json</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -23253,7 +23253,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997273; Yeom medio=0.5001001052322953; Shadow medio=0.5016489; LiRA composto=0.502277</t>
+          <t>LiRA medio=0.4990908; Yeom medio=0.5012730588018359; Shadow medio=0.5016101; LiRA composto=0.49656</t>
         </is>
       </c>
       <c r="K296" s="3" t="inlineStr">
@@ -23292,7 +23292,7 @@
       </c>
       <c r="L296" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M296" s="4" t="inlineStr">
@@ -23316,7 +23316,7 @@
     <row r="297" ht="90" customHeight="1">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_073952.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_125958.json</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -23326,11 +23326,11 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
@@ -23344,12 +23344,12 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H297" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I297" s="3" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4985705; Yeom medio=0.5027887367096913; Shadow medio=0.5029678000000001; LiRA composto=0.503597</t>
+          <t>LiRA medio=0.5000165000000001; Yeom medio=0.49860830175646453; Shadow medio=0.49871509999999997; LiRA composto=0.501325</t>
         </is>
       </c>
       <c r="K297" s="3" t="inlineStr">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="L297" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M297" s="4" t="inlineStr">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="O297" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P297" s="3" t="n"/>
@@ -23393,7 +23393,7 @@
     <row r="298" ht="90" customHeight="1">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_101906.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_154115.json</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -23403,11 +23403,11 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
@@ -23421,12 +23421,12 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H298" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I298" s="3" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5000697; Yeom medio=0.4992625830796393; Shadow medio=0.5006257; LiRA composto=0.50064</t>
+          <t>LiRA medio=0.49547470000000005; Yeom medio=0.4998060941716229; Shadow medio=0.5016756000000001; LiRA composto=0.493375</t>
         </is>
       </c>
       <c r="K298" s="3" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="L298" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="O298" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P298" s="3" t="n"/>
@@ -23470,7 +23470,7 @@
     <row r="299" ht="90" customHeight="1">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_125758.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_182128.json</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -23480,11 +23480,11 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
@@ -23498,12 +23498,12 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
         </is>
       </c>
       <c r="H299" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I299" s="3" t="inlineStr">
@@ -23513,7 +23513,7 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010308; Yeom medio=0.5012359131513038; Shadow medio=0.5019937999999999; LiRA composto=0.499856</t>
+          <t>LiRA medio=0.49985480000000004; Yeom medio=0.5061390053404418; Shadow medio=0.5038358; LiRA composto=0.500351</t>
         </is>
       </c>
       <c r="K299" s="3" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="L299" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="O299" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P299" s="3" t="n"/>
@@ -23547,7 +23547,7 @@
     <row r="300" ht="90" customHeight="1">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260922_234305.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_210136.json</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -23561,7 +23561,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5001295; Yeom medio=0.49683259053359585; Shadow medio=0.49730420000000003; LiRA composto=0.49799</t>
+          <t>LiRA medio=0.4991365; Yeom medio=0.5003720274583884; Shadow medio=0.5009321000000001; LiRA composto=0.496163</t>
         </is>
       </c>
       <c r="K300" s="3" t="inlineStr">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="L300" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
@@ -23624,7 +23624,7 @@
     <row r="301" ht="90" customHeight="1">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_022133.json</t>
+          <t>altre_macchine: rq2-iid/experiment_20260923_234138.json</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
@@ -23638,7 +23638,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002134; Yeom medio=0.4992528097560955; Shadow medio=0.5018565999999999; LiRA composto=0.496275</t>
+          <t>LiRA medio=0.5021373; Yeom medio=0.5007196890101487; Shadow medio=0.5010036; LiRA composto=0.505533</t>
         </is>
       </c>
       <c r="K301" s="3" t="inlineStr">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="L301" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-iid/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr">
@@ -23701,7 +23701,7 @@
     <row r="302" ht="90" customHeight="1">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_045959.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_021212.json</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -23711,11 +23711,11 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
@@ -23729,12 +23729,12 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H302" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I302" s="3" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49730750000000007; Yeom medio=0.5013561115504457; Shadow medio=0.502413; LiRA composto=0.494383</t>
+          <t>LiRA medio=0.49871699999999997; Yeom medio=0.4992244148810894; Shadow medio=0.49964450000000016; LiRA composto=0.501071</t>
         </is>
       </c>
       <c r="K302" s="3" t="inlineStr">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="L302" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr">
@@ -23769,7 +23769,7 @@
       </c>
       <c r="O302" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P302" s="3" t="n"/>
@@ -23778,7 +23778,7 @@
     <row r="303" ht="90" customHeight="1">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_073901.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_045650.json</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
@@ -23788,11 +23788,11 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E303" s="3" t="inlineStr">
         <is>
@@ -23806,12 +23806,12 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H303" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I303" s="3" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5003536000000001; Yeom medio=0.5037016364627064; Shadow medio=0.5024371000000001; LiRA composto=0.500249</t>
+          <t>LiRA medio=0.4997273; Yeom medio=0.5001001052322953; Shadow medio=0.5016489; LiRA composto=0.502277</t>
         </is>
       </c>
       <c r="K303" s="3" t="inlineStr">
@@ -23831,7 +23831,7 @@
       </c>
       <c r="L303" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="O303" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P303" s="3" t="n"/>
@@ -23855,7 +23855,7 @@
     <row r="304" ht="90" customHeight="1">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq2-per_site/experiment_20260923_101922.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_073952.json</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -23865,11 +23865,11 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
@@ -23883,12 +23883,12 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H304" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I304" s="3" t="inlineStr">
@@ -23898,7 +23898,7 @@
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4997687; Yeom medio=0.5006942539356262; Shadow medio=0.5027999999999999; LiRA composto=0.502273</t>
+          <t>LiRA medio=0.4985705; Yeom medio=0.5027887367096913; Shadow medio=0.5029678000000001; LiRA composto=0.503597</t>
         </is>
       </c>
       <c r="K304" s="3" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="L304" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
@@ -23923,7 +23923,7 @@
       </c>
       <c r="O304" s="3" t="inlineStr">
         <is>
-          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P304" s="3" t="n"/>
@@ -23932,7 +23932,7 @@
     <row r="305" ht="90" customHeight="1">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0.01/experiment_20260924_165648.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_101906.json</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
@@ -23942,11 +23942,11 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D305" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
@@ -23960,12 +23960,12 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H305" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I305" s="3" t="inlineStr">
@@ -23975,7 +23975,7 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5015818; Yeom medio=0.4964074975793191; Shadow medio=0.49682729999999997; LiRA composto=0.503803</t>
+          <t>LiRA medio=0.5000697; Yeom medio=0.4992625830796393; Shadow medio=0.5006257; LiRA composto=0.50064</t>
         </is>
       </c>
       <c r="K305" s="3" t="inlineStr">
@@ -23985,7 +23985,7 @@
       </c>
       <c r="L305" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr">
@@ -24000,7 +24000,7 @@
       </c>
       <c r="O305" s="3" t="inlineStr">
         <is>
-          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P305" s="3" t="n"/>
@@ -24009,7 +24009,7 @@
     <row r="306" ht="90" customHeight="1">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0.01/experiment_20260924_221235.json</t>
+          <t>altre_macchine: rq2-per_site-eps64/experiment_20260925_125758.json</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -24019,11 +24019,11 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=64.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
         </is>
       </c>
       <c r="D306" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
@@ -24037,12 +24037,12 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+          <t>A1 — update grezzo g (limite superiore, oltre lo Scenario 1)</t>
         </is>
       </c>
       <c r="H306" s="3" t="inlineStr">
         <is>
-          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+          <t>eps_naive=640.0; eps_avanzata=3.9904954117194346e+30; eps_migliore=640.0; nessun accountant RDP, nessun enforcement</t>
         </is>
       </c>
       <c r="I306" s="3" t="inlineStr">
@@ -24052,7 +24052,7 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5004695; Yeom medio=0.4989074674027784; Shadow medio=0.5014131; LiRA composto=0.502175</t>
+          <t>LiRA medio=0.5010308; Yeom medio=0.5012359131513038; Shadow medio=0.5019937999999999; LiRA composto=0.499856</t>
         </is>
       </c>
       <c r="K306" s="3" t="inlineStr">
@@ -24062,7 +24062,7 @@
       </c>
       <c r="L306" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site-eps64/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr">
@@ -24077,7 +24077,7 @@
       </c>
       <c r="O306" s="3" t="inlineStr">
         <is>
-          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3d4d318 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P306" s="3" t="n"/>
@@ -24086,7 +24086,7 @@
     <row r="307" ht="90" customHeight="1">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0.01/experiment_20260925_032646.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260922_234305.json</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
@@ -24100,7 +24100,7 @@
         </is>
       </c>
       <c r="D307" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E307" s="3" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49852079999999993; Yeom medio=0.5012063210441634; Shadow medio=0.5031516999999999; LiRA composto=0.499601</t>
+          <t>LiRA medio=0.5001295; Yeom medio=0.49683259053359585; Shadow medio=0.49730420000000003; LiRA composto=0.49799</t>
         </is>
       </c>
       <c r="K307" s="3" t="inlineStr">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="L307" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M307" s="4" t="inlineStr">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="O307" s="3" t="inlineStr">
         <is>
-          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P307" s="3" t="n"/>
@@ -24163,7 +24163,7 @@
     <row r="308" ht="90" customHeight="1">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0.01/experiment_20260925_084437.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_022133.json</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="D308" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49975250000000004; Yeom medio=0.5038203772885959; Shadow medio=0.5022984; LiRA composto=0.501778</t>
+          <t>LiRA medio=0.5002134; Yeom medio=0.4992528097560955; Shadow medio=0.5018565999999999; LiRA composto=0.496275</t>
         </is>
       </c>
       <c r="K308" s="3" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="L308" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M308" s="4" t="inlineStr">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="O308" s="3" t="inlineStr">
         <is>
-          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P308" s="3" t="n"/>
@@ -24240,7 +24240,7 @@
     <row r="309" ht="90" customHeight="1">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0.01/experiment_20260925_133815.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_045959.json</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
@@ -24254,7 +24254,7 @@
         </is>
       </c>
       <c r="D309" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.4984249; Yeom medio=0.5007472539951816; Shadow medio=0.5031239000000001; LiRA composto=0.50021</t>
+          <t>LiRA medio=0.49730750000000007; Yeom medio=0.5013561115504457; Shadow medio=0.502413; LiRA composto=0.494383</t>
         </is>
       </c>
       <c r="K309" s="3" t="inlineStr">
@@ -24293,7 +24293,7 @@
       </c>
       <c r="L309" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M309" s="4" t="inlineStr">
@@ -24308,7 +24308,7 @@
       </c>
       <c r="O309" s="3" t="inlineStr">
         <is>
-          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P309" s="3" t="n"/>
@@ -24317,7 +24317,7 @@
     <row r="310" ht="90" customHeight="1">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0/experiment_20260924_164137.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_073901.json</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -24331,11 +24331,11 @@
         </is>
       </c>
       <c r="D310" s="3" t="n">
-        <v>42</v>
+        <v>789</v>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>FedAvg, mu=0.0</t>
+          <t>FedProx, mu=0.01</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49936689999999995; Yeom medio=0.49896478232850994; Shadow medio=0.499537; LiRA composto=0.501141</t>
+          <t>LiRA medio=0.5003536000000001; Yeom medio=0.5037016364627064; Shadow medio=0.5024371000000001; LiRA composto=0.500249</t>
         </is>
       </c>
       <c r="K310" s="3" t="inlineStr">
@@ -24370,7 +24370,7 @@
       </c>
       <c r="L310" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M310" s="4" t="inlineStr">
@@ -24385,7 +24385,7 @@
       </c>
       <c r="O310" s="3" t="inlineStr">
         <is>
-          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P310" s="3" t="n"/>
@@ -24394,7 +24394,7 @@
     <row r="311" ht="90" customHeight="1">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0/experiment_20260924_214509.json</t>
+          <t>altre_macchine: rq2-per_site/experiment_20260923_101922.json</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
@@ -24408,11 +24408,11 @@
         </is>
       </c>
       <c r="D311" s="3" t="n">
-        <v>123</v>
+        <v>1234</v>
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>FedAvg, mu=0.0</t>
+          <t>FedProx, mu=0.01</t>
         </is>
       </c>
       <c r="F311" s="3" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5018366; Yeom medio=0.4994514143625247; Shadow medio=0.49923510000000004; LiRA composto=0.501229</t>
+          <t>LiRA medio=0.4997687; Yeom medio=0.5006942539356262; Shadow medio=0.5027999999999999; LiRA composto=0.502273</t>
         </is>
       </c>
       <c r="K311" s="3" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="L311" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq2-per_site/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M311" s="4" t="inlineStr">
@@ -24462,7 +24462,7 @@
       </c>
       <c r="O311" s="3" t="inlineStr">
         <is>
-          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+          <t>nessun difetto noto; commit 3815da7 registrato, hash degli split non registrato</t>
         </is>
       </c>
       <c r="P311" s="3" t="n"/>
@@ -24471,7 +24471,7 @@
     <row r="312" ht="90" customHeight="1">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0/experiment_20260925_024537.json</t>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260924_165648.json</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -24485,11 +24485,11 @@
         </is>
       </c>
       <c r="D312" s="3" t="n">
-        <v>456</v>
+        <v>42</v>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>FedAvg, mu=0.0</t>
+          <t>FedProx, mu=0.01</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.49861310000000003; Yeom medio=0.500195309199002; Shadow medio=0.4969758000000001; LiRA composto=0.494877</t>
+          <t>LiRA medio=0.5015818; Yeom medio=0.4964074975793191; Shadow medio=0.49682729999999997; LiRA composto=0.503803</t>
         </is>
       </c>
       <c r="K312" s="3" t="inlineStr">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="L312" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M312" s="4" t="inlineStr">
@@ -24548,7 +24548,7 @@
     <row r="313" ht="90" customHeight="1">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0/experiment_20260925_074700.json</t>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260924_221235.json</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
@@ -24562,11 +24562,11 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>789</v>
+        <v>123</v>
       </c>
       <c r="E313" s="3" t="inlineStr">
         <is>
-          <t>FedAvg, mu=0.0</t>
+          <t>FedProx, mu=0.01</t>
         </is>
       </c>
       <c r="F313" s="3" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5010486000000001; Yeom medio=0.5041437448294415; Shadow medio=0.5024178; LiRA composto=0.501158</t>
+          <t>LiRA medio=0.5004695; Yeom medio=0.4989074674027784; Shadow medio=0.5014131; LiRA composto=0.502175</t>
         </is>
       </c>
       <c r="K313" s="3" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="L313" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M313" s="4" t="inlineStr">
@@ -24625,7 +24625,7 @@
     <row r="314" ht="90" customHeight="1">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>altre_macchine: rq3-mu0/experiment_20260925_124719.json</t>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260925_032646.json</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -24639,11 +24639,11 @@
         </is>
       </c>
       <c r="D314" s="3" t="n">
-        <v>1234</v>
+        <v>456</v>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>FedAvg, mu=0.0</t>
+          <t>FedProx, mu=0.01</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
-          <t>LiRA medio=0.5002865; Yeom medio=0.49920311493345915; Shadow medio=0.4992279; LiRA composto=0.505826</t>
+          <t>LiRA medio=0.49852079999999993; Yeom medio=0.5012063210441634; Shadow medio=0.5031516999999999; LiRA composto=0.499601</t>
         </is>
       </c>
       <c r="K314" s="3" t="inlineStr">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="L314" s="3" t="inlineStr">
         <is>
-          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
         </is>
       </c>
       <c r="M314" s="4" t="inlineStr">
@@ -24698,6 +24698,545 @@
       </c>
       <c r="P314" s="3" t="n"/>
       <c r="Q314" s="3" t="n"/>
+    </row>
+    <row r="315" ht="90" customHeight="1">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260925_084437.json</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I315" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J315" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49975250000000004; Yeom medio=0.5038203772885959; Shadow medio=0.5022984; LiRA composto=0.501778</t>
+        </is>
+      </c>
+      <c r="K315" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L315" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M315" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N315" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O315" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P315" s="3" t="n"/>
+      <c r="Q315" s="3" t="n"/>
+    </row>
+    <row r="316" ht="90" customHeight="1">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0.01/experiment_20260925_133815.json</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>FedProx, mu=0.01</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I316" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J316" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.4984249; Yeom medio=0.5007472539951816; Shadow medio=0.5031239000000001; LiRA composto=0.50021</t>
+        </is>
+      </c>
+      <c r="K316" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L316" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0.01/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M316" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N316" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O316" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P316" s="3" t="n"/>
+      <c r="Q316" s="3" t="n"/>
+    </row>
+    <row r="317" ht="90" customHeight="1">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260924_164137.json</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I317" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J317" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49936689999999995; Yeom medio=0.49896478232850994; Shadow medio=0.499537; LiRA composto=0.501141</t>
+        </is>
+      </c>
+      <c r="K317" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L317" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M317" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N317" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O317" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P317" s="3" t="n"/>
+      <c r="Q317" s="3" t="n"/>
+    </row>
+    <row r="318" ht="90" customHeight="1">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260924_214509.json</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H318" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I318" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J318" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5018366; Yeom medio=0.4994514143625247; Shadow medio=0.49923510000000004; LiRA composto=0.501229</t>
+        </is>
+      </c>
+      <c r="K318" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L318" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M318" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N318" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O318" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P318" s="3" t="n"/>
+      <c r="Q318" s="3" t="n"/>
+    </row>
+    <row r="319" ht="90" customHeight="1">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260925_024537.json</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H319" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I319" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J319" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.49861310000000003; Yeom medio=0.500195309199002; Shadow medio=0.4969758000000001; LiRA composto=0.494877</t>
+        </is>
+      </c>
+      <c r="K319" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L319" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M319" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N319" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O319" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P319" s="3" t="n"/>
+      <c r="Q319" s="3" t="n"/>
+    </row>
+    <row r="320" ht="90" customHeight="1">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260925_074700.json</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H320" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I320" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J320" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5010486000000001; Yeom medio=0.5041437448294415; Shadow medio=0.5024178; LiRA composto=0.501158</t>
+        </is>
+      </c>
+      <c r="K320" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L320" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M320" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N320" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O320" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P320" s="3" t="n"/>
+      <c r="Q320" s="3" t="n"/>
+    </row>
+    <row r="321" ht="90" customHeight="1">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>altre_macchine: rq3-mu0/experiment_20260925_124719.json</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=dp-fedavg; no_dp=True; eps=1.0; delta=1e-05; round=10; epoche=50; batch=32; feature=n.d.; hidden=None; latent=4</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>FedAvg, mu=0.0</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>naturale</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>A0 — update non privatizzato (nessun clipping, nessun rumore)</t>
+        </is>
+      </c>
+      <c r="H321" s="3" t="inlineStr">
+        <is>
+          <t>eps_naive=None; eps_avanzata=None; eps_migliore=None; nessun accountant RDP, nessun enforcement</t>
+        </is>
+      </c>
+      <c r="I321" s="3" t="inlineStr">
+        <is>
+          <t>10 round valutati</t>
+        </is>
+      </c>
+      <c r="J321" s="3" t="inlineStr">
+        <is>
+          <t>LiRA medio=0.5002865; Yeom medio=0.49920311493345915; Shadow medio=0.4992279; LiRA composto=0.505826</t>
+        </is>
+      </c>
+      <c r="K321" s="3" t="inlineStr">
+        <is>
+          <t>nessun log associabile per nome</t>
+        </is>
+      </c>
+      <c r="L321" s="3" t="inlineStr">
+        <is>
+          <t>experiments_altre_macchine/rq3-mu0/ (JSON + xlsx + history/)</t>
+        </is>
+      </c>
+      <c r="M321" s="4" t="inlineStr">
+        <is>
+          <t>completata da verificare</t>
+        </is>
+      </c>
+      <c r="N321" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — inventario</t>
+        </is>
+      </c>
+      <c r="O321" s="3" t="inlineStr">
+        <is>
+          <t>commit 478d471 con modifiche non committate al salvataggio (-dirty): verificare con git diff che non toccassero il codice eseguito; hash degli split non registrato</t>
+        </is>
+      </c>
+      <c r="P321" s="3" t="n"/>
+      <c r="Q321" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
